--- a/PLBY.xlsx
+++ b/PLBY.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1.Finance\Anaylsen\Models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62D3F351-3F99-45D3-895A-6DFEF12E348E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C4D815B-ECE6-4B6A-A61A-5C2FB5093755}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="225" yWindow="1950" windowWidth="38175" windowHeight="15240" xr2:uid="{D4E60F1B-0F1D-4B9A-94C9-25B8981ADED0}"/>
+    <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="20925" activeTab="1" xr2:uid="{D4E60F1B-0F1D-4B9A-94C9-25B8981ADED0}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="63">
   <si>
     <t>Playboy Group</t>
   </si>
@@ -215,6 +215,18 @@
   <si>
     <t>in 2022 sold corporate jet.</t>
   </si>
+  <si>
+    <t>Q325</t>
+  </si>
+  <si>
+    <t>Q125</t>
+  </si>
+  <si>
+    <t>Q225</t>
+  </si>
+  <si>
+    <t>Q425</t>
+  </si>
 </sst>
 </file>
 
@@ -224,13 +236,19 @@
     <numFmt numFmtId="164" formatCode="#,##0.0"/>
     <numFmt numFmtId="165" formatCode="#,##0.000"/>
   </numFmts>
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
@@ -294,23 +312,26 @@
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="2" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="4" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="4" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hyperlink" xfId="2" builtinId="8"/>
@@ -667,7 +688,7 @@
         <v>2</v>
       </c>
       <c r="H2" s="2">
-        <v>1.2</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.2">
@@ -675,10 +696,10 @@
         <v>3</v>
       </c>
       <c r="H3" s="4">
-        <v>93.747068999999996</v>
-      </c>
-      <c r="I3" s="3" t="s">
-        <v>18</v>
+        <v>107.757372</v>
+      </c>
+      <c r="I3" s="11" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.2">
@@ -690,7 +711,7 @@
       </c>
       <c r="H4" s="4">
         <f>+H3*H2</f>
-        <v>112.4964828</v>
+        <v>183.18753240000001</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.2">
@@ -701,11 +722,10 @@
         <v>5</v>
       </c>
       <c r="H5" s="4">
-        <f>30.904+0.1</f>
-        <v>31.004000000000001</v>
-      </c>
-      <c r="I5" s="3" t="s">
-        <v>18</v>
+        <v>27.463000000000001</v>
+      </c>
+      <c r="I5" s="11" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.2">
@@ -713,11 +733,11 @@
         <v>6</v>
       </c>
       <c r="H6" s="4">
-        <f>0.381+176.194</f>
-        <v>176.57499999999999</v>
-      </c>
-      <c r="I6" s="3" t="s">
-        <v>18</v>
+        <f>175.271+1.524</f>
+        <v>176.79499999999999</v>
+      </c>
+      <c r="I6" s="11" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.2">
@@ -726,7 +746,7 @@
       </c>
       <c r="H7" s="4">
         <f>+H4-H5+H6</f>
-        <v>258.06748279999999</v>
+        <v>332.5195324</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.2">
@@ -773,25 +793,26 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8A91E0A3-3CAA-440F-9224-A6E6ECBE846B}">
-  <dimension ref="A1:CF273"/>
+  <dimension ref="A1:CJ273"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.42578125" style="2" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="30" style="2" bestFit="1" customWidth="1"/>
     <col min="3" max="10" width="9.28515625" style="2" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="9.140625" style="2"/>
-    <col min="12" max="15" width="9.28515625" style="2" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="9.42578125" style="2" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="9.28515625" style="2" bestFit="1" customWidth="1"/>
-    <col min="19" max="16384" width="9.140625" style="2"/>
+    <col min="11" max="14" width="9.28515625" style="2" customWidth="1"/>
+    <col min="15" max="15" width="9.140625" style="2"/>
+    <col min="16" max="19" width="9.28515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="9.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="9.28515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="23" max="16384" width="9.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:84" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:88" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:84" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:88" x14ac:dyDescent="0.2">
       <c r="C2" s="3" t="s">
         <v>12</v>
       </c>
@@ -816,29 +837,41 @@
       <c r="J2" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="L2" s="3" t="s">
+      <c r="K2" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="L2" s="11" t="s">
+        <v>61</v>
+      </c>
+      <c r="M2" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="N2" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="P2" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="M2" s="3" t="s">
+      <c r="Q2" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="N2" s="3" t="s">
+      <c r="R2" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="O2" s="3" t="s">
+      <c r="S2" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="P2" s="3" t="s">
+      <c r="T2" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="Q2" s="3" t="s">
+      <c r="U2" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="R2" s="3" t="s">
+      <c r="V2" s="3" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="3" spans="1:84" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:88" x14ac:dyDescent="0.2">
       <c r="B3" s="2" t="s">
         <v>37</v>
       </c>
@@ -919,8 +952,12 @@
       <c r="BM3" s="4"/>
       <c r="BN3" s="4"/>
       <c r="BO3" s="4"/>
-    </row>
-    <row r="4" spans="1:84" x14ac:dyDescent="0.2">
+      <c r="BP3" s="4"/>
+      <c r="BQ3" s="4"/>
+      <c r="BR3" s="4"/>
+      <c r="BS3" s="4"/>
+    </row>
+    <row r="4" spans="1:88" x14ac:dyDescent="0.2">
       <c r="B4" s="2" t="s">
         <v>38</v>
       </c>
@@ -1001,8 +1038,12 @@
       <c r="BM4" s="4"/>
       <c r="BN4" s="4"/>
       <c r="BO4" s="4"/>
-    </row>
-    <row r="5" spans="1:84" x14ac:dyDescent="0.2">
+      <c r="BP4" s="4"/>
+      <c r="BQ4" s="4"/>
+      <c r="BR4" s="4"/>
+      <c r="BS4" s="4"/>
+    </row>
+    <row r="5" spans="1:88" x14ac:dyDescent="0.2">
       <c r="B5" s="2" t="s">
         <v>39</v>
       </c>
@@ -1083,8 +1124,12 @@
       <c r="BM5" s="4"/>
       <c r="BN5" s="4"/>
       <c r="BO5" s="4"/>
-    </row>
-    <row r="6" spans="1:84" x14ac:dyDescent="0.2">
+      <c r="BP5" s="4"/>
+      <c r="BQ5" s="4"/>
+      <c r="BR5" s="4"/>
+      <c r="BS5" s="4"/>
+    </row>
+    <row r="6" spans="1:88" x14ac:dyDescent="0.2">
       <c r="B6" s="2" t="s">
         <v>40</v>
       </c>
@@ -1165,8 +1210,12 @@
       <c r="BM6" s="4"/>
       <c r="BN6" s="4"/>
       <c r="BO6" s="4"/>
-    </row>
-    <row r="7" spans="1:84" x14ac:dyDescent="0.2">
+      <c r="BP6" s="4"/>
+      <c r="BQ6" s="4"/>
+      <c r="BR6" s="4"/>
+      <c r="BS6" s="4"/>
+    </row>
+    <row r="7" spans="1:88" x14ac:dyDescent="0.2">
       <c r="B7" s="5" t="s">
         <v>19</v>
       </c>
@@ -1180,7 +1229,7 @@
         <v>16.276</v>
       </c>
       <c r="F7" s="6">
-        <f>+Q7-SUM(C7:E7)</f>
+        <f>+U7-SUM(C7:E7)</f>
         <v>56.36999999999999</v>
       </c>
       <c r="G7" s="6">
@@ -1193,27 +1242,29 @@
         <v>12.864000000000001</v>
       </c>
       <c r="J7" s="6">
-        <f>+R7-SUM(G7:I7)</f>
+        <f>+V7-SUM(G7:I7)</f>
         <v>50.067000000000007</v>
       </c>
       <c r="K7" s="6"/>
       <c r="L7" s="6"/>
-      <c r="M7" s="6"/>
+      <c r="M7" s="6">
+        <v>28.994</v>
+      </c>
       <c r="N7" s="6"/>
       <c r="O7" s="6"/>
-      <c r="P7" s="6">
+      <c r="P7" s="6"/>
+      <c r="Q7" s="6"/>
+      <c r="R7" s="6"/>
+      <c r="S7" s="6"/>
+      <c r="T7" s="6">
         <v>185.536</v>
       </c>
-      <c r="Q7" s="6">
+      <c r="U7" s="6">
         <v>142.94999999999999</v>
       </c>
-      <c r="R7" s="6">
+      <c r="V7" s="6">
         <v>116.13500000000001</v>
       </c>
-      <c r="S7" s="4"/>
-      <c r="T7" s="4"/>
-      <c r="U7" s="4"/>
-      <c r="V7" s="4"/>
       <c r="W7" s="4"/>
       <c r="X7" s="4"/>
       <c r="Y7" s="4"/>
@@ -1276,8 +1327,12 @@
       <c r="CD7" s="4"/>
       <c r="CE7" s="4"/>
       <c r="CF7" s="4"/>
-    </row>
-    <row r="8" spans="1:84" x14ac:dyDescent="0.2">
+      <c r="CG7" s="4"/>
+      <c r="CH7" s="4"/>
+      <c r="CI7" s="4"/>
+      <c r="CJ7" s="4"/>
+    </row>
+    <row r="8" spans="1:88" x14ac:dyDescent="0.2">
       <c r="B8" s="2" t="s">
         <v>20</v>
       </c>
@@ -1291,7 +1346,7 @@
         <v>1.282</v>
       </c>
       <c r="F8" s="4">
-        <f>+Q8-SUM(C8:E8)</f>
+        <f>+U8-SUM(C8:E8)</f>
         <v>22.058999999999997</v>
       </c>
       <c r="G8" s="4">
@@ -1304,27 +1359,29 @@
         <v>3.82</v>
       </c>
       <c r="J8" s="4">
-        <f>+R8-SUM(G8:I8)</f>
+        <f>+V8-SUM(G8:I8)</f>
         <v>17.435000000000002</v>
       </c>
       <c r="K8" s="4"/>
       <c r="L8" s="4"/>
-      <c r="M8" s="4"/>
+      <c r="M8" s="4">
+        <v>6.9539999999999997</v>
+      </c>
       <c r="N8" s="4"/>
       <c r="O8" s="4"/>
-      <c r="P8" s="4">
+      <c r="P8" s="4"/>
+      <c r="Q8" s="4"/>
+      <c r="R8" s="4"/>
+      <c r="S8" s="4"/>
+      <c r="T8" s="4">
         <v>82.944999999999993</v>
       </c>
-      <c r="Q8" s="4">
+      <c r="U8" s="4">
         <v>54.777000000000001</v>
       </c>
-      <c r="R8" s="4">
+      <c r="V8" s="4">
         <v>41.78</v>
       </c>
-      <c r="S8" s="4"/>
-      <c r="T8" s="4"/>
-      <c r="U8" s="4"/>
-      <c r="V8" s="4"/>
       <c r="W8" s="4"/>
       <c r="X8" s="4"/>
       <c r="Y8" s="4"/>
@@ -1387,8 +1444,12 @@
       <c r="CD8" s="4"/>
       <c r="CE8" s="4"/>
       <c r="CF8" s="4"/>
-    </row>
-    <row r="9" spans="1:84" x14ac:dyDescent="0.2">
+      <c r="CG8" s="4"/>
+      <c r="CH8" s="4"/>
+      <c r="CI8" s="4"/>
+      <c r="CJ8" s="4"/>
+    </row>
+    <row r="9" spans="1:88" x14ac:dyDescent="0.2">
       <c r="B9" s="2" t="s">
         <v>21</v>
       </c>
@@ -1421,42 +1482,51 @@
         <v>9.0440000000000005</v>
       </c>
       <c r="J9" s="4">
-        <f t="shared" ref="J9" si="1">+J7-J8</f>
+        <f t="shared" ref="J9:M9" si="1">+J7-J8</f>
         <v>32.632000000000005</v>
       </c>
-      <c r="K9" s="4"/>
+      <c r="K9" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
       <c r="L9" s="4">
-        <f t="shared" ref="L9:M9" si="2">+L7-L8</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="M9" s="4">
+        <f t="shared" si="1"/>
+        <v>22.04</v>
+      </c>
+      <c r="N9" s="4"/>
+      <c r="O9" s="4"/>
+      <c r="P9" s="4">
+        <f t="shared" ref="P9:Q9" si="2">+P7-P8</f>
+        <v>0</v>
+      </c>
+      <c r="Q9" s="4">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="N9" s="4">
-        <f t="shared" ref="N9" si="3">+N7-N8</f>
+      <c r="R9" s="4">
+        <f t="shared" ref="R9" si="3">+R7-R8</f>
         <v>0</v>
       </c>
-      <c r="O9" s="4">
-        <f t="shared" ref="O9" si="4">+O7-O8</f>
+      <c r="S9" s="4">
+        <f t="shared" ref="S9" si="4">+S7-S8</f>
         <v>0</v>
       </c>
-      <c r="P9" s="4">
-        <f t="shared" ref="P9" si="5">+P7-P8</f>
+      <c r="T9" s="4">
+        <f t="shared" ref="T9" si="5">+T7-T8</f>
         <v>102.59100000000001</v>
       </c>
-      <c r="Q9" s="4">
-        <f t="shared" ref="Q9" si="6">+Q7-Q8</f>
+      <c r="U9" s="4">
+        <f t="shared" ref="U9" si="6">+U7-U8</f>
         <v>88.172999999999988</v>
       </c>
-      <c r="R9" s="4">
-        <f t="shared" ref="R9" si="7">+R7-R8</f>
+      <c r="V9" s="4">
+        <f t="shared" ref="V9" si="7">+V7-V8</f>
         <v>74.355000000000004</v>
       </c>
-      <c r="S9" s="4"/>
-      <c r="T9" s="4"/>
-      <c r="U9" s="4"/>
-      <c r="V9" s="4"/>
       <c r="W9" s="4"/>
       <c r="X9" s="4"/>
       <c r="Y9" s="4"/>
@@ -1519,8 +1589,12 @@
       <c r="CD9" s="4"/>
       <c r="CE9" s="4"/>
       <c r="CF9" s="4"/>
-    </row>
-    <row r="10" spans="1:84" x14ac:dyDescent="0.2">
+      <c r="CG9" s="4"/>
+      <c r="CH9" s="4"/>
+      <c r="CI9" s="4"/>
+      <c r="CJ9" s="4"/>
+    </row>
+    <row r="10" spans="1:88" x14ac:dyDescent="0.2">
       <c r="B10" s="2" t="s">
         <v>22</v>
       </c>
@@ -1534,7 +1608,7 @@
         <v>15.471</v>
       </c>
       <c r="F10" s="4">
-        <f>+Q10-SUM(C10:E10)</f>
+        <f>+U10-SUM(C10:E10)</f>
         <v>34.161000000000001</v>
       </c>
       <c r="G10" s="4">
@@ -1547,27 +1621,29 @@
         <v>15.478999999999999</v>
       </c>
       <c r="J10" s="4">
-        <f>+R10-SUM(G10:I10)</f>
+        <f>+V10-SUM(G10:I10)</f>
         <v>35.435999999999993</v>
       </c>
       <c r="K10" s="4"/>
       <c r="L10" s="4"/>
-      <c r="M10" s="4"/>
+      <c r="M10" s="4">
+        <v>20.434000000000001</v>
+      </c>
       <c r="N10" s="4"/>
       <c r="O10" s="4"/>
-      <c r="P10" s="4">
+      <c r="P10" s="4"/>
+      <c r="Q10" s="4"/>
+      <c r="R10" s="4"/>
+      <c r="S10" s="4"/>
+      <c r="T10" s="4">
         <v>150.535</v>
       </c>
-      <c r="Q10" s="4">
+      <c r="U10" s="4">
         <v>123.554</v>
       </c>
-      <c r="R10" s="4">
+      <c r="V10" s="4">
         <v>98.715999999999994</v>
       </c>
-      <c r="S10" s="4"/>
-      <c r="T10" s="4"/>
-      <c r="U10" s="4"/>
-      <c r="V10" s="4"/>
       <c r="W10" s="4"/>
       <c r="X10" s="4"/>
       <c r="Y10" s="4"/>
@@ -1630,8 +1706,12 @@
       <c r="CD10" s="4"/>
       <c r="CE10" s="4"/>
       <c r="CF10" s="4"/>
-    </row>
-    <row r="11" spans="1:84" x14ac:dyDescent="0.2">
+      <c r="CG10" s="4"/>
+      <c r="CH10" s="4"/>
+      <c r="CI10" s="4"/>
+      <c r="CJ10" s="4"/>
+    </row>
+    <row r="11" spans="1:88" x14ac:dyDescent="0.2">
       <c r="B11" s="2" t="s">
         <v>23</v>
       </c>
@@ -1645,7 +1725,7 @@
         <v>0.39200000000000002</v>
       </c>
       <c r="F11" s="4">
-        <f>+Q11-SUM(C11:E11)</f>
+        <f>+U11-SUM(C11:E11)</f>
         <v>8.2519999999999811</v>
       </c>
       <c r="G11" s="4">
@@ -1658,27 +1738,29 @@
         <v>21.707000000000001</v>
       </c>
       <c r="J11" s="4">
-        <f>+R11-SUM(G11:I11)</f>
+        <f>+V11-SUM(G11:I11)</f>
         <v>1.3550000000000004</v>
       </c>
       <c r="K11" s="4"/>
       <c r="L11" s="4"/>
-      <c r="M11" s="4"/>
+      <c r="M11" s="4">
+        <v>0.245</v>
+      </c>
       <c r="N11" s="4"/>
       <c r="O11" s="4"/>
-      <c r="P11" s="4">
+      <c r="P11" s="4"/>
+      <c r="Q11" s="4"/>
+      <c r="R11" s="4"/>
+      <c r="S11" s="4"/>
+      <c r="T11" s="4">
         <v>283.5</v>
       </c>
-      <c r="Q11" s="4">
+      <c r="U11" s="4">
         <v>154.88399999999999</v>
       </c>
-      <c r="R11" s="4">
+      <c r="V11" s="4">
         <v>26.077999999999999</v>
       </c>
-      <c r="S11" s="4"/>
-      <c r="T11" s="4"/>
-      <c r="U11" s="4"/>
-      <c r="V11" s="4"/>
       <c r="W11" s="4"/>
       <c r="X11" s="4"/>
       <c r="Y11" s="4"/>
@@ -1741,8 +1823,12 @@
       <c r="CD11" s="4"/>
       <c r="CE11" s="4"/>
       <c r="CF11" s="4"/>
-    </row>
-    <row r="12" spans="1:84" x14ac:dyDescent="0.2">
+      <c r="CG11" s="4"/>
+      <c r="CH11" s="4"/>
+      <c r="CI11" s="4"/>
+      <c r="CJ11" s="4"/>
+    </row>
+    <row r="12" spans="1:88" x14ac:dyDescent="0.2">
       <c r="B12" s="2" t="s">
         <v>45</v>
       </c>
@@ -1756,7 +1842,7 @@
         <v>0.71799999999999997</v>
       </c>
       <c r="F12" s="4">
-        <f>+Q12-SUM(C12:E12)</f>
+        <f>+U12-SUM(C12:E12)</f>
         <v>-0.35499999999999993</v>
       </c>
       <c r="G12" s="4">
@@ -1769,29 +1855,31 @@
         <v>0</v>
       </c>
       <c r="J12" s="4">
-        <f>+R12-SUM(G12:I12)</f>
+        <f>+V12-SUM(G12:I12)</f>
         <v>0.41700000000000004</v>
       </c>
       <c r="K12" s="4"/>
       <c r="L12" s="4"/>
-      <c r="M12" s="4"/>
+      <c r="M12" s="4">
+        <v>-5.0000000000000001E-3</v>
+      </c>
       <c r="N12" s="4"/>
       <c r="O12" s="4"/>
-      <c r="P12" s="4">
+      <c r="P12" s="4"/>
+      <c r="Q12" s="4"/>
+      <c r="R12" s="4"/>
+      <c r="S12" s="4"/>
+      <c r="T12" s="4">
         <f>-(29.173+5.689+0.482)</f>
         <v>-35.343999999999994</v>
       </c>
-      <c r="Q12" s="4">
+      <c r="U12" s="4">
         <f>-0.436+0.54</f>
         <v>0.10400000000000004</v>
       </c>
-      <c r="R12" s="4">
+      <c r="V12" s="4">
         <v>0.39900000000000002</v>
       </c>
-      <c r="S12" s="4"/>
-      <c r="T12" s="4"/>
-      <c r="U12" s="4"/>
-      <c r="V12" s="4"/>
       <c r="W12" s="4"/>
       <c r="X12" s="4"/>
       <c r="Y12" s="4"/>
@@ -1854,8 +1942,12 @@
       <c r="CD12" s="4"/>
       <c r="CE12" s="4"/>
       <c r="CF12" s="4"/>
-    </row>
-    <row r="13" spans="1:84" x14ac:dyDescent="0.2">
+      <c r="CG12" s="4"/>
+      <c r="CH12" s="4"/>
+      <c r="CI12" s="4"/>
+      <c r="CJ12" s="4"/>
+    </row>
+    <row r="13" spans="1:88" x14ac:dyDescent="0.2">
       <c r="B13" s="2" t="s">
         <v>24</v>
       </c>
@@ -1888,42 +1980,51 @@
         <v>-28.141999999999999</v>
       </c>
       <c r="J13" s="4">
-        <f t="shared" ref="J13" si="9">+J9-SUM(J10:J12)</f>
+        <f t="shared" ref="J13:M13" si="9">+J9-SUM(J10:J12)</f>
         <v>-4.5759999999999934</v>
       </c>
-      <c r="K13" s="4"/>
+      <c r="K13" s="4">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
       <c r="L13" s="4">
-        <f t="shared" ref="L13:M13" si="10">+L9-SUM(L10:L12)</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="M13" s="4">
+        <f t="shared" si="9"/>
+        <v>1.3659999999999961</v>
+      </c>
+      <c r="N13" s="4"/>
+      <c r="O13" s="4"/>
+      <c r="P13" s="4">
+        <f t="shared" ref="P13:Q13" si="10">+P9-SUM(P10:P12)</f>
+        <v>0</v>
+      </c>
+      <c r="Q13" s="4">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="N13" s="4">
-        <f t="shared" ref="N13" si="11">+N9-SUM(N10:N12)</f>
+      <c r="R13" s="4">
+        <f t="shared" ref="R13" si="11">+R9-SUM(R10:R12)</f>
         <v>0</v>
       </c>
-      <c r="O13" s="4">
-        <f t="shared" ref="O13" si="12">+O9-SUM(O10:O12)</f>
+      <c r="S13" s="4">
+        <f t="shared" ref="S13" si="12">+S9-SUM(S10:S12)</f>
         <v>0</v>
       </c>
-      <c r="P13" s="4">
-        <f t="shared" ref="P13" si="13">+P9-SUM(P10:P12)</f>
+      <c r="T13" s="4">
+        <f t="shared" ref="T13" si="13">+T9-SUM(T10:T12)</f>
         <v>-296.09999999999997</v>
       </c>
-      <c r="Q13" s="4">
-        <f t="shared" ref="Q13" si="14">+Q9-SUM(Q10:Q12)</f>
+      <c r="U13" s="4">
+        <f t="shared" ref="U13" si="14">+U9-SUM(U10:U12)</f>
         <v>-190.36899999999997</v>
       </c>
-      <c r="R13" s="4">
-        <f t="shared" ref="R13" si="15">+R9-SUM(R10:R12)</f>
+      <c r="V13" s="4">
+        <f t="shared" ref="V13" si="15">+V9-SUM(V10:V12)</f>
         <v>-50.837999999999994</v>
       </c>
-      <c r="S13" s="4"/>
-      <c r="T13" s="4"/>
-      <c r="U13" s="4"/>
-      <c r="V13" s="4"/>
       <c r="W13" s="4"/>
       <c r="X13" s="4"/>
       <c r="Y13" s="4"/>
@@ -1986,8 +2087,12 @@
       <c r="CD13" s="4"/>
       <c r="CE13" s="4"/>
       <c r="CF13" s="4"/>
-    </row>
-    <row r="14" spans="1:84" x14ac:dyDescent="0.2">
+      <c r="CG13" s="4"/>
+      <c r="CH13" s="4"/>
+      <c r="CI13" s="4"/>
+      <c r="CJ13" s="4"/>
+    </row>
+    <row r="14" spans="1:88" x14ac:dyDescent="0.2">
       <c r="B14" s="2" t="s">
         <v>26</v>
       </c>
@@ -2001,7 +2106,7 @@
         <v>6.62</v>
       </c>
       <c r="F14" s="4">
-        <f>+Q14-SUM(C14:E14)</f>
+        <f>+U14-SUM(C14:E14)</f>
         <v>5.7070000000000007</v>
       </c>
       <c r="G14" s="4">
@@ -2014,27 +2119,29 @@
         <v>6.6859999999999999</v>
       </c>
       <c r="J14" s="4">
-        <f>+R14-SUM(G14:I14)</f>
+        <f>+V14-SUM(G14:I14)</f>
         <v>3.9879999999999995</v>
       </c>
       <c r="K14" s="4"/>
       <c r="L14" s="4"/>
-      <c r="M14" s="4"/>
+      <c r="M14" s="4">
+        <v>1.925</v>
+      </c>
       <c r="N14" s="4"/>
       <c r="O14" s="4"/>
-      <c r="P14" s="4">
+      <c r="P14" s="4"/>
+      <c r="Q14" s="4"/>
+      <c r="R14" s="4"/>
+      <c r="S14" s="4"/>
+      <c r="T14" s="4">
         <v>17.719000000000001</v>
       </c>
-      <c r="Q14" s="4">
+      <c r="U14" s="4">
         <v>23.292999999999999</v>
       </c>
-      <c r="R14" s="4">
+      <c r="V14" s="4">
         <v>23.689</v>
       </c>
-      <c r="S14" s="4"/>
-      <c r="T14" s="4"/>
-      <c r="U14" s="4"/>
-      <c r="V14" s="4"/>
       <c r="W14" s="4"/>
       <c r="X14" s="4"/>
       <c r="Y14" s="4"/>
@@ -2097,8 +2204,12 @@
       <c r="CD14" s="4"/>
       <c r="CE14" s="4"/>
       <c r="CF14" s="4"/>
-    </row>
-    <row r="15" spans="1:84" x14ac:dyDescent="0.2">
+      <c r="CG14" s="4"/>
+      <c r="CH14" s="4"/>
+      <c r="CI14" s="4"/>
+      <c r="CJ14" s="4"/>
+    </row>
+    <row r="15" spans="1:88" x14ac:dyDescent="0.2">
       <c r="B15" s="2" t="s">
         <v>25</v>
       </c>
@@ -2114,7 +2225,7 @@
         <v>0.22800000000000001</v>
       </c>
       <c r="F15" s="4">
-        <f>+Q15-SUM(C15:E15)</f>
+        <f>+U15-SUM(C15:E15)</f>
         <v>0.33799999999999919</v>
       </c>
       <c r="G15" s="4">
@@ -2127,29 +2238,31 @@
         <v>1.6160000000000001</v>
       </c>
       <c r="J15" s="4">
-        <f>+R15-SUM(G15:I15)</f>
+        <f>+V15-SUM(G15:I15)</f>
         <v>-3.0430000000000001</v>
       </c>
       <c r="K15" s="4"/>
       <c r="L15" s="4"/>
-      <c r="M15" s="4"/>
+      <c r="M15" s="4">
+        <v>0.46</v>
+      </c>
       <c r="N15" s="4"/>
       <c r="O15" s="4"/>
-      <c r="P15" s="4">
+      <c r="P15" s="4"/>
+      <c r="Q15" s="4"/>
+      <c r="R15" s="4"/>
+      <c r="S15" s="4"/>
+      <c r="T15" s="4">
         <f>-1.266+9.401-0.711</f>
         <v>7.4239999999999995</v>
       </c>
-      <c r="Q15" s="4">
+      <c r="U15" s="4">
         <f>6.133+6.505+0.806</f>
         <v>13.443999999999999</v>
       </c>
-      <c r="R15" s="4">
+      <c r="V15" s="4">
         <v>-1.722</v>
       </c>
-      <c r="S15" s="4"/>
-      <c r="T15" s="4"/>
-      <c r="U15" s="4"/>
-      <c r="V15" s="4"/>
       <c r="W15" s="4"/>
       <c r="X15" s="4"/>
       <c r="Y15" s="4"/>
@@ -2212,8 +2325,12 @@
       <c r="CD15" s="4"/>
       <c r="CE15" s="4"/>
       <c r="CF15" s="4"/>
-    </row>
-    <row r="16" spans="1:84" x14ac:dyDescent="0.2">
+      <c r="CG15" s="4"/>
+      <c r="CH15" s="4"/>
+      <c r="CI15" s="4"/>
+      <c r="CJ15" s="4"/>
+    </row>
+    <row r="16" spans="1:88" x14ac:dyDescent="0.2">
       <c r="B16" s="2" t="s">
         <v>27</v>
       </c>
@@ -2230,7 +2347,7 @@
         <v>-7.979000000000001</v>
       </c>
       <c r="F16" s="4">
-        <f t="shared" ref="F16:J16" si="17">+F13-F14+F15</f>
+        <f t="shared" ref="F16:M16" si="17">+F13-F14+F15</f>
         <v>-13.115999999999994</v>
       </c>
       <c r="G16" s="4">
@@ -2249,39 +2366,48 @@
         <f t="shared" si="17"/>
         <v>-11.606999999999992</v>
       </c>
-      <c r="K16" s="4"/>
+      <c r="K16" s="4">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
       <c r="L16" s="4">
-        <f t="shared" ref="L16" si="18">+L13-L14+L15</f>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="M16" s="4">
-        <f t="shared" ref="M16" si="19">+M13-M14+M15</f>
+        <f t="shared" si="17"/>
+        <v>-9.9000000000003918E-2</v>
+      </c>
+      <c r="N16" s="4"/>
+      <c r="O16" s="4"/>
+      <c r="P16" s="4">
+        <f t="shared" ref="P16" si="18">+P13-P14+P15</f>
         <v>0</v>
       </c>
-      <c r="N16" s="4">
-        <f t="shared" ref="N16" si="20">+N13-N14+N15</f>
+      <c r="Q16" s="4">
+        <f t="shared" ref="Q16" si="19">+Q13-Q14+Q15</f>
         <v>0</v>
       </c>
-      <c r="O16" s="4">
-        <f t="shared" ref="O16" si="21">+O13-O14+O15</f>
+      <c r="R16" s="4">
+        <f t="shared" ref="R16" si="20">+R13-R14+R15</f>
         <v>0</v>
       </c>
-      <c r="P16" s="4">
-        <f t="shared" ref="P16" si="22">+P13-P14+P15</f>
+      <c r="S16" s="4">
+        <f t="shared" ref="S16" si="21">+S13-S14+S15</f>
+        <v>0</v>
+      </c>
+      <c r="T16" s="4">
+        <f t="shared" ref="T16" si="22">+T13-T14+T15</f>
         <v>-306.39499999999998</v>
       </c>
-      <c r="Q16" s="4">
-        <f t="shared" ref="Q16" si="23">+Q13-Q14+Q15</f>
+      <c r="U16" s="4">
+        <f t="shared" ref="U16" si="23">+U13-U14+U15</f>
         <v>-200.21799999999999</v>
       </c>
-      <c r="R16" s="4">
-        <f t="shared" ref="R16" si="24">+R13-R14+R15</f>
+      <c r="V16" s="4">
+        <f t="shared" ref="V16" si="24">+V13-V14+V15</f>
         <v>-76.248999999999981</v>
       </c>
-      <c r="S16" s="4"/>
-      <c r="T16" s="4"/>
-      <c r="U16" s="4"/>
-      <c r="V16" s="4"/>
       <c r="W16" s="4"/>
       <c r="X16" s="4"/>
       <c r="Y16" s="4"/>
@@ -2344,8 +2470,12 @@
       <c r="CD16" s="4"/>
       <c r="CE16" s="4"/>
       <c r="CF16" s="4"/>
-    </row>
-    <row r="17" spans="2:84" x14ac:dyDescent="0.2">
+      <c r="CG16" s="4"/>
+      <c r="CH16" s="4"/>
+      <c r="CI16" s="4"/>
+      <c r="CJ16" s="4"/>
+    </row>
+    <row r="17" spans="2:88" x14ac:dyDescent="0.2">
       <c r="B17" s="2" t="s">
         <v>28</v>
       </c>
@@ -2359,7 +2489,7 @@
         <v>-0.92900000000000005</v>
       </c>
       <c r="F17" s="4">
-        <f>+Q17-SUM(C17:E17)</f>
+        <f>+U17-SUM(C17:E17)</f>
         <v>-2.302999999999999</v>
       </c>
       <c r="G17" s="4">
@@ -2372,27 +2502,29 @@
         <v>0.56799999999999995</v>
       </c>
       <c r="J17" s="4">
-        <f>+R17-SUM(G17:I17)</f>
+        <f>+V17-SUM(G17:I17)</f>
         <v>0.91100000000000003</v>
       </c>
       <c r="K17" s="4"/>
       <c r="L17" s="4"/>
-      <c r="M17" s="4"/>
+      <c r="M17" s="4">
+        <v>-0.56000000000000005</v>
+      </c>
       <c r="N17" s="4"/>
       <c r="O17" s="4"/>
-      <c r="P17" s="4">
+      <c r="P17" s="4"/>
+      <c r="Q17" s="4"/>
+      <c r="R17" s="4"/>
+      <c r="S17" s="4"/>
+      <c r="T17" s="4">
         <v>-55.704000000000001</v>
       </c>
-      <c r="Q17" s="4">
+      <c r="U17" s="4">
         <v>-13.77</v>
       </c>
-      <c r="R17" s="4">
+      <c r="V17" s="4">
         <v>3.1480000000000001</v>
       </c>
-      <c r="S17" s="4"/>
-      <c r="T17" s="4"/>
-      <c r="U17" s="4"/>
-      <c r="V17" s="4"/>
       <c r="W17" s="4"/>
       <c r="X17" s="4"/>
       <c r="Y17" s="4"/>
@@ -2455,8 +2587,12 @@
       <c r="CD17" s="4"/>
       <c r="CE17" s="4"/>
       <c r="CF17" s="4"/>
-    </row>
-    <row r="18" spans="2:84" x14ac:dyDescent="0.2">
+      <c r="CG17" s="4"/>
+      <c r="CH17" s="4"/>
+      <c r="CI17" s="4"/>
+      <c r="CJ17" s="4"/>
+    </row>
+    <row r="18" spans="2:88" x14ac:dyDescent="0.2">
       <c r="B18" s="2" t="s">
         <v>29</v>
       </c>
@@ -2489,42 +2625,51 @@
         <v>-33.78</v>
       </c>
       <c r="J18" s="4">
-        <f t="shared" ref="J18" si="26">+J16-J17</f>
+        <f t="shared" ref="J18:M18" si="26">+J16-J17</f>
         <v>-12.517999999999992</v>
       </c>
-      <c r="K18" s="4"/>
+      <c r="K18" s="4">
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
       <c r="L18" s="4">
-        <f t="shared" ref="L18" si="27">+L16-L17</f>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="M18" s="4">
-        <f t="shared" ref="M18" si="28">+M16-M17</f>
+        <f t="shared" si="26"/>
+        <v>0.46099999999999614</v>
+      </c>
+      <c r="N18" s="4"/>
+      <c r="O18" s="4"/>
+      <c r="P18" s="4">
+        <f t="shared" ref="P18" si="27">+P16-P17</f>
         <v>0</v>
       </c>
-      <c r="N18" s="4">
-        <f t="shared" ref="N18" si="29">+N16-N17</f>
+      <c r="Q18" s="4">
+        <f t="shared" ref="Q18" si="28">+Q16-Q17</f>
         <v>0</v>
       </c>
-      <c r="O18" s="4">
-        <f t="shared" ref="O18" si="30">+O16-O17</f>
+      <c r="R18" s="4">
+        <f t="shared" ref="R18" si="29">+R16-R17</f>
         <v>0</v>
       </c>
-      <c r="P18" s="4">
-        <f t="shared" ref="P18" si="31">+P16-P17</f>
+      <c r="S18" s="4">
+        <f t="shared" ref="S18" si="30">+S16-S17</f>
+        <v>0</v>
+      </c>
+      <c r="T18" s="4">
+        <f t="shared" ref="T18" si="31">+T16-T17</f>
         <v>-250.69099999999997</v>
       </c>
-      <c r="Q18" s="4">
-        <f t="shared" ref="Q18" si="32">+Q16-Q17</f>
+      <c r="U18" s="4">
+        <f t="shared" ref="U18" si="32">+U16-U17</f>
         <v>-186.44799999999998</v>
       </c>
-      <c r="R18" s="4">
-        <f t="shared" ref="R18" si="33">+R16-R17</f>
+      <c r="V18" s="4">
+        <f t="shared" ref="V18" si="33">+V16-V17</f>
         <v>-79.396999999999977</v>
       </c>
-      <c r="S18" s="4"/>
-      <c r="T18" s="4"/>
-      <c r="U18" s="4"/>
-      <c r="V18" s="4"/>
       <c r="W18" s="4"/>
       <c r="X18" s="4"/>
       <c r="Y18" s="4"/>
@@ -2587,8 +2732,12 @@
       <c r="CD18" s="4"/>
       <c r="CE18" s="4"/>
       <c r="CF18" s="4"/>
-    </row>
-    <row r="19" spans="2:84" x14ac:dyDescent="0.2">
+      <c r="CG18" s="4"/>
+      <c r="CH18" s="4"/>
+      <c r="CI18" s="4"/>
+      <c r="CJ18" s="4"/>
+    </row>
+    <row r="19" spans="2:88" x14ac:dyDescent="0.2">
       <c r="B19" s="2" t="s">
         <v>30</v>
       </c>
@@ -2602,7 +2751,7 @@
         <v>0.115</v>
       </c>
       <c r="F19" s="4">
-        <f>+Q19-SUM(C19:E19)</f>
+        <f>+U19-SUM(C19:E19)</f>
         <v>-7.0650000000000004</v>
       </c>
       <c r="G19" s="4">
@@ -2615,27 +2764,29 @@
         <v>-4.2999999999999997E-2</v>
       </c>
       <c r="J19" s="4">
-        <f>+R19-SUM(G19:I19)</f>
+        <f>+V19-SUM(G19:I19)</f>
         <v>4.2999999999999997E-2</v>
       </c>
       <c r="K19" s="4"/>
       <c r="L19" s="4"/>
-      <c r="M19" s="4"/>
+      <c r="M19" s="4">
+        <v>0</v>
+      </c>
       <c r="N19" s="4"/>
       <c r="O19" s="4"/>
-      <c r="P19" s="4">
+      <c r="P19" s="4"/>
+      <c r="Q19" s="4"/>
+      <c r="R19" s="4"/>
+      <c r="S19" s="4"/>
+      <c r="T19" s="4">
         <v>27.013000000000002</v>
       </c>
-      <c r="Q19" s="4">
+      <c r="U19" s="4">
         <v>-6.03</v>
       </c>
-      <c r="R19" s="4">
+      <c r="V19" s="4">
         <v>0</v>
       </c>
-      <c r="S19" s="4"/>
-      <c r="T19" s="4"/>
-      <c r="U19" s="4"/>
-      <c r="V19" s="4"/>
       <c r="W19" s="4"/>
       <c r="X19" s="4"/>
       <c r="Y19" s="4"/>
@@ -2698,8 +2849,12 @@
       <c r="CD19" s="4"/>
       <c r="CE19" s="4"/>
       <c r="CF19" s="4"/>
-    </row>
-    <row r="20" spans="2:84" x14ac:dyDescent="0.2">
+      <c r="CG19" s="4"/>
+      <c r="CH19" s="4"/>
+      <c r="CI19" s="4"/>
+      <c r="CJ19" s="4"/>
+    </row>
+    <row r="20" spans="2:88" x14ac:dyDescent="0.2">
       <c r="B20" s="2" t="s">
         <v>31</v>
       </c>
@@ -2732,42 +2887,51 @@
         <v>-33.737000000000002</v>
       </c>
       <c r="J20" s="4">
-        <f t="shared" ref="J20" si="35">+J18-J19</f>
+        <f t="shared" ref="J20:M20" si="35">+J18-J19</f>
         <v>-12.560999999999991</v>
       </c>
-      <c r="K20" s="4"/>
+      <c r="K20" s="4">
+        <f t="shared" si="35"/>
+        <v>0</v>
+      </c>
       <c r="L20" s="4">
-        <f t="shared" ref="L20" si="36">+L18-L19</f>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="M20" s="4">
-        <f t="shared" ref="M20" si="37">+M18-M19</f>
+        <f t="shared" si="35"/>
+        <v>0.46099999999999614</v>
+      </c>
+      <c r="N20" s="4"/>
+      <c r="O20" s="4"/>
+      <c r="P20" s="4">
+        <f t="shared" ref="P20" si="36">+P18-P19</f>
         <v>0</v>
       </c>
-      <c r="N20" s="4">
-        <f t="shared" ref="N20" si="38">+N18-N19</f>
+      <c r="Q20" s="4">
+        <f t="shared" ref="Q20" si="37">+Q18-Q19</f>
         <v>0</v>
       </c>
-      <c r="O20" s="4">
-        <f t="shared" ref="O20" si="39">+O18-O19</f>
+      <c r="R20" s="4">
+        <f t="shared" ref="R20" si="38">+R18-R19</f>
         <v>0</v>
       </c>
-      <c r="P20" s="4">
-        <f t="shared" ref="P20" si="40">+P18-P19</f>
+      <c r="S20" s="4">
+        <f t="shared" ref="S20" si="39">+S18-S19</f>
+        <v>0</v>
+      </c>
+      <c r="T20" s="4">
+        <f t="shared" ref="T20" si="40">+T18-T19</f>
         <v>-277.70399999999995</v>
       </c>
-      <c r="Q20" s="4">
-        <f t="shared" ref="Q20" si="41">+Q18-Q19</f>
+      <c r="U20" s="4">
+        <f t="shared" ref="U20" si="41">+U18-U19</f>
         <v>-180.41799999999998</v>
       </c>
-      <c r="R20" s="4">
-        <f t="shared" ref="R20" si="42">+R18-R19</f>
+      <c r="V20" s="4">
+        <f t="shared" ref="V20" si="42">+V18-V19</f>
         <v>-79.396999999999977</v>
       </c>
-      <c r="S20" s="4"/>
-      <c r="T20" s="4"/>
-      <c r="U20" s="4"/>
-      <c r="V20" s="4"/>
       <c r="W20" s="4"/>
       <c r="X20" s="4"/>
       <c r="Y20" s="4"/>
@@ -2830,8 +2994,12 @@
       <c r="CD20" s="4"/>
       <c r="CE20" s="4"/>
       <c r="CF20" s="4"/>
-    </row>
-    <row r="21" spans="2:84" x14ac:dyDescent="0.2">
+      <c r="CG20" s="4"/>
+      <c r="CH20" s="4"/>
+      <c r="CI20" s="4"/>
+      <c r="CJ20" s="4"/>
+    </row>
+    <row r="21" spans="2:88" x14ac:dyDescent="0.2">
       <c r="C21" s="4"/>
       <c r="D21" s="4"/>
       <c r="E21" s="4"/>
@@ -2914,8 +3082,12 @@
       <c r="CD21" s="4"/>
       <c r="CE21" s="4"/>
       <c r="CF21" s="4"/>
-    </row>
-    <row r="22" spans="2:84" x14ac:dyDescent="0.2">
+      <c r="CG21" s="4"/>
+      <c r="CH21" s="4"/>
+      <c r="CI21" s="4"/>
+      <c r="CJ21" s="4"/>
+    </row>
+    <row r="22" spans="2:88" x14ac:dyDescent="0.2">
       <c r="B22" s="2" t="s">
         <v>32</v>
       </c>
@@ -2948,42 +3120,51 @@
         <v>-0.45230304392427384</v>
       </c>
       <c r="J22" s="8">
-        <f t="shared" ref="J22" si="44">+J20/J23</f>
+        <f t="shared" ref="J22:M22" si="44">+J20/J23</f>
         <v>-0.16517067393040669</v>
       </c>
-      <c r="K22" s="4"/>
+      <c r="K22" s="8" t="e">
+        <f t="shared" si="44"/>
+        <v>#DIV/0!</v>
+      </c>
       <c r="L22" s="8" t="e">
-        <f t="shared" ref="L22" si="45">+L20/L23</f>
+        <f t="shared" si="44"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="M22" s="8" t="e">
-        <f t="shared" ref="M22" si="46">+M20/M23</f>
+      <c r="M22" s="8">
+        <f t="shared" si="44"/>
+        <v>4.4973917420492397E-3</v>
+      </c>
+      <c r="N22" s="8"/>
+      <c r="O22" s="4"/>
+      <c r="P22" s="8" t="e">
+        <f t="shared" ref="P22" si="45">+P20/P23</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="N22" s="8" t="e">
-        <f t="shared" ref="N22" si="47">+N20/N23</f>
+      <c r="Q22" s="8" t="e">
+        <f t="shared" ref="Q22" si="46">+Q20/Q23</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="O22" s="8" t="e">
-        <f t="shared" ref="O22" si="48">+O20/O23</f>
+      <c r="R22" s="8" t="e">
+        <f t="shared" ref="R22" si="47">+R20/R23</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="P22" s="8">
-        <f t="shared" ref="P22" si="49">+P20/P23</f>
+      <c r="S22" s="8" t="e">
+        <f t="shared" ref="S22" si="48">+S20/S23</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T22" s="8">
+        <f t="shared" ref="T22" si="49">+T20/T23</f>
         <v>-5.8562167453079654</v>
       </c>
-      <c r="Q22" s="8">
-        <f t="shared" ref="Q22" si="50">+Q20/Q23</f>
+      <c r="U22" s="8">
+        <f t="shared" ref="U22" si="50">+U20/U23</f>
         <v>-2.529717109236294</v>
       </c>
-      <c r="R22" s="8">
-        <f t="shared" ref="R22" si="51">+R20/R23</f>
+      <c r="V22" s="8">
+        <f t="shared" ref="V22" si="51">+V20/V23</f>
         <v>-1.0440296153214319</v>
       </c>
-      <c r="S22" s="4"/>
-      <c r="T22" s="4"/>
-      <c r="U22" s="4"/>
-      <c r="V22" s="4"/>
       <c r="W22" s="4"/>
       <c r="X22" s="4"/>
       <c r="Y22" s="4"/>
@@ -3046,8 +3227,12 @@
       <c r="CD22" s="4"/>
       <c r="CE22" s="4"/>
       <c r="CF22" s="4"/>
-    </row>
-    <row r="23" spans="2:84" x14ac:dyDescent="0.2">
+      <c r="CG22" s="4"/>
+      <c r="CH22" s="4"/>
+      <c r="CI22" s="4"/>
+      <c r="CJ22" s="4"/>
+    </row>
+    <row r="23" spans="2:88" x14ac:dyDescent="0.2">
       <c r="B23" s="2" t="s">
         <v>3</v>
       </c>
@@ -3061,7 +3246,7 @@
         <v>73.891104999999996</v>
       </c>
       <c r="F23" s="4">
-        <f>+Q23</f>
+        <f>+U23</f>
         <v>71.319436999999994</v>
       </c>
       <c r="G23" s="4">
@@ -3074,27 +3259,29 @@
         <v>74.589371999999997</v>
       </c>
       <c r="J23" s="4">
-        <f>+R23</f>
+        <f>+V23</f>
         <v>76.048608999999999</v>
       </c>
       <c r="K23" s="4"/>
       <c r="L23" s="4"/>
-      <c r="M23" s="4"/>
+      <c r="M23" s="4">
+        <v>102.503857</v>
+      </c>
       <c r="N23" s="4"/>
       <c r="O23" s="4"/>
-      <c r="P23" s="4">
+      <c r="P23" s="4"/>
+      <c r="Q23" s="4"/>
+      <c r="R23" s="4"/>
+      <c r="S23" s="4"/>
+      <c r="T23" s="4">
         <v>47.420375999999997</v>
       </c>
-      <c r="Q23" s="4">
+      <c r="U23" s="4">
         <v>71.319436999999994</v>
       </c>
-      <c r="R23" s="4">
+      <c r="V23" s="4">
         <v>76.048608999999999</v>
       </c>
-      <c r="S23" s="4"/>
-      <c r="T23" s="4"/>
-      <c r="U23" s="4"/>
-      <c r="V23" s="4"/>
       <c r="W23" s="4"/>
       <c r="X23" s="4"/>
       <c r="Y23" s="4"/>
@@ -3157,8 +3344,12 @@
       <c r="CD23" s="4"/>
       <c r="CE23" s="4"/>
       <c r="CF23" s="4"/>
-    </row>
-    <row r="24" spans="2:84" x14ac:dyDescent="0.2">
+      <c r="CG23" s="4"/>
+      <c r="CH23" s="4"/>
+      <c r="CI23" s="4"/>
+      <c r="CJ23" s="4"/>
+    </row>
+    <row r="24" spans="2:88" x14ac:dyDescent="0.2">
       <c r="C24" s="4"/>
       <c r="D24" s="4"/>
       <c r="E24" s="4"/>
@@ -3241,8 +3432,12 @@
       <c r="CD24" s="4"/>
       <c r="CE24" s="4"/>
       <c r="CF24" s="4"/>
-    </row>
-    <row r="25" spans="2:84" x14ac:dyDescent="0.2">
+      <c r="CG24" s="4"/>
+      <c r="CH24" s="4"/>
+      <c r="CI24" s="4"/>
+      <c r="CJ24" s="4"/>
+    </row>
+    <row r="25" spans="2:88" x14ac:dyDescent="0.2">
       <c r="B25" s="2" t="s">
         <v>41</v>
       </c>
@@ -3266,27 +3461,27 @@
         <f t="shared" ref="J25:J29" si="55">+J3/F3-1</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="K25" s="4"/>
-      <c r="L25" s="4"/>
-      <c r="M25" s="4"/>
-      <c r="N25" s="4"/>
+      <c r="K25" s="9"/>
+      <c r="L25" s="9"/>
+      <c r="M25" s="9"/>
+      <c r="N25" s="9"/>
       <c r="O25" s="4"/>
-      <c r="P25" s="9" t="e">
-        <f t="shared" ref="P25" si="56">+P4/P2</f>
+      <c r="P25" s="4"/>
+      <c r="Q25" s="4"/>
+      <c r="R25" s="4"/>
+      <c r="S25" s="4"/>
+      <c r="T25" s="9" t="e">
+        <f t="shared" ref="T25" si="56">+T4/T2</f>
         <v>#VALUE!</v>
       </c>
-      <c r="Q25" s="9" t="e">
-        <f t="shared" ref="Q25:Q28" si="57">+Q3/P3-1</f>
+      <c r="U25" s="9" t="e">
+        <f t="shared" ref="U25:U28" si="57">+U3/T3-1</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="R25" s="9" t="e">
-        <f t="shared" ref="R25" si="58">+R3/Q3-1</f>
+      <c r="V25" s="9" t="e">
+        <f t="shared" ref="V25" si="58">+V3/U3-1</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="S25" s="4"/>
-      <c r="T25" s="4"/>
-      <c r="U25" s="4"/>
-      <c r="V25" s="4"/>
       <c r="W25" s="4"/>
       <c r="X25" s="4"/>
       <c r="Y25" s="4"/>
@@ -3349,8 +3544,12 @@
       <c r="CD25" s="4"/>
       <c r="CE25" s="4"/>
       <c r="CF25" s="4"/>
-    </row>
-    <row r="26" spans="2:84" x14ac:dyDescent="0.2">
+      <c r="CG25" s="4"/>
+      <c r="CH25" s="4"/>
+      <c r="CI25" s="4"/>
+      <c r="CJ25" s="4"/>
+    </row>
+    <row r="26" spans="2:88" x14ac:dyDescent="0.2">
       <c r="B26" s="2" t="s">
         <v>42</v>
       </c>
@@ -3374,27 +3573,27 @@
         <f t="shared" si="55"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="K26" s="4"/>
-      <c r="L26" s="4"/>
-      <c r="M26" s="4"/>
-      <c r="N26" s="4"/>
+      <c r="K26" s="9"/>
+      <c r="L26" s="9"/>
+      <c r="M26" s="9"/>
+      <c r="N26" s="9"/>
       <c r="O26" s="4"/>
-      <c r="P26" s="9" t="e">
-        <f t="shared" ref="P26" si="59">+P5/P3</f>
+      <c r="P26" s="4"/>
+      <c r="Q26" s="4"/>
+      <c r="R26" s="4"/>
+      <c r="S26" s="4"/>
+      <c r="T26" s="9" t="e">
+        <f t="shared" ref="T26" si="59">+T5/T3</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="Q26" s="9" t="e">
+      <c r="U26" s="9" t="e">
         <f t="shared" si="57"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="R26" s="9" t="e">
-        <f t="shared" ref="R26" si="60">+R4/Q4-1</f>
+      <c r="V26" s="9" t="e">
+        <f t="shared" ref="V26" si="60">+V4/U4-1</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="S26" s="4"/>
-      <c r="T26" s="4"/>
-      <c r="U26" s="4"/>
-      <c r="V26" s="4"/>
       <c r="W26" s="4"/>
       <c r="X26" s="4"/>
       <c r="Y26" s="4"/>
@@ -3457,8 +3656,12 @@
       <c r="CD26" s="4"/>
       <c r="CE26" s="4"/>
       <c r="CF26" s="4"/>
-    </row>
-    <row r="27" spans="2:84" x14ac:dyDescent="0.2">
+      <c r="CG26" s="4"/>
+      <c r="CH26" s="4"/>
+      <c r="CI26" s="4"/>
+      <c r="CJ26" s="4"/>
+    </row>
+    <row r="27" spans="2:88" x14ac:dyDescent="0.2">
       <c r="B27" s="2" t="s">
         <v>43</v>
       </c>
@@ -3482,27 +3685,27 @@
         <f t="shared" si="55"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="K27" s="4"/>
-      <c r="L27" s="4"/>
-      <c r="M27" s="4"/>
-      <c r="N27" s="4"/>
+      <c r="K27" s="9"/>
+      <c r="L27" s="9"/>
+      <c r="M27" s="9"/>
+      <c r="N27" s="9"/>
       <c r="O27" s="4"/>
-      <c r="P27" s="9" t="e">
-        <f t="shared" ref="P27" si="61">+P6/P4</f>
+      <c r="P27" s="4"/>
+      <c r="Q27" s="4"/>
+      <c r="R27" s="4"/>
+      <c r="S27" s="4"/>
+      <c r="T27" s="9" t="e">
+        <f t="shared" ref="T27" si="61">+T6/T4</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="Q27" s="9" t="e">
+      <c r="U27" s="9" t="e">
         <f t="shared" si="57"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="R27" s="9" t="e">
-        <f t="shared" ref="R27" si="62">+R5/Q5-1</f>
+      <c r="V27" s="9" t="e">
+        <f t="shared" ref="V27" si="62">+V5/U5-1</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="S27" s="4"/>
-      <c r="T27" s="4"/>
-      <c r="U27" s="4"/>
-      <c r="V27" s="4"/>
       <c r="W27" s="4"/>
       <c r="X27" s="4"/>
       <c r="Y27" s="4"/>
@@ -3565,8 +3768,12 @@
       <c r="CD27" s="4"/>
       <c r="CE27" s="4"/>
       <c r="CF27" s="4"/>
-    </row>
-    <row r="28" spans="2:84" x14ac:dyDescent="0.2">
+      <c r="CG27" s="4"/>
+      <c r="CH27" s="4"/>
+      <c r="CI27" s="4"/>
+      <c r="CJ27" s="4"/>
+    </row>
+    <row r="28" spans="2:88" x14ac:dyDescent="0.2">
       <c r="B28" s="2" t="s">
         <v>44</v>
       </c>
@@ -3590,27 +3797,27 @@
         <f t="shared" si="55"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="K28" s="4"/>
-      <c r="L28" s="4"/>
-      <c r="M28" s="4"/>
-      <c r="N28" s="4"/>
+      <c r="K28" s="9"/>
+      <c r="L28" s="9"/>
+      <c r="M28" s="9"/>
+      <c r="N28" s="9"/>
       <c r="O28" s="4"/>
-      <c r="P28" s="9" t="e">
-        <f t="shared" ref="P28" si="63">+P7/P5</f>
+      <c r="P28" s="4"/>
+      <c r="Q28" s="4"/>
+      <c r="R28" s="4"/>
+      <c r="S28" s="4"/>
+      <c r="T28" s="9" t="e">
+        <f t="shared" ref="T28" si="63">+T7/T5</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="Q28" s="9" t="e">
+      <c r="U28" s="9" t="e">
         <f t="shared" si="57"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="R28" s="9" t="e">
-        <f t="shared" ref="R28" si="64">+R6/Q6-1</f>
+      <c r="V28" s="9" t="e">
+        <f t="shared" ref="V28" si="64">+V6/U6-1</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="S28" s="4"/>
-      <c r="T28" s="4"/>
-      <c r="U28" s="4"/>
-      <c r="V28" s="4"/>
       <c r="W28" s="4"/>
       <c r="X28" s="4"/>
       <c r="Y28" s="4"/>
@@ -3673,8 +3880,12 @@
       <c r="CD28" s="4"/>
       <c r="CE28" s="4"/>
       <c r="CF28" s="4"/>
-    </row>
-    <row r="29" spans="2:84" x14ac:dyDescent="0.2">
+      <c r="CG28" s="4"/>
+      <c r="CH28" s="4"/>
+      <c r="CI28" s="4"/>
+      <c r="CJ28" s="4"/>
+    </row>
+    <row r="29" spans="2:88" x14ac:dyDescent="0.2">
       <c r="B29" s="2" t="s">
         <v>33</v>
       </c>
@@ -3698,28 +3909,28 @@
         <f t="shared" si="55"/>
         <v>-0.11181479510377834</v>
       </c>
-      <c r="K29" s="4"/>
-      <c r="L29" s="4"/>
-      <c r="M29" s="4"/>
-      <c r="N29" s="4"/>
+      <c r="K29" s="9"/>
+      <c r="L29" s="9"/>
+      <c r="M29" s="9"/>
+      <c r="N29" s="9"/>
       <c r="O29" s="4"/>
-      <c r="P29" s="9" t="e">
-        <f t="shared" ref="P29" si="65">+P8/P6</f>
+      <c r="P29" s="4"/>
+      <c r="Q29" s="4"/>
+      <c r="R29" s="4"/>
+      <c r="S29" s="4"/>
+      <c r="T29" s="9" t="e">
+        <f t="shared" ref="T29" si="65">+T8/T6</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="Q29" s="9">
-        <f>+Q7/P7-1</f>
+      <c r="U29" s="9">
+        <f>+U7/T7-1</f>
         <v>-0.22952957916522942</v>
       </c>
-      <c r="R29" s="9">
-        <f t="shared" ref="R29" si="66">+R7/Q7-1</f>
+      <c r="V29" s="9">
+        <f t="shared" ref="V29" si="66">+V7/U7-1</f>
         <v>-0.18758307100384741</v>
       </c>
-      <c r="S29" s="9"/>
-      <c r="T29" s="4"/>
-      <c r="U29" s="4"/>
-      <c r="V29" s="4"/>
-      <c r="W29" s="4"/>
+      <c r="W29" s="9"/>
       <c r="X29" s="4"/>
       <c r="Y29" s="4"/>
       <c r="Z29" s="4"/>
@@ -3781,8 +3992,12 @@
       <c r="CD29" s="4"/>
       <c r="CE29" s="4"/>
       <c r="CF29" s="4"/>
-    </row>
-    <row r="30" spans="2:84" x14ac:dyDescent="0.2">
+      <c r="CG29" s="4"/>
+      <c r="CH29" s="4"/>
+      <c r="CI29" s="4"/>
+      <c r="CJ29" s="4"/>
+    </row>
+    <row r="30" spans="2:88" x14ac:dyDescent="0.2">
       <c r="B30" s="2" t="s">
         <v>34</v>
       </c>
@@ -3818,40 +4033,40 @@
         <f t="shared" ref="J30" si="68">+J9/J7</f>
         <v>0.65176663271216573</v>
       </c>
-      <c r="K30" s="4"/>
-      <c r="L30" s="9" t="e">
-        <f t="shared" ref="L30:Q30" si="69">+L9/L7</f>
+      <c r="K30" s="9"/>
+      <c r="L30" s="9"/>
+      <c r="M30" s="9"/>
+      <c r="N30" s="9"/>
+      <c r="O30" s="4"/>
+      <c r="P30" s="9" t="e">
+        <f t="shared" ref="P30:U30" si="69">+P9/P7</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="M30" s="9" t="e">
+      <c r="Q30" s="9" t="e">
         <f t="shared" si="69"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="N30" s="9" t="e">
+      <c r="R30" s="9" t="e">
         <f t="shared" si="69"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="O30" s="9" t="e">
+      <c r="S30" s="9" t="e">
         <f t="shared" si="69"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="P30" s="9">
+      <c r="T30" s="9">
         <f t="shared" si="69"/>
         <v>0.55294390307002417</v>
       </c>
-      <c r="Q30" s="9">
+      <c r="U30" s="9">
         <f t="shared" si="69"/>
         <v>0.61681007345225602</v>
       </c>
-      <c r="R30" s="9">
-        <f t="shared" ref="R30" si="70">+R9/R7</f>
+      <c r="V30" s="9">
+        <f t="shared" ref="V30" si="70">+V9/V7</f>
         <v>0.64024626512248672</v>
       </c>
-      <c r="S30" s="9"/>
-      <c r="T30" s="4"/>
-      <c r="U30" s="4"/>
-      <c r="V30" s="4"/>
-      <c r="W30" s="4"/>
+      <c r="W30" s="9"/>
       <c r="X30" s="4"/>
       <c r="Y30" s="4"/>
       <c r="Z30" s="4"/>
@@ -3913,8 +4128,12 @@
       <c r="CD30" s="4"/>
       <c r="CE30" s="4"/>
       <c r="CF30" s="4"/>
-    </row>
-    <row r="31" spans="2:84" x14ac:dyDescent="0.2">
+      <c r="CG30" s="4"/>
+      <c r="CH30" s="4"/>
+      <c r="CI30" s="4"/>
+      <c r="CJ30" s="4"/>
+    </row>
+    <row r="31" spans="2:88" x14ac:dyDescent="0.2">
       <c r="B31" s="2" t="s">
         <v>35</v>
       </c>
@@ -3950,40 +4169,40 @@
         <f t="shared" ref="J31" si="72">+J13/J7</f>
         <v>-9.1397527313399896E-2</v>
       </c>
-      <c r="K31" s="4"/>
-      <c r="L31" s="9" t="e">
-        <f t="shared" ref="L31:Q31" si="73">+L13/L7</f>
+      <c r="K31" s="9"/>
+      <c r="L31" s="9"/>
+      <c r="M31" s="9"/>
+      <c r="N31" s="9"/>
+      <c r="O31" s="4"/>
+      <c r="P31" s="9" t="e">
+        <f t="shared" ref="P31:U31" si="73">+P13/P7</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="M31" s="9" t="e">
+      <c r="Q31" s="9" t="e">
         <f t="shared" si="73"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="N31" s="9" t="e">
+      <c r="R31" s="9" t="e">
         <f t="shared" si="73"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="O31" s="9" t="e">
+      <c r="S31" s="9" t="e">
         <f t="shared" si="73"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="P31" s="9">
+      <c r="T31" s="9">
         <f t="shared" si="73"/>
         <v>-1.5959166954122108</v>
       </c>
-      <c r="Q31" s="9">
+      <c r="U31" s="9">
         <f t="shared" si="73"/>
         <v>-1.3317173837005944</v>
       </c>
-      <c r="R31" s="9">
-        <f t="shared" ref="R31" si="74">+R13/R7</f>
+      <c r="V31" s="9">
+        <f t="shared" ref="V31" si="74">+V13/V7</f>
         <v>-0.43774917122314538</v>
       </c>
-      <c r="S31" s="9"/>
-      <c r="T31" s="4"/>
-      <c r="U31" s="4"/>
-      <c r="V31" s="4"/>
-      <c r="W31" s="4"/>
+      <c r="W31" s="9"/>
       <c r="X31" s="4"/>
       <c r="Y31" s="4"/>
       <c r="Z31" s="4"/>
@@ -4045,8 +4264,12 @@
       <c r="CD31" s="4"/>
       <c r="CE31" s="4"/>
       <c r="CF31" s="4"/>
-    </row>
-    <row r="32" spans="2:84" x14ac:dyDescent="0.2">
+      <c r="CG31" s="4"/>
+      <c r="CH31" s="4"/>
+      <c r="CI31" s="4"/>
+      <c r="CJ31" s="4"/>
+    </row>
+    <row r="32" spans="2:88" x14ac:dyDescent="0.2">
       <c r="B32" s="2" t="s">
         <v>36</v>
       </c>
@@ -4082,40 +4305,40 @@
         <f t="shared" ref="J32" si="76">+J17/J16</f>
         <v>-7.8487119841475023E-2</v>
       </c>
-      <c r="K32" s="4"/>
-      <c r="L32" s="9" t="e">
-        <f t="shared" ref="L32:Q32" si="77">+L17/L16</f>
+      <c r="K32" s="9"/>
+      <c r="L32" s="9"/>
+      <c r="M32" s="9"/>
+      <c r="N32" s="9"/>
+      <c r="O32" s="4"/>
+      <c r="P32" s="9" t="e">
+        <f t="shared" ref="P32:U32" si="77">+P17/P16</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="M32" s="9" t="e">
+      <c r="Q32" s="9" t="e">
         <f t="shared" si="77"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="N32" s="9" t="e">
+      <c r="R32" s="9" t="e">
         <f t="shared" si="77"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="O32" s="9" t="e">
+      <c r="S32" s="9" t="e">
         <f t="shared" si="77"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="P32" s="9">
+      <c r="T32" s="9">
         <f t="shared" si="77"/>
         <v>0.18180453336379512</v>
       </c>
-      <c r="Q32" s="9">
+      <c r="U32" s="9">
         <f t="shared" si="77"/>
         <v>6.8775035211619331E-2</v>
       </c>
-      <c r="R32" s="9">
-        <f t="shared" ref="R32" si="78">+R17/R16</f>
+      <c r="V32" s="9">
+        <f t="shared" ref="V32" si="78">+V17/V16</f>
         <v>-4.1285787354588266E-2</v>
       </c>
-      <c r="S32" s="9"/>
-      <c r="T32" s="4"/>
-      <c r="U32" s="4"/>
-      <c r="V32" s="4"/>
-      <c r="W32" s="4"/>
+      <c r="W32" s="9"/>
       <c r="X32" s="4"/>
       <c r="Y32" s="4"/>
       <c r="Z32" s="4"/>
@@ -4177,8 +4400,12 @@
       <c r="CD32" s="4"/>
       <c r="CE32" s="4"/>
       <c r="CF32" s="4"/>
-    </row>
-    <row r="33" spans="3:84" x14ac:dyDescent="0.2">
+      <c r="CG32" s="4"/>
+      <c r="CH32" s="4"/>
+      <c r="CI32" s="4"/>
+      <c r="CJ32" s="4"/>
+    </row>
+    <row r="33" spans="3:88" x14ac:dyDescent="0.2">
       <c r="C33" s="4"/>
       <c r="D33" s="4"/>
       <c r="E33" s="4"/>
@@ -4261,8 +4488,12 @@
       <c r="CD33" s="4"/>
       <c r="CE33" s="4"/>
       <c r="CF33" s="4"/>
-    </row>
-    <row r="34" spans="3:84" x14ac:dyDescent="0.2">
+      <c r="CG33" s="4"/>
+      <c r="CH33" s="4"/>
+      <c r="CI33" s="4"/>
+      <c r="CJ33" s="4"/>
+    </row>
+    <row r="34" spans="3:88" x14ac:dyDescent="0.2">
       <c r="C34" s="4"/>
       <c r="D34" s="4"/>
       <c r="E34" s="4"/>
@@ -4345,8 +4576,12 @@
       <c r="CD34" s="4"/>
       <c r="CE34" s="4"/>
       <c r="CF34" s="4"/>
-    </row>
-    <row r="35" spans="3:84" x14ac:dyDescent="0.2">
+      <c r="CG34" s="4"/>
+      <c r="CH34" s="4"/>
+      <c r="CI34" s="4"/>
+      <c r="CJ34" s="4"/>
+    </row>
+    <row r="35" spans="3:88" x14ac:dyDescent="0.2">
       <c r="C35" s="4"/>
       <c r="D35" s="4"/>
       <c r="E35" s="4"/>
@@ -4429,8 +4664,12 @@
       <c r="CD35" s="4"/>
       <c r="CE35" s="4"/>
       <c r="CF35" s="4"/>
-    </row>
-    <row r="36" spans="3:84" x14ac:dyDescent="0.2">
+      <c r="CG35" s="4"/>
+      <c r="CH35" s="4"/>
+      <c r="CI35" s="4"/>
+      <c r="CJ35" s="4"/>
+    </row>
+    <row r="36" spans="3:88" x14ac:dyDescent="0.2">
       <c r="C36" s="4"/>
       <c r="D36" s="4"/>
       <c r="E36" s="4"/>
@@ -4513,8 +4752,12 @@
       <c r="CD36" s="4"/>
       <c r="CE36" s="4"/>
       <c r="CF36" s="4"/>
-    </row>
-    <row r="37" spans="3:84" x14ac:dyDescent="0.2">
+      <c r="CG36" s="4"/>
+      <c r="CH36" s="4"/>
+      <c r="CI36" s="4"/>
+      <c r="CJ36" s="4"/>
+    </row>
+    <row r="37" spans="3:88" x14ac:dyDescent="0.2">
       <c r="C37" s="4"/>
       <c r="D37" s="4"/>
       <c r="E37" s="4"/>
@@ -4597,8 +4840,12 @@
       <c r="CD37" s="4"/>
       <c r="CE37" s="4"/>
       <c r="CF37" s="4"/>
-    </row>
-    <row r="38" spans="3:84" x14ac:dyDescent="0.2">
+      <c r="CG37" s="4"/>
+      <c r="CH37" s="4"/>
+      <c r="CI37" s="4"/>
+      <c r="CJ37" s="4"/>
+    </row>
+    <row r="38" spans="3:88" x14ac:dyDescent="0.2">
       <c r="C38" s="4"/>
       <c r="D38" s="4"/>
       <c r="E38" s="4"/>
@@ -4681,8 +4928,12 @@
       <c r="CD38" s="4"/>
       <c r="CE38" s="4"/>
       <c r="CF38" s="4"/>
-    </row>
-    <row r="39" spans="3:84" x14ac:dyDescent="0.2">
+      <c r="CG38" s="4"/>
+      <c r="CH38" s="4"/>
+      <c r="CI38" s="4"/>
+      <c r="CJ38" s="4"/>
+    </row>
+    <row r="39" spans="3:88" x14ac:dyDescent="0.2">
       <c r="C39" s="4"/>
       <c r="D39" s="4"/>
       <c r="E39" s="4"/>
@@ -4765,8 +5016,12 @@
       <c r="CD39" s="4"/>
       <c r="CE39" s="4"/>
       <c r="CF39" s="4"/>
-    </row>
-    <row r="40" spans="3:84" x14ac:dyDescent="0.2">
+      <c r="CG39" s="4"/>
+      <c r="CH39" s="4"/>
+      <c r="CI39" s="4"/>
+      <c r="CJ39" s="4"/>
+    </row>
+    <row r="40" spans="3:88" x14ac:dyDescent="0.2">
       <c r="C40" s="4"/>
       <c r="D40" s="4"/>
       <c r="E40" s="4"/>
@@ -4849,8 +5104,12 @@
       <c r="CD40" s="4"/>
       <c r="CE40" s="4"/>
       <c r="CF40" s="4"/>
-    </row>
-    <row r="41" spans="3:84" x14ac:dyDescent="0.2">
+      <c r="CG40" s="4"/>
+      <c r="CH40" s="4"/>
+      <c r="CI40" s="4"/>
+      <c r="CJ40" s="4"/>
+    </row>
+    <row r="41" spans="3:88" x14ac:dyDescent="0.2">
       <c r="C41" s="4"/>
       <c r="D41" s="4"/>
       <c r="E41" s="4"/>
@@ -4933,8 +5192,12 @@
       <c r="CD41" s="4"/>
       <c r="CE41" s="4"/>
       <c r="CF41" s="4"/>
-    </row>
-    <row r="42" spans="3:84" x14ac:dyDescent="0.2">
+      <c r="CG41" s="4"/>
+      <c r="CH41" s="4"/>
+      <c r="CI41" s="4"/>
+      <c r="CJ41" s="4"/>
+    </row>
+    <row r="42" spans="3:88" x14ac:dyDescent="0.2">
       <c r="C42" s="4"/>
       <c r="D42" s="4"/>
       <c r="E42" s="4"/>
@@ -5017,8 +5280,12 @@
       <c r="CD42" s="4"/>
       <c r="CE42" s="4"/>
       <c r="CF42" s="4"/>
-    </row>
-    <row r="43" spans="3:84" x14ac:dyDescent="0.2">
+      <c r="CG42" s="4"/>
+      <c r="CH42" s="4"/>
+      <c r="CI42" s="4"/>
+      <c r="CJ42" s="4"/>
+    </row>
+    <row r="43" spans="3:88" x14ac:dyDescent="0.2">
       <c r="C43" s="4"/>
       <c r="D43" s="4"/>
       <c r="E43" s="4"/>
@@ -5101,8 +5368,12 @@
       <c r="CD43" s="4"/>
       <c r="CE43" s="4"/>
       <c r="CF43" s="4"/>
-    </row>
-    <row r="44" spans="3:84" x14ac:dyDescent="0.2">
+      <c r="CG43" s="4"/>
+      <c r="CH43" s="4"/>
+      <c r="CI43" s="4"/>
+      <c r="CJ43" s="4"/>
+    </row>
+    <row r="44" spans="3:88" x14ac:dyDescent="0.2">
       <c r="C44" s="4"/>
       <c r="D44" s="4"/>
       <c r="E44" s="4"/>
@@ -5185,8 +5456,12 @@
       <c r="CD44" s="4"/>
       <c r="CE44" s="4"/>
       <c r="CF44" s="4"/>
-    </row>
-    <row r="45" spans="3:84" x14ac:dyDescent="0.2">
+      <c r="CG44" s="4"/>
+      <c r="CH44" s="4"/>
+      <c r="CI44" s="4"/>
+      <c r="CJ44" s="4"/>
+    </row>
+    <row r="45" spans="3:88" x14ac:dyDescent="0.2">
       <c r="C45" s="4"/>
       <c r="D45" s="4"/>
       <c r="E45" s="4"/>
@@ -5269,8 +5544,12 @@
       <c r="CD45" s="4"/>
       <c r="CE45" s="4"/>
       <c r="CF45" s="4"/>
-    </row>
-    <row r="46" spans="3:84" x14ac:dyDescent="0.2">
+      <c r="CG45" s="4"/>
+      <c r="CH45" s="4"/>
+      <c r="CI45" s="4"/>
+      <c r="CJ45" s="4"/>
+    </row>
+    <row r="46" spans="3:88" x14ac:dyDescent="0.2">
       <c r="C46" s="4"/>
       <c r="D46" s="4"/>
       <c r="E46" s="4"/>
@@ -5353,8 +5632,12 @@
       <c r="CD46" s="4"/>
       <c r="CE46" s="4"/>
       <c r="CF46" s="4"/>
-    </row>
-    <row r="47" spans="3:84" x14ac:dyDescent="0.2">
+      <c r="CG46" s="4"/>
+      <c r="CH46" s="4"/>
+      <c r="CI46" s="4"/>
+      <c r="CJ46" s="4"/>
+    </row>
+    <row r="47" spans="3:88" x14ac:dyDescent="0.2">
       <c r="C47" s="4"/>
       <c r="D47" s="4"/>
       <c r="E47" s="4"/>
@@ -5437,8 +5720,12 @@
       <c r="CD47" s="4"/>
       <c r="CE47" s="4"/>
       <c r="CF47" s="4"/>
-    </row>
-    <row r="48" spans="3:84" x14ac:dyDescent="0.2">
+      <c r="CG47" s="4"/>
+      <c r="CH47" s="4"/>
+      <c r="CI47" s="4"/>
+      <c r="CJ47" s="4"/>
+    </row>
+    <row r="48" spans="3:88" x14ac:dyDescent="0.2">
       <c r="C48" s="4"/>
       <c r="D48" s="4"/>
       <c r="E48" s="4"/>
@@ -5521,8 +5808,12 @@
       <c r="CD48" s="4"/>
       <c r="CE48" s="4"/>
       <c r="CF48" s="4"/>
-    </row>
-    <row r="49" spans="3:84" x14ac:dyDescent="0.2">
+      <c r="CG48" s="4"/>
+      <c r="CH48" s="4"/>
+      <c r="CI48" s="4"/>
+      <c r="CJ48" s="4"/>
+    </row>
+    <row r="49" spans="3:88" x14ac:dyDescent="0.2">
       <c r="C49" s="4"/>
       <c r="D49" s="4"/>
       <c r="E49" s="4"/>
@@ -5605,8 +5896,12 @@
       <c r="CD49" s="4"/>
       <c r="CE49" s="4"/>
       <c r="CF49" s="4"/>
-    </row>
-    <row r="50" spans="3:84" x14ac:dyDescent="0.2">
+      <c r="CG49" s="4"/>
+      <c r="CH49" s="4"/>
+      <c r="CI49" s="4"/>
+      <c r="CJ49" s="4"/>
+    </row>
+    <row r="50" spans="3:88" x14ac:dyDescent="0.2">
       <c r="C50" s="4"/>
       <c r="D50" s="4"/>
       <c r="E50" s="4"/>
@@ -5689,8 +5984,12 @@
       <c r="CD50" s="4"/>
       <c r="CE50" s="4"/>
       <c r="CF50" s="4"/>
-    </row>
-    <row r="51" spans="3:84" x14ac:dyDescent="0.2">
+      <c r="CG50" s="4"/>
+      <c r="CH50" s="4"/>
+      <c r="CI50" s="4"/>
+      <c r="CJ50" s="4"/>
+    </row>
+    <row r="51" spans="3:88" x14ac:dyDescent="0.2">
       <c r="C51" s="4"/>
       <c r="D51" s="4"/>
       <c r="E51" s="4"/>
@@ -5773,8 +6072,12 @@
       <c r="CD51" s="4"/>
       <c r="CE51" s="4"/>
       <c r="CF51" s="4"/>
-    </row>
-    <row r="52" spans="3:84" x14ac:dyDescent="0.2">
+      <c r="CG51" s="4"/>
+      <c r="CH51" s="4"/>
+      <c r="CI51" s="4"/>
+      <c r="CJ51" s="4"/>
+    </row>
+    <row r="52" spans="3:88" x14ac:dyDescent="0.2">
       <c r="C52" s="4"/>
       <c r="D52" s="4"/>
       <c r="E52" s="4"/>
@@ -5857,8 +6160,12 @@
       <c r="CD52" s="4"/>
       <c r="CE52" s="4"/>
       <c r="CF52" s="4"/>
-    </row>
-    <row r="53" spans="3:84" x14ac:dyDescent="0.2">
+      <c r="CG52" s="4"/>
+      <c r="CH52" s="4"/>
+      <c r="CI52" s="4"/>
+      <c r="CJ52" s="4"/>
+    </row>
+    <row r="53" spans="3:88" x14ac:dyDescent="0.2">
       <c r="C53" s="4"/>
       <c r="D53" s="4"/>
       <c r="E53" s="4"/>
@@ -5941,8 +6248,12 @@
       <c r="CD53" s="4"/>
       <c r="CE53" s="4"/>
       <c r="CF53" s="4"/>
-    </row>
-    <row r="54" spans="3:84" x14ac:dyDescent="0.2">
+      <c r="CG53" s="4"/>
+      <c r="CH53" s="4"/>
+      <c r="CI53" s="4"/>
+      <c r="CJ53" s="4"/>
+    </row>
+    <row r="54" spans="3:88" x14ac:dyDescent="0.2">
       <c r="C54" s="4"/>
       <c r="D54" s="4"/>
       <c r="E54" s="4"/>
@@ -6025,8 +6336,12 @@
       <c r="CD54" s="4"/>
       <c r="CE54" s="4"/>
       <c r="CF54" s="4"/>
-    </row>
-    <row r="55" spans="3:84" x14ac:dyDescent="0.2">
+      <c r="CG54" s="4"/>
+      <c r="CH54" s="4"/>
+      <c r="CI54" s="4"/>
+      <c r="CJ54" s="4"/>
+    </row>
+    <row r="55" spans="3:88" x14ac:dyDescent="0.2">
       <c r="C55" s="4"/>
       <c r="D55" s="4"/>
       <c r="E55" s="4"/>
@@ -6109,8 +6424,12 @@
       <c r="CD55" s="4"/>
       <c r="CE55" s="4"/>
       <c r="CF55" s="4"/>
-    </row>
-    <row r="56" spans="3:84" x14ac:dyDescent="0.2">
+      <c r="CG55" s="4"/>
+      <c r="CH55" s="4"/>
+      <c r="CI55" s="4"/>
+      <c r="CJ55" s="4"/>
+    </row>
+    <row r="56" spans="3:88" x14ac:dyDescent="0.2">
       <c r="C56" s="4"/>
       <c r="D56" s="4"/>
       <c r="E56" s="4"/>
@@ -6193,8 +6512,12 @@
       <c r="CD56" s="4"/>
       <c r="CE56" s="4"/>
       <c r="CF56" s="4"/>
-    </row>
-    <row r="57" spans="3:84" x14ac:dyDescent="0.2">
+      <c r="CG56" s="4"/>
+      <c r="CH56" s="4"/>
+      <c r="CI56" s="4"/>
+      <c r="CJ56" s="4"/>
+    </row>
+    <row r="57" spans="3:88" x14ac:dyDescent="0.2">
       <c r="C57" s="4"/>
       <c r="D57" s="4"/>
       <c r="E57" s="4"/>
@@ -6277,8 +6600,12 @@
       <c r="CD57" s="4"/>
       <c r="CE57" s="4"/>
       <c r="CF57" s="4"/>
-    </row>
-    <row r="58" spans="3:84" x14ac:dyDescent="0.2">
+      <c r="CG57" s="4"/>
+      <c r="CH57" s="4"/>
+      <c r="CI57" s="4"/>
+      <c r="CJ57" s="4"/>
+    </row>
+    <row r="58" spans="3:88" x14ac:dyDescent="0.2">
       <c r="C58" s="4"/>
       <c r="D58" s="4"/>
       <c r="E58" s="4"/>
@@ -6361,8 +6688,12 @@
       <c r="CD58" s="4"/>
       <c r="CE58" s="4"/>
       <c r="CF58" s="4"/>
-    </row>
-    <row r="59" spans="3:84" x14ac:dyDescent="0.2">
+      <c r="CG58" s="4"/>
+      <c r="CH58" s="4"/>
+      <c r="CI58" s="4"/>
+      <c r="CJ58" s="4"/>
+    </row>
+    <row r="59" spans="3:88" x14ac:dyDescent="0.2">
       <c r="C59" s="4"/>
       <c r="D59" s="4"/>
       <c r="E59" s="4"/>
@@ -6445,8 +6776,12 @@
       <c r="CD59" s="4"/>
       <c r="CE59" s="4"/>
       <c r="CF59" s="4"/>
-    </row>
-    <row r="60" spans="3:84" x14ac:dyDescent="0.2">
+      <c r="CG59" s="4"/>
+      <c r="CH59" s="4"/>
+      <c r="CI59" s="4"/>
+      <c r="CJ59" s="4"/>
+    </row>
+    <row r="60" spans="3:88" x14ac:dyDescent="0.2">
       <c r="C60" s="4"/>
       <c r="D60" s="4"/>
       <c r="E60" s="4"/>
@@ -6529,8 +6864,12 @@
       <c r="CD60" s="4"/>
       <c r="CE60" s="4"/>
       <c r="CF60" s="4"/>
-    </row>
-    <row r="61" spans="3:84" x14ac:dyDescent="0.2">
+      <c r="CG60" s="4"/>
+      <c r="CH60" s="4"/>
+      <c r="CI60" s="4"/>
+      <c r="CJ60" s="4"/>
+    </row>
+    <row r="61" spans="3:88" x14ac:dyDescent="0.2">
       <c r="C61" s="4"/>
       <c r="D61" s="4"/>
       <c r="E61" s="4"/>
@@ -6613,8 +6952,12 @@
       <c r="CD61" s="4"/>
       <c r="CE61" s="4"/>
       <c r="CF61" s="4"/>
-    </row>
-    <row r="62" spans="3:84" x14ac:dyDescent="0.2">
+      <c r="CG61" s="4"/>
+      <c r="CH61" s="4"/>
+      <c r="CI61" s="4"/>
+      <c r="CJ61" s="4"/>
+    </row>
+    <row r="62" spans="3:88" x14ac:dyDescent="0.2">
       <c r="C62" s="4"/>
       <c r="D62" s="4"/>
       <c r="E62" s="4"/>
@@ -6697,8 +7040,12 @@
       <c r="CD62" s="4"/>
       <c r="CE62" s="4"/>
       <c r="CF62" s="4"/>
-    </row>
-    <row r="63" spans="3:84" x14ac:dyDescent="0.2">
+      <c r="CG62" s="4"/>
+      <c r="CH62" s="4"/>
+      <c r="CI62" s="4"/>
+      <c r="CJ62" s="4"/>
+    </row>
+    <row r="63" spans="3:88" x14ac:dyDescent="0.2">
       <c r="C63" s="4"/>
       <c r="D63" s="4"/>
       <c r="E63" s="4"/>
@@ -6781,8 +7128,12 @@
       <c r="CD63" s="4"/>
       <c r="CE63" s="4"/>
       <c r="CF63" s="4"/>
-    </row>
-    <row r="64" spans="3:84" x14ac:dyDescent="0.2">
+      <c r="CG63" s="4"/>
+      <c r="CH63" s="4"/>
+      <c r="CI63" s="4"/>
+      <c r="CJ63" s="4"/>
+    </row>
+    <row r="64" spans="3:88" x14ac:dyDescent="0.2">
       <c r="C64" s="4"/>
       <c r="D64" s="4"/>
       <c r="E64" s="4"/>
@@ -6865,8 +7216,12 @@
       <c r="CD64" s="4"/>
       <c r="CE64" s="4"/>
       <c r="CF64" s="4"/>
-    </row>
-    <row r="65" spans="3:84" x14ac:dyDescent="0.2">
+      <c r="CG64" s="4"/>
+      <c r="CH64" s="4"/>
+      <c r="CI64" s="4"/>
+      <c r="CJ64" s="4"/>
+    </row>
+    <row r="65" spans="3:88" x14ac:dyDescent="0.2">
       <c r="C65" s="4"/>
       <c r="D65" s="4"/>
       <c r="E65" s="4"/>
@@ -6949,8 +7304,12 @@
       <c r="CD65" s="4"/>
       <c r="CE65" s="4"/>
       <c r="CF65" s="4"/>
-    </row>
-    <row r="66" spans="3:84" x14ac:dyDescent="0.2">
+      <c r="CG65" s="4"/>
+      <c r="CH65" s="4"/>
+      <c r="CI65" s="4"/>
+      <c r="CJ65" s="4"/>
+    </row>
+    <row r="66" spans="3:88" x14ac:dyDescent="0.2">
       <c r="C66" s="4"/>
       <c r="D66" s="4"/>
       <c r="E66" s="4"/>
@@ -7033,8 +7392,12 @@
       <c r="CD66" s="4"/>
       <c r="CE66" s="4"/>
       <c r="CF66" s="4"/>
-    </row>
-    <row r="67" spans="3:84" x14ac:dyDescent="0.2">
+      <c r="CG66" s="4"/>
+      <c r="CH66" s="4"/>
+      <c r="CI66" s="4"/>
+      <c r="CJ66" s="4"/>
+    </row>
+    <row r="67" spans="3:88" x14ac:dyDescent="0.2">
       <c r="C67" s="4"/>
       <c r="D67" s="4"/>
       <c r="E67" s="4"/>
@@ -7117,8 +7480,12 @@
       <c r="CD67" s="4"/>
       <c r="CE67" s="4"/>
       <c r="CF67" s="4"/>
-    </row>
-    <row r="68" spans="3:84" x14ac:dyDescent="0.2">
+      <c r="CG67" s="4"/>
+      <c r="CH67" s="4"/>
+      <c r="CI67" s="4"/>
+      <c r="CJ67" s="4"/>
+    </row>
+    <row r="68" spans="3:88" x14ac:dyDescent="0.2">
       <c r="C68" s="4"/>
       <c r="D68" s="4"/>
       <c r="E68" s="4"/>
@@ -7201,8 +7568,12 @@
       <c r="CD68" s="4"/>
       <c r="CE68" s="4"/>
       <c r="CF68" s="4"/>
-    </row>
-    <row r="69" spans="3:84" x14ac:dyDescent="0.2">
+      <c r="CG68" s="4"/>
+      <c r="CH68" s="4"/>
+      <c r="CI68" s="4"/>
+      <c r="CJ68" s="4"/>
+    </row>
+    <row r="69" spans="3:88" x14ac:dyDescent="0.2">
       <c r="C69" s="4"/>
       <c r="D69" s="4"/>
       <c r="E69" s="4"/>
@@ -7285,8 +7656,12 @@
       <c r="CD69" s="4"/>
       <c r="CE69" s="4"/>
       <c r="CF69" s="4"/>
-    </row>
-    <row r="70" spans="3:84" x14ac:dyDescent="0.2">
+      <c r="CG69" s="4"/>
+      <c r="CH69" s="4"/>
+      <c r="CI69" s="4"/>
+      <c r="CJ69" s="4"/>
+    </row>
+    <row r="70" spans="3:88" x14ac:dyDescent="0.2">
       <c r="C70" s="4"/>
       <c r="D70" s="4"/>
       <c r="E70" s="4"/>
@@ -7369,8 +7744,12 @@
       <c r="CD70" s="4"/>
       <c r="CE70" s="4"/>
       <c r="CF70" s="4"/>
-    </row>
-    <row r="71" spans="3:84" x14ac:dyDescent="0.2">
+      <c r="CG70" s="4"/>
+      <c r="CH70" s="4"/>
+      <c r="CI70" s="4"/>
+      <c r="CJ70" s="4"/>
+    </row>
+    <row r="71" spans="3:88" x14ac:dyDescent="0.2">
       <c r="C71" s="4"/>
       <c r="D71" s="4"/>
       <c r="E71" s="4"/>
@@ -7453,8 +7832,12 @@
       <c r="CD71" s="4"/>
       <c r="CE71" s="4"/>
       <c r="CF71" s="4"/>
-    </row>
-    <row r="72" spans="3:84" x14ac:dyDescent="0.2">
+      <c r="CG71" s="4"/>
+      <c r="CH71" s="4"/>
+      <c r="CI71" s="4"/>
+      <c r="CJ71" s="4"/>
+    </row>
+    <row r="72" spans="3:88" x14ac:dyDescent="0.2">
       <c r="C72" s="4"/>
       <c r="D72" s="4"/>
       <c r="E72" s="4"/>
@@ -7537,8 +7920,12 @@
       <c r="CD72" s="4"/>
       <c r="CE72" s="4"/>
       <c r="CF72" s="4"/>
-    </row>
-    <row r="73" spans="3:84" x14ac:dyDescent="0.2">
+      <c r="CG72" s="4"/>
+      <c r="CH72" s="4"/>
+      <c r="CI72" s="4"/>
+      <c r="CJ72" s="4"/>
+    </row>
+    <row r="73" spans="3:88" x14ac:dyDescent="0.2">
       <c r="C73" s="4"/>
       <c r="D73" s="4"/>
       <c r="E73" s="4"/>
@@ -7621,8 +8008,12 @@
       <c r="CD73" s="4"/>
       <c r="CE73" s="4"/>
       <c r="CF73" s="4"/>
-    </row>
-    <row r="74" spans="3:84" x14ac:dyDescent="0.2">
+      <c r="CG73" s="4"/>
+      <c r="CH73" s="4"/>
+      <c r="CI73" s="4"/>
+      <c r="CJ73" s="4"/>
+    </row>
+    <row r="74" spans="3:88" x14ac:dyDescent="0.2">
       <c r="C74" s="4"/>
       <c r="D74" s="4"/>
       <c r="E74" s="4"/>
@@ -7705,8 +8096,12 @@
       <c r="CD74" s="4"/>
       <c r="CE74" s="4"/>
       <c r="CF74" s="4"/>
-    </row>
-    <row r="75" spans="3:84" x14ac:dyDescent="0.2">
+      <c r="CG74" s="4"/>
+      <c r="CH74" s="4"/>
+      <c r="CI74" s="4"/>
+      <c r="CJ74" s="4"/>
+    </row>
+    <row r="75" spans="3:88" x14ac:dyDescent="0.2">
       <c r="C75" s="4"/>
       <c r="D75" s="4"/>
       <c r="E75" s="4"/>
@@ -7789,8 +8184,12 @@
       <c r="CD75" s="4"/>
       <c r="CE75" s="4"/>
       <c r="CF75" s="4"/>
-    </row>
-    <row r="76" spans="3:84" x14ac:dyDescent="0.2">
+      <c r="CG75" s="4"/>
+      <c r="CH75" s="4"/>
+      <c r="CI75" s="4"/>
+      <c r="CJ75" s="4"/>
+    </row>
+    <row r="76" spans="3:88" x14ac:dyDescent="0.2">
       <c r="C76" s="4"/>
       <c r="D76" s="4"/>
       <c r="E76" s="4"/>
@@ -7873,8 +8272,12 @@
       <c r="CD76" s="4"/>
       <c r="CE76" s="4"/>
       <c r="CF76" s="4"/>
-    </row>
-    <row r="77" spans="3:84" x14ac:dyDescent="0.2">
+      <c r="CG76" s="4"/>
+      <c r="CH76" s="4"/>
+      <c r="CI76" s="4"/>
+      <c r="CJ76" s="4"/>
+    </row>
+    <row r="77" spans="3:88" x14ac:dyDescent="0.2">
       <c r="C77" s="4"/>
       <c r="D77" s="4"/>
       <c r="E77" s="4"/>
@@ -7957,8 +8360,12 @@
       <c r="CD77" s="4"/>
       <c r="CE77" s="4"/>
       <c r="CF77" s="4"/>
-    </row>
-    <row r="78" spans="3:84" x14ac:dyDescent="0.2">
+      <c r="CG77" s="4"/>
+      <c r="CH77" s="4"/>
+      <c r="CI77" s="4"/>
+      <c r="CJ77" s="4"/>
+    </row>
+    <row r="78" spans="3:88" x14ac:dyDescent="0.2">
       <c r="C78" s="4"/>
       <c r="D78" s="4"/>
       <c r="E78" s="4"/>
@@ -8041,8 +8448,12 @@
       <c r="CD78" s="4"/>
       <c r="CE78" s="4"/>
       <c r="CF78" s="4"/>
-    </row>
-    <row r="79" spans="3:84" x14ac:dyDescent="0.2">
+      <c r="CG78" s="4"/>
+      <c r="CH78" s="4"/>
+      <c r="CI78" s="4"/>
+      <c r="CJ78" s="4"/>
+    </row>
+    <row r="79" spans="3:88" x14ac:dyDescent="0.2">
       <c r="C79" s="4"/>
       <c r="D79" s="4"/>
       <c r="E79" s="4"/>
@@ -8125,8 +8536,12 @@
       <c r="CD79" s="4"/>
       <c r="CE79" s="4"/>
       <c r="CF79" s="4"/>
-    </row>
-    <row r="80" spans="3:84" x14ac:dyDescent="0.2">
+      <c r="CG79" s="4"/>
+      <c r="CH79" s="4"/>
+      <c r="CI79" s="4"/>
+      <c r="CJ79" s="4"/>
+    </row>
+    <row r="80" spans="3:88" x14ac:dyDescent="0.2">
       <c r="C80" s="4"/>
       <c r="D80" s="4"/>
       <c r="E80" s="4"/>
@@ -8209,8 +8624,12 @@
       <c r="CD80" s="4"/>
       <c r="CE80" s="4"/>
       <c r="CF80" s="4"/>
-    </row>
-    <row r="81" spans="3:84" x14ac:dyDescent="0.2">
+      <c r="CG80" s="4"/>
+      <c r="CH80" s="4"/>
+      <c r="CI80" s="4"/>
+      <c r="CJ80" s="4"/>
+    </row>
+    <row r="81" spans="3:88" x14ac:dyDescent="0.2">
       <c r="C81" s="4"/>
       <c r="D81" s="4"/>
       <c r="E81" s="4"/>
@@ -8293,8 +8712,12 @@
       <c r="CD81" s="4"/>
       <c r="CE81" s="4"/>
       <c r="CF81" s="4"/>
-    </row>
-    <row r="82" spans="3:84" x14ac:dyDescent="0.2">
+      <c r="CG81" s="4"/>
+      <c r="CH81" s="4"/>
+      <c r="CI81" s="4"/>
+      <c r="CJ81" s="4"/>
+    </row>
+    <row r="82" spans="3:88" x14ac:dyDescent="0.2">
       <c r="C82" s="4"/>
       <c r="D82" s="4"/>
       <c r="E82" s="4"/>
@@ -8377,8 +8800,12 @@
       <c r="CD82" s="4"/>
       <c r="CE82" s="4"/>
       <c r="CF82" s="4"/>
-    </row>
-    <row r="83" spans="3:84" x14ac:dyDescent="0.2">
+      <c r="CG82" s="4"/>
+      <c r="CH82" s="4"/>
+      <c r="CI82" s="4"/>
+      <c r="CJ82" s="4"/>
+    </row>
+    <row r="83" spans="3:88" x14ac:dyDescent="0.2">
       <c r="C83" s="4"/>
       <c r="D83" s="4"/>
       <c r="E83" s="4"/>
@@ -8461,8 +8888,12 @@
       <c r="CD83" s="4"/>
       <c r="CE83" s="4"/>
       <c r="CF83" s="4"/>
-    </row>
-    <row r="84" spans="3:84" x14ac:dyDescent="0.2">
+      <c r="CG83" s="4"/>
+      <c r="CH83" s="4"/>
+      <c r="CI83" s="4"/>
+      <c r="CJ83" s="4"/>
+    </row>
+    <row r="84" spans="3:88" x14ac:dyDescent="0.2">
       <c r="C84" s="4"/>
       <c r="D84" s="4"/>
       <c r="E84" s="4"/>
@@ -8545,8 +8976,12 @@
       <c r="CD84" s="4"/>
       <c r="CE84" s="4"/>
       <c r="CF84" s="4"/>
-    </row>
-    <row r="85" spans="3:84" x14ac:dyDescent="0.2">
+      <c r="CG84" s="4"/>
+      <c r="CH84" s="4"/>
+      <c r="CI84" s="4"/>
+      <c r="CJ84" s="4"/>
+    </row>
+    <row r="85" spans="3:88" x14ac:dyDescent="0.2">
       <c r="C85" s="4"/>
       <c r="D85" s="4"/>
       <c r="E85" s="4"/>
@@ -8629,8 +9064,12 @@
       <c r="CD85" s="4"/>
       <c r="CE85" s="4"/>
       <c r="CF85" s="4"/>
-    </row>
-    <row r="86" spans="3:84" x14ac:dyDescent="0.2">
+      <c r="CG85" s="4"/>
+      <c r="CH85" s="4"/>
+      <c r="CI85" s="4"/>
+      <c r="CJ85" s="4"/>
+    </row>
+    <row r="86" spans="3:88" x14ac:dyDescent="0.2">
       <c r="C86" s="4"/>
       <c r="D86" s="4"/>
       <c r="E86" s="4"/>
@@ -8713,8 +9152,12 @@
       <c r="CD86" s="4"/>
       <c r="CE86" s="4"/>
       <c r="CF86" s="4"/>
-    </row>
-    <row r="87" spans="3:84" x14ac:dyDescent="0.2">
+      <c r="CG86" s="4"/>
+      <c r="CH86" s="4"/>
+      <c r="CI86" s="4"/>
+      <c r="CJ86" s="4"/>
+    </row>
+    <row r="87" spans="3:88" x14ac:dyDescent="0.2">
       <c r="C87" s="4"/>
       <c r="D87" s="4"/>
       <c r="E87" s="4"/>
@@ -8797,8 +9240,12 @@
       <c r="CD87" s="4"/>
       <c r="CE87" s="4"/>
       <c r="CF87" s="4"/>
-    </row>
-    <row r="88" spans="3:84" x14ac:dyDescent="0.2">
+      <c r="CG87" s="4"/>
+      <c r="CH87" s="4"/>
+      <c r="CI87" s="4"/>
+      <c r="CJ87" s="4"/>
+    </row>
+    <row r="88" spans="3:88" x14ac:dyDescent="0.2">
       <c r="C88" s="4"/>
       <c r="D88" s="4"/>
       <c r="E88" s="4"/>
@@ -8881,8 +9328,12 @@
       <c r="CD88" s="4"/>
       <c r="CE88" s="4"/>
       <c r="CF88" s="4"/>
-    </row>
-    <row r="89" spans="3:84" x14ac:dyDescent="0.2">
+      <c r="CG88" s="4"/>
+      <c r="CH88" s="4"/>
+      <c r="CI88" s="4"/>
+      <c r="CJ88" s="4"/>
+    </row>
+    <row r="89" spans="3:88" x14ac:dyDescent="0.2">
       <c r="C89" s="4"/>
       <c r="D89" s="4"/>
       <c r="E89" s="4"/>
@@ -8965,8 +9416,12 @@
       <c r="CD89" s="4"/>
       <c r="CE89" s="4"/>
       <c r="CF89" s="4"/>
-    </row>
-    <row r="90" spans="3:84" x14ac:dyDescent="0.2">
+      <c r="CG89" s="4"/>
+      <c r="CH89" s="4"/>
+      <c r="CI89" s="4"/>
+      <c r="CJ89" s="4"/>
+    </row>
+    <row r="90" spans="3:88" x14ac:dyDescent="0.2">
       <c r="C90" s="4"/>
       <c r="D90" s="4"/>
       <c r="E90" s="4"/>
@@ -9049,8 +9504,12 @@
       <c r="CD90" s="4"/>
       <c r="CE90" s="4"/>
       <c r="CF90" s="4"/>
-    </row>
-    <row r="91" spans="3:84" x14ac:dyDescent="0.2">
+      <c r="CG90" s="4"/>
+      <c r="CH90" s="4"/>
+      <c r="CI90" s="4"/>
+      <c r="CJ90" s="4"/>
+    </row>
+    <row r="91" spans="3:88" x14ac:dyDescent="0.2">
       <c r="C91" s="4"/>
       <c r="D91" s="4"/>
       <c r="E91" s="4"/>
@@ -9133,8 +9592,12 @@
       <c r="CD91" s="4"/>
       <c r="CE91" s="4"/>
       <c r="CF91" s="4"/>
-    </row>
-    <row r="92" spans="3:84" x14ac:dyDescent="0.2">
+      <c r="CG91" s="4"/>
+      <c r="CH91" s="4"/>
+      <c r="CI91" s="4"/>
+      <c r="CJ91" s="4"/>
+    </row>
+    <row r="92" spans="3:88" x14ac:dyDescent="0.2">
       <c r="C92" s="4"/>
       <c r="D92" s="4"/>
       <c r="E92" s="4"/>
@@ -9217,8 +9680,12 @@
       <c r="CD92" s="4"/>
       <c r="CE92" s="4"/>
       <c r="CF92" s="4"/>
-    </row>
-    <row r="93" spans="3:84" x14ac:dyDescent="0.2">
+      <c r="CG92" s="4"/>
+      <c r="CH92" s="4"/>
+      <c r="CI92" s="4"/>
+      <c r="CJ92" s="4"/>
+    </row>
+    <row r="93" spans="3:88" x14ac:dyDescent="0.2">
       <c r="C93" s="4"/>
       <c r="D93" s="4"/>
       <c r="E93" s="4"/>
@@ -9301,8 +9768,12 @@
       <c r="CD93" s="4"/>
       <c r="CE93" s="4"/>
       <c r="CF93" s="4"/>
-    </row>
-    <row r="94" spans="3:84" x14ac:dyDescent="0.2">
+      <c r="CG93" s="4"/>
+      <c r="CH93" s="4"/>
+      <c r="CI93" s="4"/>
+      <c r="CJ93" s="4"/>
+    </row>
+    <row r="94" spans="3:88" x14ac:dyDescent="0.2">
       <c r="C94" s="4"/>
       <c r="D94" s="4"/>
       <c r="E94" s="4"/>
@@ -9385,8 +9856,12 @@
       <c r="CD94" s="4"/>
       <c r="CE94" s="4"/>
       <c r="CF94" s="4"/>
-    </row>
-    <row r="95" spans="3:84" x14ac:dyDescent="0.2">
+      <c r="CG94" s="4"/>
+      <c r="CH94" s="4"/>
+      <c r="CI94" s="4"/>
+      <c r="CJ94" s="4"/>
+    </row>
+    <row r="95" spans="3:88" x14ac:dyDescent="0.2">
       <c r="C95" s="4"/>
       <c r="D95" s="4"/>
       <c r="E95" s="4"/>
@@ -9469,8 +9944,12 @@
       <c r="CD95" s="4"/>
       <c r="CE95" s="4"/>
       <c r="CF95" s="4"/>
-    </row>
-    <row r="96" spans="3:84" x14ac:dyDescent="0.2">
+      <c r="CG95" s="4"/>
+      <c r="CH95" s="4"/>
+      <c r="CI95" s="4"/>
+      <c r="CJ95" s="4"/>
+    </row>
+    <row r="96" spans="3:88" x14ac:dyDescent="0.2">
       <c r="C96" s="4"/>
       <c r="D96" s="4"/>
       <c r="E96" s="4"/>
@@ -9553,8 +10032,12 @@
       <c r="CD96" s="4"/>
       <c r="CE96" s="4"/>
       <c r="CF96" s="4"/>
-    </row>
-    <row r="97" spans="3:84" x14ac:dyDescent="0.2">
+      <c r="CG96" s="4"/>
+      <c r="CH96" s="4"/>
+      <c r="CI96" s="4"/>
+      <c r="CJ96" s="4"/>
+    </row>
+    <row r="97" spans="3:88" x14ac:dyDescent="0.2">
       <c r="C97" s="4"/>
       <c r="D97" s="4"/>
       <c r="E97" s="4"/>
@@ -9637,8 +10120,12 @@
       <c r="CD97" s="4"/>
       <c r="CE97" s="4"/>
       <c r="CF97" s="4"/>
-    </row>
-    <row r="98" spans="3:84" x14ac:dyDescent="0.2">
+      <c r="CG97" s="4"/>
+      <c r="CH97" s="4"/>
+      <c r="CI97" s="4"/>
+      <c r="CJ97" s="4"/>
+    </row>
+    <row r="98" spans="3:88" x14ac:dyDescent="0.2">
       <c r="C98" s="4"/>
       <c r="D98" s="4"/>
       <c r="E98" s="4"/>
@@ -9721,8 +10208,12 @@
       <c r="CD98" s="4"/>
       <c r="CE98" s="4"/>
       <c r="CF98" s="4"/>
-    </row>
-    <row r="99" spans="3:84" x14ac:dyDescent="0.2">
+      <c r="CG98" s="4"/>
+      <c r="CH98" s="4"/>
+      <c r="CI98" s="4"/>
+      <c r="CJ98" s="4"/>
+    </row>
+    <row r="99" spans="3:88" x14ac:dyDescent="0.2">
       <c r="C99" s="4"/>
       <c r="D99" s="4"/>
       <c r="E99" s="4"/>
@@ -9805,8 +10296,12 @@
       <c r="CD99" s="4"/>
       <c r="CE99" s="4"/>
       <c r="CF99" s="4"/>
-    </row>
-    <row r="100" spans="3:84" x14ac:dyDescent="0.2">
+      <c r="CG99" s="4"/>
+      <c r="CH99" s="4"/>
+      <c r="CI99" s="4"/>
+      <c r="CJ99" s="4"/>
+    </row>
+    <row r="100" spans="3:88" x14ac:dyDescent="0.2">
       <c r="C100" s="4"/>
       <c r="D100" s="4"/>
       <c r="E100" s="4"/>
@@ -9889,8 +10384,12 @@
       <c r="CD100" s="4"/>
       <c r="CE100" s="4"/>
       <c r="CF100" s="4"/>
-    </row>
-    <row r="101" spans="3:84" x14ac:dyDescent="0.2">
+      <c r="CG100" s="4"/>
+      <c r="CH100" s="4"/>
+      <c r="CI100" s="4"/>
+      <c r="CJ100" s="4"/>
+    </row>
+    <row r="101" spans="3:88" x14ac:dyDescent="0.2">
       <c r="C101" s="4"/>
       <c r="D101" s="4"/>
       <c r="E101" s="4"/>
@@ -9973,8 +10472,12 @@
       <c r="CD101" s="4"/>
       <c r="CE101" s="4"/>
       <c r="CF101" s="4"/>
-    </row>
-    <row r="102" spans="3:84" x14ac:dyDescent="0.2">
+      <c r="CG101" s="4"/>
+      <c r="CH101" s="4"/>
+      <c r="CI101" s="4"/>
+      <c r="CJ101" s="4"/>
+    </row>
+    <row r="102" spans="3:88" x14ac:dyDescent="0.2">
       <c r="C102" s="4"/>
       <c r="D102" s="4"/>
       <c r="E102" s="4"/>
@@ -10057,8 +10560,12 @@
       <c r="CD102" s="4"/>
       <c r="CE102" s="4"/>
       <c r="CF102" s="4"/>
-    </row>
-    <row r="103" spans="3:84" x14ac:dyDescent="0.2">
+      <c r="CG102" s="4"/>
+      <c r="CH102" s="4"/>
+      <c r="CI102" s="4"/>
+      <c r="CJ102" s="4"/>
+    </row>
+    <row r="103" spans="3:88" x14ac:dyDescent="0.2">
       <c r="C103" s="4"/>
       <c r="D103" s="4"/>
       <c r="E103" s="4"/>
@@ -10141,8 +10648,12 @@
       <c r="CD103" s="4"/>
       <c r="CE103" s="4"/>
       <c r="CF103" s="4"/>
-    </row>
-    <row r="104" spans="3:84" x14ac:dyDescent="0.2">
+      <c r="CG103" s="4"/>
+      <c r="CH103" s="4"/>
+      <c r="CI103" s="4"/>
+      <c r="CJ103" s="4"/>
+    </row>
+    <row r="104" spans="3:88" x14ac:dyDescent="0.2">
       <c r="C104" s="4"/>
       <c r="D104" s="4"/>
       <c r="E104" s="4"/>
@@ -10225,8 +10736,12 @@
       <c r="CD104" s="4"/>
       <c r="CE104" s="4"/>
       <c r="CF104" s="4"/>
-    </row>
-    <row r="105" spans="3:84" x14ac:dyDescent="0.2">
+      <c r="CG104" s="4"/>
+      <c r="CH104" s="4"/>
+      <c r="CI104" s="4"/>
+      <c r="CJ104" s="4"/>
+    </row>
+    <row r="105" spans="3:88" x14ac:dyDescent="0.2">
       <c r="C105" s="4"/>
       <c r="D105" s="4"/>
       <c r="E105" s="4"/>
@@ -10309,8 +10824,12 @@
       <c r="CD105" s="4"/>
       <c r="CE105" s="4"/>
       <c r="CF105" s="4"/>
-    </row>
-    <row r="106" spans="3:84" x14ac:dyDescent="0.2">
+      <c r="CG105" s="4"/>
+      <c r="CH105" s="4"/>
+      <c r="CI105" s="4"/>
+      <c r="CJ105" s="4"/>
+    </row>
+    <row r="106" spans="3:88" x14ac:dyDescent="0.2">
       <c r="C106" s="4"/>
       <c r="D106" s="4"/>
       <c r="E106" s="4"/>
@@ -10393,8 +10912,12 @@
       <c r="CD106" s="4"/>
       <c r="CE106" s="4"/>
       <c r="CF106" s="4"/>
-    </row>
-    <row r="107" spans="3:84" x14ac:dyDescent="0.2">
+      <c r="CG106" s="4"/>
+      <c r="CH106" s="4"/>
+      <c r="CI106" s="4"/>
+      <c r="CJ106" s="4"/>
+    </row>
+    <row r="107" spans="3:88" x14ac:dyDescent="0.2">
       <c r="C107" s="4"/>
       <c r="D107" s="4"/>
       <c r="E107" s="4"/>
@@ -10477,8 +11000,12 @@
       <c r="CD107" s="4"/>
       <c r="CE107" s="4"/>
       <c r="CF107" s="4"/>
-    </row>
-    <row r="108" spans="3:84" x14ac:dyDescent="0.2">
+      <c r="CG107" s="4"/>
+      <c r="CH107" s="4"/>
+      <c r="CI107" s="4"/>
+      <c r="CJ107" s="4"/>
+    </row>
+    <row r="108" spans="3:88" x14ac:dyDescent="0.2">
       <c r="C108" s="4"/>
       <c r="D108" s="4"/>
       <c r="E108" s="4"/>
@@ -10561,8 +11088,12 @@
       <c r="CD108" s="4"/>
       <c r="CE108" s="4"/>
       <c r="CF108" s="4"/>
-    </row>
-    <row r="109" spans="3:84" x14ac:dyDescent="0.2">
+      <c r="CG108" s="4"/>
+      <c r="CH108" s="4"/>
+      <c r="CI108" s="4"/>
+      <c r="CJ108" s="4"/>
+    </row>
+    <row r="109" spans="3:88" x14ac:dyDescent="0.2">
       <c r="C109" s="4"/>
       <c r="D109" s="4"/>
       <c r="E109" s="4"/>
@@ -10645,8 +11176,12 @@
       <c r="CD109" s="4"/>
       <c r="CE109" s="4"/>
       <c r="CF109" s="4"/>
-    </row>
-    <row r="110" spans="3:84" x14ac:dyDescent="0.2">
+      <c r="CG109" s="4"/>
+      <c r="CH109" s="4"/>
+      <c r="CI109" s="4"/>
+      <c r="CJ109" s="4"/>
+    </row>
+    <row r="110" spans="3:88" x14ac:dyDescent="0.2">
       <c r="C110" s="4"/>
       <c r="D110" s="4"/>
       <c r="E110" s="4"/>
@@ -10729,8 +11264,12 @@
       <c r="CD110" s="4"/>
       <c r="CE110" s="4"/>
       <c r="CF110" s="4"/>
-    </row>
-    <row r="111" spans="3:84" x14ac:dyDescent="0.2">
+      <c r="CG110" s="4"/>
+      <c r="CH110" s="4"/>
+      <c r="CI110" s="4"/>
+      <c r="CJ110" s="4"/>
+    </row>
+    <row r="111" spans="3:88" x14ac:dyDescent="0.2">
       <c r="C111" s="4"/>
       <c r="D111" s="4"/>
       <c r="E111" s="4"/>
@@ -10813,8 +11352,12 @@
       <c r="CD111" s="4"/>
       <c r="CE111" s="4"/>
       <c r="CF111" s="4"/>
-    </row>
-    <row r="112" spans="3:84" x14ac:dyDescent="0.2">
+      <c r="CG111" s="4"/>
+      <c r="CH111" s="4"/>
+      <c r="CI111" s="4"/>
+      <c r="CJ111" s="4"/>
+    </row>
+    <row r="112" spans="3:88" x14ac:dyDescent="0.2">
       <c r="C112" s="4"/>
       <c r="D112" s="4"/>
       <c r="E112" s="4"/>
@@ -10897,8 +11440,12 @@
       <c r="CD112" s="4"/>
       <c r="CE112" s="4"/>
       <c r="CF112" s="4"/>
-    </row>
-    <row r="113" spans="3:84" x14ac:dyDescent="0.2">
+      <c r="CG112" s="4"/>
+      <c r="CH112" s="4"/>
+      <c r="CI112" s="4"/>
+      <c r="CJ112" s="4"/>
+    </row>
+    <row r="113" spans="3:88" x14ac:dyDescent="0.2">
       <c r="C113" s="4"/>
       <c r="D113" s="4"/>
       <c r="E113" s="4"/>
@@ -10981,8 +11528,12 @@
       <c r="CD113" s="4"/>
       <c r="CE113" s="4"/>
       <c r="CF113" s="4"/>
-    </row>
-    <row r="114" spans="3:84" x14ac:dyDescent="0.2">
+      <c r="CG113" s="4"/>
+      <c r="CH113" s="4"/>
+      <c r="CI113" s="4"/>
+      <c r="CJ113" s="4"/>
+    </row>
+    <row r="114" spans="3:88" x14ac:dyDescent="0.2">
       <c r="C114" s="4"/>
       <c r="D114" s="4"/>
       <c r="E114" s="4"/>
@@ -11065,8 +11616,12 @@
       <c r="CD114" s="4"/>
       <c r="CE114" s="4"/>
       <c r="CF114" s="4"/>
-    </row>
-    <row r="115" spans="3:84" x14ac:dyDescent="0.2">
+      <c r="CG114" s="4"/>
+      <c r="CH114" s="4"/>
+      <c r="CI114" s="4"/>
+      <c r="CJ114" s="4"/>
+    </row>
+    <row r="115" spans="3:88" x14ac:dyDescent="0.2">
       <c r="C115" s="4"/>
       <c r="D115" s="4"/>
       <c r="E115" s="4"/>
@@ -11149,8 +11704,12 @@
       <c r="CD115" s="4"/>
       <c r="CE115" s="4"/>
       <c r="CF115" s="4"/>
-    </row>
-    <row r="116" spans="3:84" x14ac:dyDescent="0.2">
+      <c r="CG115" s="4"/>
+      <c r="CH115" s="4"/>
+      <c r="CI115" s="4"/>
+      <c r="CJ115" s="4"/>
+    </row>
+    <row r="116" spans="3:88" x14ac:dyDescent="0.2">
       <c r="C116" s="4"/>
       <c r="D116" s="4"/>
       <c r="E116" s="4"/>
@@ -11233,8 +11792,12 @@
       <c r="CD116" s="4"/>
       <c r="CE116" s="4"/>
       <c r="CF116" s="4"/>
-    </row>
-    <row r="117" spans="3:84" x14ac:dyDescent="0.2">
+      <c r="CG116" s="4"/>
+      <c r="CH116" s="4"/>
+      <c r="CI116" s="4"/>
+      <c r="CJ116" s="4"/>
+    </row>
+    <row r="117" spans="3:88" x14ac:dyDescent="0.2">
       <c r="C117" s="4"/>
       <c r="D117" s="4"/>
       <c r="E117" s="4"/>
@@ -11317,8 +11880,12 @@
       <c r="CD117" s="4"/>
       <c r="CE117" s="4"/>
       <c r="CF117" s="4"/>
-    </row>
-    <row r="118" spans="3:84" x14ac:dyDescent="0.2">
+      <c r="CG117" s="4"/>
+      <c r="CH117" s="4"/>
+      <c r="CI117" s="4"/>
+      <c r="CJ117" s="4"/>
+    </row>
+    <row r="118" spans="3:88" x14ac:dyDescent="0.2">
       <c r="C118" s="4"/>
       <c r="D118" s="4"/>
       <c r="E118" s="4"/>
@@ -11401,8 +11968,12 @@
       <c r="CD118" s="4"/>
       <c r="CE118" s="4"/>
       <c r="CF118" s="4"/>
-    </row>
-    <row r="119" spans="3:84" x14ac:dyDescent="0.2">
+      <c r="CG118" s="4"/>
+      <c r="CH118" s="4"/>
+      <c r="CI118" s="4"/>
+      <c r="CJ118" s="4"/>
+    </row>
+    <row r="119" spans="3:88" x14ac:dyDescent="0.2">
       <c r="C119" s="4"/>
       <c r="D119" s="4"/>
       <c r="E119" s="4"/>
@@ -11485,8 +12056,12 @@
       <c r="CD119" s="4"/>
       <c r="CE119" s="4"/>
       <c r="CF119" s="4"/>
-    </row>
-    <row r="120" spans="3:84" x14ac:dyDescent="0.2">
+      <c r="CG119" s="4"/>
+      <c r="CH119" s="4"/>
+      <c r="CI119" s="4"/>
+      <c r="CJ119" s="4"/>
+    </row>
+    <row r="120" spans="3:88" x14ac:dyDescent="0.2">
       <c r="C120" s="4"/>
       <c r="D120" s="4"/>
       <c r="E120" s="4"/>
@@ -11569,8 +12144,12 @@
       <c r="CD120" s="4"/>
       <c r="CE120" s="4"/>
       <c r="CF120" s="4"/>
-    </row>
-    <row r="121" spans="3:84" x14ac:dyDescent="0.2">
+      <c r="CG120" s="4"/>
+      <c r="CH120" s="4"/>
+      <c r="CI120" s="4"/>
+      <c r="CJ120" s="4"/>
+    </row>
+    <row r="121" spans="3:88" x14ac:dyDescent="0.2">
       <c r="C121" s="4"/>
       <c r="D121" s="4"/>
       <c r="E121" s="4"/>
@@ -11653,8 +12232,12 @@
       <c r="CD121" s="4"/>
       <c r="CE121" s="4"/>
       <c r="CF121" s="4"/>
-    </row>
-    <row r="122" spans="3:84" x14ac:dyDescent="0.2">
+      <c r="CG121" s="4"/>
+      <c r="CH121" s="4"/>
+      <c r="CI121" s="4"/>
+      <c r="CJ121" s="4"/>
+    </row>
+    <row r="122" spans="3:88" x14ac:dyDescent="0.2">
       <c r="C122" s="4"/>
       <c r="D122" s="4"/>
       <c r="E122" s="4"/>
@@ -11737,8 +12320,12 @@
       <c r="CD122" s="4"/>
       <c r="CE122" s="4"/>
       <c r="CF122" s="4"/>
-    </row>
-    <row r="123" spans="3:84" x14ac:dyDescent="0.2">
+      <c r="CG122" s="4"/>
+      <c r="CH122" s="4"/>
+      <c r="CI122" s="4"/>
+      <c r="CJ122" s="4"/>
+    </row>
+    <row r="123" spans="3:88" x14ac:dyDescent="0.2">
       <c r="C123" s="4"/>
       <c r="D123" s="4"/>
       <c r="E123" s="4"/>
@@ -11821,8 +12408,12 @@
       <c r="CD123" s="4"/>
       <c r="CE123" s="4"/>
       <c r="CF123" s="4"/>
-    </row>
-    <row r="124" spans="3:84" x14ac:dyDescent="0.2">
+      <c r="CG123" s="4"/>
+      <c r="CH123" s="4"/>
+      <c r="CI123" s="4"/>
+      <c r="CJ123" s="4"/>
+    </row>
+    <row r="124" spans="3:88" x14ac:dyDescent="0.2">
       <c r="C124" s="4"/>
       <c r="D124" s="4"/>
       <c r="E124" s="4"/>
@@ -11905,8 +12496,12 @@
       <c r="CD124" s="4"/>
       <c r="CE124" s="4"/>
       <c r="CF124" s="4"/>
-    </row>
-    <row r="125" spans="3:84" x14ac:dyDescent="0.2">
+      <c r="CG124" s="4"/>
+      <c r="CH124" s="4"/>
+      <c r="CI124" s="4"/>
+      <c r="CJ124" s="4"/>
+    </row>
+    <row r="125" spans="3:88" x14ac:dyDescent="0.2">
       <c r="C125" s="4"/>
       <c r="D125" s="4"/>
       <c r="E125" s="4"/>
@@ -11989,8 +12584,12 @@
       <c r="CD125" s="4"/>
       <c r="CE125" s="4"/>
       <c r="CF125" s="4"/>
-    </row>
-    <row r="126" spans="3:84" x14ac:dyDescent="0.2">
+      <c r="CG125" s="4"/>
+      <c r="CH125" s="4"/>
+      <c r="CI125" s="4"/>
+      <c r="CJ125" s="4"/>
+    </row>
+    <row r="126" spans="3:88" x14ac:dyDescent="0.2">
       <c r="C126" s="4"/>
       <c r="D126" s="4"/>
       <c r="E126" s="4"/>
@@ -12073,8 +12672,12 @@
       <c r="CD126" s="4"/>
       <c r="CE126" s="4"/>
       <c r="CF126" s="4"/>
-    </row>
-    <row r="127" spans="3:84" x14ac:dyDescent="0.2">
+      <c r="CG126" s="4"/>
+      <c r="CH126" s="4"/>
+      <c r="CI126" s="4"/>
+      <c r="CJ126" s="4"/>
+    </row>
+    <row r="127" spans="3:88" x14ac:dyDescent="0.2">
       <c r="C127" s="4"/>
       <c r="D127" s="4"/>
       <c r="E127" s="4"/>
@@ -12157,8 +12760,12 @@
       <c r="CD127" s="4"/>
       <c r="CE127" s="4"/>
       <c r="CF127" s="4"/>
-    </row>
-    <row r="128" spans="3:84" x14ac:dyDescent="0.2">
+      <c r="CG127" s="4"/>
+      <c r="CH127" s="4"/>
+      <c r="CI127" s="4"/>
+      <c r="CJ127" s="4"/>
+    </row>
+    <row r="128" spans="3:88" x14ac:dyDescent="0.2">
       <c r="C128" s="4"/>
       <c r="D128" s="4"/>
       <c r="E128" s="4"/>
@@ -12241,8 +12848,12 @@
       <c r="CD128" s="4"/>
       <c r="CE128" s="4"/>
       <c r="CF128" s="4"/>
-    </row>
-    <row r="129" spans="3:84" x14ac:dyDescent="0.2">
+      <c r="CG128" s="4"/>
+      <c r="CH128" s="4"/>
+      <c r="CI128" s="4"/>
+      <c r="CJ128" s="4"/>
+    </row>
+    <row r="129" spans="3:88" x14ac:dyDescent="0.2">
       <c r="C129" s="4"/>
       <c r="D129" s="4"/>
       <c r="E129" s="4"/>
@@ -12325,8 +12936,12 @@
       <c r="CD129" s="4"/>
       <c r="CE129" s="4"/>
       <c r="CF129" s="4"/>
-    </row>
-    <row r="130" spans="3:84" x14ac:dyDescent="0.2">
+      <c r="CG129" s="4"/>
+      <c r="CH129" s="4"/>
+      <c r="CI129" s="4"/>
+      <c r="CJ129" s="4"/>
+    </row>
+    <row r="130" spans="3:88" x14ac:dyDescent="0.2">
       <c r="C130" s="4"/>
       <c r="D130" s="4"/>
       <c r="E130" s="4"/>
@@ -12409,8 +13024,12 @@
       <c r="CD130" s="4"/>
       <c r="CE130" s="4"/>
       <c r="CF130" s="4"/>
-    </row>
-    <row r="131" spans="3:84" x14ac:dyDescent="0.2">
+      <c r="CG130" s="4"/>
+      <c r="CH130" s="4"/>
+      <c r="CI130" s="4"/>
+      <c r="CJ130" s="4"/>
+    </row>
+    <row r="131" spans="3:88" x14ac:dyDescent="0.2">
       <c r="C131" s="4"/>
       <c r="D131" s="4"/>
       <c r="E131" s="4"/>
@@ -12493,8 +13112,12 @@
       <c r="CD131" s="4"/>
       <c r="CE131" s="4"/>
       <c r="CF131" s="4"/>
-    </row>
-    <row r="132" spans="3:84" x14ac:dyDescent="0.2">
+      <c r="CG131" s="4"/>
+      <c r="CH131" s="4"/>
+      <c r="CI131" s="4"/>
+      <c r="CJ131" s="4"/>
+    </row>
+    <row r="132" spans="3:88" x14ac:dyDescent="0.2">
       <c r="C132" s="4"/>
       <c r="D132" s="4"/>
       <c r="E132" s="4"/>
@@ -12577,8 +13200,12 @@
       <c r="CD132" s="4"/>
       <c r="CE132" s="4"/>
       <c r="CF132" s="4"/>
-    </row>
-    <row r="133" spans="3:84" x14ac:dyDescent="0.2">
+      <c r="CG132" s="4"/>
+      <c r="CH132" s="4"/>
+      <c r="CI132" s="4"/>
+      <c r="CJ132" s="4"/>
+    </row>
+    <row r="133" spans="3:88" x14ac:dyDescent="0.2">
       <c r="C133" s="4"/>
       <c r="D133" s="4"/>
       <c r="E133" s="4"/>
@@ -12661,8 +13288,12 @@
       <c r="CD133" s="4"/>
       <c r="CE133" s="4"/>
       <c r="CF133" s="4"/>
-    </row>
-    <row r="134" spans="3:84" x14ac:dyDescent="0.2">
+      <c r="CG133" s="4"/>
+      <c r="CH133" s="4"/>
+      <c r="CI133" s="4"/>
+      <c r="CJ133" s="4"/>
+    </row>
+    <row r="134" spans="3:88" x14ac:dyDescent="0.2">
       <c r="C134" s="4"/>
       <c r="D134" s="4"/>
       <c r="E134" s="4"/>
@@ -12745,8 +13376,12 @@
       <c r="CD134" s="4"/>
       <c r="CE134" s="4"/>
       <c r="CF134" s="4"/>
-    </row>
-    <row r="135" spans="3:84" x14ac:dyDescent="0.2">
+      <c r="CG134" s="4"/>
+      <c r="CH134" s="4"/>
+      <c r="CI134" s="4"/>
+      <c r="CJ134" s="4"/>
+    </row>
+    <row r="135" spans="3:88" x14ac:dyDescent="0.2">
       <c r="C135" s="4"/>
       <c r="D135" s="4"/>
       <c r="E135" s="4"/>
@@ -12829,8 +13464,12 @@
       <c r="CD135" s="4"/>
       <c r="CE135" s="4"/>
       <c r="CF135" s="4"/>
-    </row>
-    <row r="136" spans="3:84" x14ac:dyDescent="0.2">
+      <c r="CG135" s="4"/>
+      <c r="CH135" s="4"/>
+      <c r="CI135" s="4"/>
+      <c r="CJ135" s="4"/>
+    </row>
+    <row r="136" spans="3:88" x14ac:dyDescent="0.2">
       <c r="C136" s="4"/>
       <c r="D136" s="4"/>
       <c r="E136" s="4"/>
@@ -12913,8 +13552,12 @@
       <c r="CD136" s="4"/>
       <c r="CE136" s="4"/>
       <c r="CF136" s="4"/>
-    </row>
-    <row r="137" spans="3:84" x14ac:dyDescent="0.2">
+      <c r="CG136" s="4"/>
+      <c r="CH136" s="4"/>
+      <c r="CI136" s="4"/>
+      <c r="CJ136" s="4"/>
+    </row>
+    <row r="137" spans="3:88" x14ac:dyDescent="0.2">
       <c r="C137" s="4"/>
       <c r="D137" s="4"/>
       <c r="E137" s="4"/>
@@ -12997,8 +13640,12 @@
       <c r="CD137" s="4"/>
       <c r="CE137" s="4"/>
       <c r="CF137" s="4"/>
-    </row>
-    <row r="138" spans="3:84" x14ac:dyDescent="0.2">
+      <c r="CG137" s="4"/>
+      <c r="CH137" s="4"/>
+      <c r="CI137" s="4"/>
+      <c r="CJ137" s="4"/>
+    </row>
+    <row r="138" spans="3:88" x14ac:dyDescent="0.2">
       <c r="C138" s="4"/>
       <c r="D138" s="4"/>
       <c r="E138" s="4"/>
@@ -13081,8 +13728,12 @@
       <c r="CD138" s="4"/>
       <c r="CE138" s="4"/>
       <c r="CF138" s="4"/>
-    </row>
-    <row r="139" spans="3:84" x14ac:dyDescent="0.2">
+      <c r="CG138" s="4"/>
+      <c r="CH138" s="4"/>
+      <c r="CI138" s="4"/>
+      <c r="CJ138" s="4"/>
+    </row>
+    <row r="139" spans="3:88" x14ac:dyDescent="0.2">
       <c r="C139" s="4"/>
       <c r="D139" s="4"/>
       <c r="E139" s="4"/>
@@ -13165,8 +13816,12 @@
       <c r="CD139" s="4"/>
       <c r="CE139" s="4"/>
       <c r="CF139" s="4"/>
-    </row>
-    <row r="140" spans="3:84" x14ac:dyDescent="0.2">
+      <c r="CG139" s="4"/>
+      <c r="CH139" s="4"/>
+      <c r="CI139" s="4"/>
+      <c r="CJ139" s="4"/>
+    </row>
+    <row r="140" spans="3:88" x14ac:dyDescent="0.2">
       <c r="C140" s="4"/>
       <c r="D140" s="4"/>
       <c r="E140" s="4"/>
@@ -13249,8 +13904,12 @@
       <c r="CD140" s="4"/>
       <c r="CE140" s="4"/>
       <c r="CF140" s="4"/>
-    </row>
-    <row r="141" spans="3:84" x14ac:dyDescent="0.2">
+      <c r="CG140" s="4"/>
+      <c r="CH140" s="4"/>
+      <c r="CI140" s="4"/>
+      <c r="CJ140" s="4"/>
+    </row>
+    <row r="141" spans="3:88" x14ac:dyDescent="0.2">
       <c r="C141" s="4"/>
       <c r="D141" s="4"/>
       <c r="E141" s="4"/>
@@ -13333,8 +13992,12 @@
       <c r="CD141" s="4"/>
       <c r="CE141" s="4"/>
       <c r="CF141" s="4"/>
-    </row>
-    <row r="142" spans="3:84" x14ac:dyDescent="0.2">
+      <c r="CG141" s="4"/>
+      <c r="CH141" s="4"/>
+      <c r="CI141" s="4"/>
+      <c r="CJ141" s="4"/>
+    </row>
+    <row r="142" spans="3:88" x14ac:dyDescent="0.2">
       <c r="C142" s="4"/>
       <c r="D142" s="4"/>
       <c r="E142" s="4"/>
@@ -13417,8 +14080,12 @@
       <c r="CD142" s="4"/>
       <c r="CE142" s="4"/>
       <c r="CF142" s="4"/>
-    </row>
-    <row r="143" spans="3:84" x14ac:dyDescent="0.2">
+      <c r="CG142" s="4"/>
+      <c r="CH142" s="4"/>
+      <c r="CI142" s="4"/>
+      <c r="CJ142" s="4"/>
+    </row>
+    <row r="143" spans="3:88" x14ac:dyDescent="0.2">
       <c r="C143" s="4"/>
       <c r="D143" s="4"/>
       <c r="E143" s="4"/>
@@ -13501,8 +14168,12 @@
       <c r="CD143" s="4"/>
       <c r="CE143" s="4"/>
       <c r="CF143" s="4"/>
-    </row>
-    <row r="144" spans="3:84" x14ac:dyDescent="0.2">
+      <c r="CG143" s="4"/>
+      <c r="CH143" s="4"/>
+      <c r="CI143" s="4"/>
+      <c r="CJ143" s="4"/>
+    </row>
+    <row r="144" spans="3:88" x14ac:dyDescent="0.2">
       <c r="C144" s="4"/>
       <c r="D144" s="4"/>
       <c r="E144" s="4"/>
@@ -13585,8 +14256,12 @@
       <c r="CD144" s="4"/>
       <c r="CE144" s="4"/>
       <c r="CF144" s="4"/>
-    </row>
-    <row r="145" spans="3:84" x14ac:dyDescent="0.2">
+      <c r="CG144" s="4"/>
+      <c r="CH144" s="4"/>
+      <c r="CI144" s="4"/>
+      <c r="CJ144" s="4"/>
+    </row>
+    <row r="145" spans="3:88" x14ac:dyDescent="0.2">
       <c r="C145" s="4"/>
       <c r="D145" s="4"/>
       <c r="E145" s="4"/>
@@ -13669,8 +14344,12 @@
       <c r="CD145" s="4"/>
       <c r="CE145" s="4"/>
       <c r="CF145" s="4"/>
-    </row>
-    <row r="146" spans="3:84" x14ac:dyDescent="0.2">
+      <c r="CG145" s="4"/>
+      <c r="CH145" s="4"/>
+      <c r="CI145" s="4"/>
+      <c r="CJ145" s="4"/>
+    </row>
+    <row r="146" spans="3:88" x14ac:dyDescent="0.2">
       <c r="C146" s="4"/>
       <c r="D146" s="4"/>
       <c r="E146" s="4"/>
@@ -13753,8 +14432,12 @@
       <c r="CD146" s="4"/>
       <c r="CE146" s="4"/>
       <c r="CF146" s="4"/>
-    </row>
-    <row r="147" spans="3:84" x14ac:dyDescent="0.2">
+      <c r="CG146" s="4"/>
+      <c r="CH146" s="4"/>
+      <c r="CI146" s="4"/>
+      <c r="CJ146" s="4"/>
+    </row>
+    <row r="147" spans="3:88" x14ac:dyDescent="0.2">
       <c r="C147" s="4"/>
       <c r="D147" s="4"/>
       <c r="E147" s="4"/>
@@ -13837,8 +14520,12 @@
       <c r="CD147" s="4"/>
       <c r="CE147" s="4"/>
       <c r="CF147" s="4"/>
-    </row>
-    <row r="148" spans="3:84" x14ac:dyDescent="0.2">
+      <c r="CG147" s="4"/>
+      <c r="CH147" s="4"/>
+      <c r="CI147" s="4"/>
+      <c r="CJ147" s="4"/>
+    </row>
+    <row r="148" spans="3:88" x14ac:dyDescent="0.2">
       <c r="C148" s="4"/>
       <c r="D148" s="4"/>
       <c r="E148" s="4"/>
@@ -13921,8 +14608,12 @@
       <c r="CD148" s="4"/>
       <c r="CE148" s="4"/>
       <c r="CF148" s="4"/>
-    </row>
-    <row r="149" spans="3:84" x14ac:dyDescent="0.2">
+      <c r="CG148" s="4"/>
+      <c r="CH148" s="4"/>
+      <c r="CI148" s="4"/>
+      <c r="CJ148" s="4"/>
+    </row>
+    <row r="149" spans="3:88" x14ac:dyDescent="0.2">
       <c r="C149" s="4"/>
       <c r="D149" s="4"/>
       <c r="E149" s="4"/>
@@ -14005,8 +14696,12 @@
       <c r="CD149" s="4"/>
       <c r="CE149" s="4"/>
       <c r="CF149" s="4"/>
-    </row>
-    <row r="150" spans="3:84" x14ac:dyDescent="0.2">
+      <c r="CG149" s="4"/>
+      <c r="CH149" s="4"/>
+      <c r="CI149" s="4"/>
+      <c r="CJ149" s="4"/>
+    </row>
+    <row r="150" spans="3:88" x14ac:dyDescent="0.2">
       <c r="C150" s="4"/>
       <c r="D150" s="4"/>
       <c r="E150" s="4"/>
@@ -14089,8 +14784,12 @@
       <c r="CD150" s="4"/>
       <c r="CE150" s="4"/>
       <c r="CF150" s="4"/>
-    </row>
-    <row r="151" spans="3:84" x14ac:dyDescent="0.2">
+      <c r="CG150" s="4"/>
+      <c r="CH150" s="4"/>
+      <c r="CI150" s="4"/>
+      <c r="CJ150" s="4"/>
+    </row>
+    <row r="151" spans="3:88" x14ac:dyDescent="0.2">
       <c r="C151" s="4"/>
       <c r="D151" s="4"/>
       <c r="E151" s="4"/>
@@ -14173,8 +14872,12 @@
       <c r="CD151" s="4"/>
       <c r="CE151" s="4"/>
       <c r="CF151" s="4"/>
-    </row>
-    <row r="152" spans="3:84" x14ac:dyDescent="0.2">
+      <c r="CG151" s="4"/>
+      <c r="CH151" s="4"/>
+      <c r="CI151" s="4"/>
+      <c r="CJ151" s="4"/>
+    </row>
+    <row r="152" spans="3:88" x14ac:dyDescent="0.2">
       <c r="C152" s="4"/>
       <c r="D152" s="4"/>
       <c r="E152" s="4"/>
@@ -14257,8 +14960,12 @@
       <c r="CD152" s="4"/>
       <c r="CE152" s="4"/>
       <c r="CF152" s="4"/>
-    </row>
-    <row r="153" spans="3:84" x14ac:dyDescent="0.2">
+      <c r="CG152" s="4"/>
+      <c r="CH152" s="4"/>
+      <c r="CI152" s="4"/>
+      <c r="CJ152" s="4"/>
+    </row>
+    <row r="153" spans="3:88" x14ac:dyDescent="0.2">
       <c r="C153" s="4"/>
       <c r="D153" s="4"/>
       <c r="E153" s="4"/>
@@ -14341,8 +15048,12 @@
       <c r="CD153" s="4"/>
       <c r="CE153" s="4"/>
       <c r="CF153" s="4"/>
-    </row>
-    <row r="154" spans="3:84" x14ac:dyDescent="0.2">
+      <c r="CG153" s="4"/>
+      <c r="CH153" s="4"/>
+      <c r="CI153" s="4"/>
+      <c r="CJ153" s="4"/>
+    </row>
+    <row r="154" spans="3:88" x14ac:dyDescent="0.2">
       <c r="C154" s="4"/>
       <c r="D154" s="4"/>
       <c r="E154" s="4"/>
@@ -14425,8 +15136,12 @@
       <c r="CD154" s="4"/>
       <c r="CE154" s="4"/>
       <c r="CF154" s="4"/>
-    </row>
-    <row r="155" spans="3:84" x14ac:dyDescent="0.2">
+      <c r="CG154" s="4"/>
+      <c r="CH154" s="4"/>
+      <c r="CI154" s="4"/>
+      <c r="CJ154" s="4"/>
+    </row>
+    <row r="155" spans="3:88" x14ac:dyDescent="0.2">
       <c r="C155" s="4"/>
       <c r="D155" s="4"/>
       <c r="E155" s="4"/>
@@ -14509,8 +15224,12 @@
       <c r="CD155" s="4"/>
       <c r="CE155" s="4"/>
       <c r="CF155" s="4"/>
-    </row>
-    <row r="156" spans="3:84" x14ac:dyDescent="0.2">
+      <c r="CG155" s="4"/>
+      <c r="CH155" s="4"/>
+      <c r="CI155" s="4"/>
+      <c r="CJ155" s="4"/>
+    </row>
+    <row r="156" spans="3:88" x14ac:dyDescent="0.2">
       <c r="C156" s="4"/>
       <c r="D156" s="4"/>
       <c r="E156" s="4"/>
@@ -14593,8 +15312,12 @@
       <c r="CD156" s="4"/>
       <c r="CE156" s="4"/>
       <c r="CF156" s="4"/>
-    </row>
-    <row r="157" spans="3:84" x14ac:dyDescent="0.2">
+      <c r="CG156" s="4"/>
+      <c r="CH156" s="4"/>
+      <c r="CI156" s="4"/>
+      <c r="CJ156" s="4"/>
+    </row>
+    <row r="157" spans="3:88" x14ac:dyDescent="0.2">
       <c r="C157" s="4"/>
       <c r="D157" s="4"/>
       <c r="E157" s="4"/>
@@ -14677,8 +15400,12 @@
       <c r="CD157" s="4"/>
       <c r="CE157" s="4"/>
       <c r="CF157" s="4"/>
-    </row>
-    <row r="158" spans="3:84" x14ac:dyDescent="0.2">
+      <c r="CG157" s="4"/>
+      <c r="CH157" s="4"/>
+      <c r="CI157" s="4"/>
+      <c r="CJ157" s="4"/>
+    </row>
+    <row r="158" spans="3:88" x14ac:dyDescent="0.2">
       <c r="C158" s="4"/>
       <c r="D158" s="4"/>
       <c r="E158" s="4"/>
@@ -14761,8 +15488,12 @@
       <c r="CD158" s="4"/>
       <c r="CE158" s="4"/>
       <c r="CF158" s="4"/>
-    </row>
-    <row r="159" spans="3:84" x14ac:dyDescent="0.2">
+      <c r="CG158" s="4"/>
+      <c r="CH158" s="4"/>
+      <c r="CI158" s="4"/>
+      <c r="CJ158" s="4"/>
+    </row>
+    <row r="159" spans="3:88" x14ac:dyDescent="0.2">
       <c r="C159" s="4"/>
       <c r="D159" s="4"/>
       <c r="E159" s="4"/>
@@ -14845,8 +15576,12 @@
       <c r="CD159" s="4"/>
       <c r="CE159" s="4"/>
       <c r="CF159" s="4"/>
-    </row>
-    <row r="160" spans="3:84" x14ac:dyDescent="0.2">
+      <c r="CG159" s="4"/>
+      <c r="CH159" s="4"/>
+      <c r="CI159" s="4"/>
+      <c r="CJ159" s="4"/>
+    </row>
+    <row r="160" spans="3:88" x14ac:dyDescent="0.2">
       <c r="C160" s="4"/>
       <c r="D160" s="4"/>
       <c r="E160" s="4"/>
@@ -14929,8 +15664,12 @@
       <c r="CD160" s="4"/>
       <c r="CE160" s="4"/>
       <c r="CF160" s="4"/>
-    </row>
-    <row r="161" spans="3:84" x14ac:dyDescent="0.2">
+      <c r="CG160" s="4"/>
+      <c r="CH160" s="4"/>
+      <c r="CI160" s="4"/>
+      <c r="CJ160" s="4"/>
+    </row>
+    <row r="161" spans="3:88" x14ac:dyDescent="0.2">
       <c r="C161" s="4"/>
       <c r="D161" s="4"/>
       <c r="E161" s="4"/>
@@ -15013,8 +15752,12 @@
       <c r="CD161" s="4"/>
       <c r="CE161" s="4"/>
       <c r="CF161" s="4"/>
-    </row>
-    <row r="162" spans="3:84" x14ac:dyDescent="0.2">
+      <c r="CG161" s="4"/>
+      <c r="CH161" s="4"/>
+      <c r="CI161" s="4"/>
+      <c r="CJ161" s="4"/>
+    </row>
+    <row r="162" spans="3:88" x14ac:dyDescent="0.2">
       <c r="C162" s="4"/>
       <c r="D162" s="4"/>
       <c r="E162" s="4"/>
@@ -15097,8 +15840,12 @@
       <c r="CD162" s="4"/>
       <c r="CE162" s="4"/>
       <c r="CF162" s="4"/>
-    </row>
-    <row r="163" spans="3:84" x14ac:dyDescent="0.2">
+      <c r="CG162" s="4"/>
+      <c r="CH162" s="4"/>
+      <c r="CI162" s="4"/>
+      <c r="CJ162" s="4"/>
+    </row>
+    <row r="163" spans="3:88" x14ac:dyDescent="0.2">
       <c r="C163" s="4"/>
       <c r="D163" s="4"/>
       <c r="E163" s="4"/>
@@ -15181,8 +15928,12 @@
       <c r="CD163" s="4"/>
       <c r="CE163" s="4"/>
       <c r="CF163" s="4"/>
-    </row>
-    <row r="164" spans="3:84" x14ac:dyDescent="0.2">
+      <c r="CG163" s="4"/>
+      <c r="CH163" s="4"/>
+      <c r="CI163" s="4"/>
+      <c r="CJ163" s="4"/>
+    </row>
+    <row r="164" spans="3:88" x14ac:dyDescent="0.2">
       <c r="C164" s="4"/>
       <c r="D164" s="4"/>
       <c r="E164" s="4"/>
@@ -15265,8 +16016,12 @@
       <c r="CD164" s="4"/>
       <c r="CE164" s="4"/>
       <c r="CF164" s="4"/>
-    </row>
-    <row r="165" spans="3:84" x14ac:dyDescent="0.2">
+      <c r="CG164" s="4"/>
+      <c r="CH164" s="4"/>
+      <c r="CI164" s="4"/>
+      <c r="CJ164" s="4"/>
+    </row>
+    <row r="165" spans="3:88" x14ac:dyDescent="0.2">
       <c r="C165" s="4"/>
       <c r="D165" s="4"/>
       <c r="E165" s="4"/>
@@ -15349,8 +16104,12 @@
       <c r="CD165" s="4"/>
       <c r="CE165" s="4"/>
       <c r="CF165" s="4"/>
-    </row>
-    <row r="166" spans="3:84" x14ac:dyDescent="0.2">
+      <c r="CG165" s="4"/>
+      <c r="CH165" s="4"/>
+      <c r="CI165" s="4"/>
+      <c r="CJ165" s="4"/>
+    </row>
+    <row r="166" spans="3:88" x14ac:dyDescent="0.2">
       <c r="C166" s="4"/>
       <c r="D166" s="4"/>
       <c r="E166" s="4"/>
@@ -15433,8 +16192,12 @@
       <c r="CD166" s="4"/>
       <c r="CE166" s="4"/>
       <c r="CF166" s="4"/>
-    </row>
-    <row r="167" spans="3:84" x14ac:dyDescent="0.2">
+      <c r="CG166" s="4"/>
+      <c r="CH166" s="4"/>
+      <c r="CI166" s="4"/>
+      <c r="CJ166" s="4"/>
+    </row>
+    <row r="167" spans="3:88" x14ac:dyDescent="0.2">
       <c r="C167" s="4"/>
       <c r="D167" s="4"/>
       <c r="E167" s="4"/>
@@ -15517,8 +16280,12 @@
       <c r="CD167" s="4"/>
       <c r="CE167" s="4"/>
       <c r="CF167" s="4"/>
-    </row>
-    <row r="168" spans="3:84" x14ac:dyDescent="0.2">
+      <c r="CG167" s="4"/>
+      <c r="CH167" s="4"/>
+      <c r="CI167" s="4"/>
+      <c r="CJ167" s="4"/>
+    </row>
+    <row r="168" spans="3:88" x14ac:dyDescent="0.2">
       <c r="C168" s="4"/>
       <c r="D168" s="4"/>
       <c r="E168" s="4"/>
@@ -15601,8 +16368,12 @@
       <c r="CD168" s="4"/>
       <c r="CE168" s="4"/>
       <c r="CF168" s="4"/>
-    </row>
-    <row r="169" spans="3:84" x14ac:dyDescent="0.2">
+      <c r="CG168" s="4"/>
+      <c r="CH168" s="4"/>
+      <c r="CI168" s="4"/>
+      <c r="CJ168" s="4"/>
+    </row>
+    <row r="169" spans="3:88" x14ac:dyDescent="0.2">
       <c r="C169" s="4"/>
       <c r="D169" s="4"/>
       <c r="E169" s="4"/>
@@ -15685,8 +16456,12 @@
       <c r="CD169" s="4"/>
       <c r="CE169" s="4"/>
       <c r="CF169" s="4"/>
-    </row>
-    <row r="170" spans="3:84" x14ac:dyDescent="0.2">
+      <c r="CG169" s="4"/>
+      <c r="CH169" s="4"/>
+      <c r="CI169" s="4"/>
+      <c r="CJ169" s="4"/>
+    </row>
+    <row r="170" spans="3:88" x14ac:dyDescent="0.2">
       <c r="C170" s="4"/>
       <c r="D170" s="4"/>
       <c r="E170" s="4"/>
@@ -15769,8 +16544,12 @@
       <c r="CD170" s="4"/>
       <c r="CE170" s="4"/>
       <c r="CF170" s="4"/>
-    </row>
-    <row r="171" spans="3:84" x14ac:dyDescent="0.2">
+      <c r="CG170" s="4"/>
+      <c r="CH170" s="4"/>
+      <c r="CI170" s="4"/>
+      <c r="CJ170" s="4"/>
+    </row>
+    <row r="171" spans="3:88" x14ac:dyDescent="0.2">
       <c r="C171" s="4"/>
       <c r="D171" s="4"/>
       <c r="E171" s="4"/>
@@ -15853,8 +16632,12 @@
       <c r="CD171" s="4"/>
       <c r="CE171" s="4"/>
       <c r="CF171" s="4"/>
-    </row>
-    <row r="172" spans="3:84" x14ac:dyDescent="0.2">
+      <c r="CG171" s="4"/>
+      <c r="CH171" s="4"/>
+      <c r="CI171" s="4"/>
+      <c r="CJ171" s="4"/>
+    </row>
+    <row r="172" spans="3:88" x14ac:dyDescent="0.2">
       <c r="C172" s="4"/>
       <c r="D172" s="4"/>
       <c r="E172" s="4"/>
@@ -15937,8 +16720,12 @@
       <c r="CD172" s="4"/>
       <c r="CE172" s="4"/>
       <c r="CF172" s="4"/>
-    </row>
-    <row r="173" spans="3:84" x14ac:dyDescent="0.2">
+      <c r="CG172" s="4"/>
+      <c r="CH172" s="4"/>
+      <c r="CI172" s="4"/>
+      <c r="CJ172" s="4"/>
+    </row>
+    <row r="173" spans="3:88" x14ac:dyDescent="0.2">
       <c r="C173" s="4"/>
       <c r="D173" s="4"/>
       <c r="E173" s="4"/>
@@ -16021,8 +16808,12 @@
       <c r="CD173" s="4"/>
       <c r="CE173" s="4"/>
       <c r="CF173" s="4"/>
-    </row>
-    <row r="174" spans="3:84" x14ac:dyDescent="0.2">
+      <c r="CG173" s="4"/>
+      <c r="CH173" s="4"/>
+      <c r="CI173" s="4"/>
+      <c r="CJ173" s="4"/>
+    </row>
+    <row r="174" spans="3:88" x14ac:dyDescent="0.2">
       <c r="C174" s="4"/>
       <c r="D174" s="4"/>
       <c r="E174" s="4"/>
@@ -16105,8 +16896,12 @@
       <c r="CD174" s="4"/>
       <c r="CE174" s="4"/>
       <c r="CF174" s="4"/>
-    </row>
-    <row r="175" spans="3:84" x14ac:dyDescent="0.2">
+      <c r="CG174" s="4"/>
+      <c r="CH174" s="4"/>
+      <c r="CI174" s="4"/>
+      <c r="CJ174" s="4"/>
+    </row>
+    <row r="175" spans="3:88" x14ac:dyDescent="0.2">
       <c r="C175" s="4"/>
       <c r="D175" s="4"/>
       <c r="E175" s="4"/>
@@ -16189,8 +16984,12 @@
       <c r="CD175" s="4"/>
       <c r="CE175" s="4"/>
       <c r="CF175" s="4"/>
-    </row>
-    <row r="176" spans="3:84" x14ac:dyDescent="0.2">
+      <c r="CG175" s="4"/>
+      <c r="CH175" s="4"/>
+      <c r="CI175" s="4"/>
+      <c r="CJ175" s="4"/>
+    </row>
+    <row r="176" spans="3:88" x14ac:dyDescent="0.2">
       <c r="C176" s="4"/>
       <c r="D176" s="4"/>
       <c r="E176" s="4"/>
@@ -16273,8 +17072,12 @@
       <c r="CD176" s="4"/>
       <c r="CE176" s="4"/>
       <c r="CF176" s="4"/>
-    </row>
-    <row r="177" spans="3:84" x14ac:dyDescent="0.2">
+      <c r="CG176" s="4"/>
+      <c r="CH176" s="4"/>
+      <c r="CI176" s="4"/>
+      <c r="CJ176" s="4"/>
+    </row>
+    <row r="177" spans="3:88" x14ac:dyDescent="0.2">
       <c r="C177" s="4"/>
       <c r="D177" s="4"/>
       <c r="E177" s="4"/>
@@ -16357,8 +17160,12 @@
       <c r="CD177" s="4"/>
       <c r="CE177" s="4"/>
       <c r="CF177" s="4"/>
-    </row>
-    <row r="178" spans="3:84" x14ac:dyDescent="0.2">
+      <c r="CG177" s="4"/>
+      <c r="CH177" s="4"/>
+      <c r="CI177" s="4"/>
+      <c r="CJ177" s="4"/>
+    </row>
+    <row r="178" spans="3:88" x14ac:dyDescent="0.2">
       <c r="C178" s="4"/>
       <c r="D178" s="4"/>
       <c r="E178" s="4"/>
@@ -16441,8 +17248,12 @@
       <c r="CD178" s="4"/>
       <c r="CE178" s="4"/>
       <c r="CF178" s="4"/>
-    </row>
-    <row r="179" spans="3:84" x14ac:dyDescent="0.2">
+      <c r="CG178" s="4"/>
+      <c r="CH178" s="4"/>
+      <c r="CI178" s="4"/>
+      <c r="CJ178" s="4"/>
+    </row>
+    <row r="179" spans="3:88" x14ac:dyDescent="0.2">
       <c r="C179" s="4"/>
       <c r="D179" s="4"/>
       <c r="E179" s="4"/>
@@ -16525,8 +17336,12 @@
       <c r="CD179" s="4"/>
       <c r="CE179" s="4"/>
       <c r="CF179" s="4"/>
-    </row>
-    <row r="180" spans="3:84" x14ac:dyDescent="0.2">
+      <c r="CG179" s="4"/>
+      <c r="CH179" s="4"/>
+      <c r="CI179" s="4"/>
+      <c r="CJ179" s="4"/>
+    </row>
+    <row r="180" spans="3:88" x14ac:dyDescent="0.2">
       <c r="C180" s="4"/>
       <c r="D180" s="4"/>
       <c r="E180" s="4"/>
@@ -16609,8 +17424,12 @@
       <c r="CD180" s="4"/>
       <c r="CE180" s="4"/>
       <c r="CF180" s="4"/>
-    </row>
-    <row r="181" spans="3:84" x14ac:dyDescent="0.2">
+      <c r="CG180" s="4"/>
+      <c r="CH180" s="4"/>
+      <c r="CI180" s="4"/>
+      <c r="CJ180" s="4"/>
+    </row>
+    <row r="181" spans="3:88" x14ac:dyDescent="0.2">
       <c r="C181" s="4"/>
       <c r="D181" s="4"/>
       <c r="E181" s="4"/>
@@ -16693,8 +17512,12 @@
       <c r="CD181" s="4"/>
       <c r="CE181" s="4"/>
       <c r="CF181" s="4"/>
-    </row>
-    <row r="182" spans="3:84" x14ac:dyDescent="0.2">
+      <c r="CG181" s="4"/>
+      <c r="CH181" s="4"/>
+      <c r="CI181" s="4"/>
+      <c r="CJ181" s="4"/>
+    </row>
+    <row r="182" spans="3:88" x14ac:dyDescent="0.2">
       <c r="C182" s="4"/>
       <c r="D182" s="4"/>
       <c r="E182" s="4"/>
@@ -16777,8 +17600,12 @@
       <c r="CD182" s="4"/>
       <c r="CE182" s="4"/>
       <c r="CF182" s="4"/>
-    </row>
-    <row r="183" spans="3:84" x14ac:dyDescent="0.2">
+      <c r="CG182" s="4"/>
+      <c r="CH182" s="4"/>
+      <c r="CI182" s="4"/>
+      <c r="CJ182" s="4"/>
+    </row>
+    <row r="183" spans="3:88" x14ac:dyDescent="0.2">
       <c r="C183" s="4"/>
       <c r="D183" s="4"/>
       <c r="E183" s="4"/>
@@ -16861,8 +17688,12 @@
       <c r="CD183" s="4"/>
       <c r="CE183" s="4"/>
       <c r="CF183" s="4"/>
-    </row>
-    <row r="184" spans="3:84" x14ac:dyDescent="0.2">
+      <c r="CG183" s="4"/>
+      <c r="CH183" s="4"/>
+      <c r="CI183" s="4"/>
+      <c r="CJ183" s="4"/>
+    </row>
+    <row r="184" spans="3:88" x14ac:dyDescent="0.2">
       <c r="C184" s="4"/>
       <c r="D184" s="4"/>
       <c r="E184" s="4"/>
@@ -16945,8 +17776,12 @@
       <c r="CD184" s="4"/>
       <c r="CE184" s="4"/>
       <c r="CF184" s="4"/>
-    </row>
-    <row r="185" spans="3:84" x14ac:dyDescent="0.2">
+      <c r="CG184" s="4"/>
+      <c r="CH184" s="4"/>
+      <c r="CI184" s="4"/>
+      <c r="CJ184" s="4"/>
+    </row>
+    <row r="185" spans="3:88" x14ac:dyDescent="0.2">
       <c r="C185" s="4"/>
       <c r="D185" s="4"/>
       <c r="E185" s="4"/>
@@ -17029,8 +17864,12 @@
       <c r="CD185" s="4"/>
       <c r="CE185" s="4"/>
       <c r="CF185" s="4"/>
-    </row>
-    <row r="186" spans="3:84" x14ac:dyDescent="0.2">
+      <c r="CG185" s="4"/>
+      <c r="CH185" s="4"/>
+      <c r="CI185" s="4"/>
+      <c r="CJ185" s="4"/>
+    </row>
+    <row r="186" spans="3:88" x14ac:dyDescent="0.2">
       <c r="C186" s="4"/>
       <c r="D186" s="4"/>
       <c r="E186" s="4"/>
@@ -17113,8 +17952,12 @@
       <c r="CD186" s="4"/>
       <c r="CE186" s="4"/>
       <c r="CF186" s="4"/>
-    </row>
-    <row r="187" spans="3:84" x14ac:dyDescent="0.2">
+      <c r="CG186" s="4"/>
+      <c r="CH186" s="4"/>
+      <c r="CI186" s="4"/>
+      <c r="CJ186" s="4"/>
+    </row>
+    <row r="187" spans="3:88" x14ac:dyDescent="0.2">
       <c r="C187" s="4"/>
       <c r="D187" s="4"/>
       <c r="E187" s="4"/>
@@ -17197,8 +18040,12 @@
       <c r="CD187" s="4"/>
       <c r="CE187" s="4"/>
       <c r="CF187" s="4"/>
-    </row>
-    <row r="188" spans="3:84" x14ac:dyDescent="0.2">
+      <c r="CG187" s="4"/>
+      <c r="CH187" s="4"/>
+      <c r="CI187" s="4"/>
+      <c r="CJ187" s="4"/>
+    </row>
+    <row r="188" spans="3:88" x14ac:dyDescent="0.2">
       <c r="C188" s="4"/>
       <c r="D188" s="4"/>
       <c r="E188" s="4"/>
@@ -17281,8 +18128,12 @@
       <c r="CD188" s="4"/>
       <c r="CE188" s="4"/>
       <c r="CF188" s="4"/>
-    </row>
-    <row r="189" spans="3:84" x14ac:dyDescent="0.2">
+      <c r="CG188" s="4"/>
+      <c r="CH188" s="4"/>
+      <c r="CI188" s="4"/>
+      <c r="CJ188" s="4"/>
+    </row>
+    <row r="189" spans="3:88" x14ac:dyDescent="0.2">
       <c r="C189" s="4"/>
       <c r="D189" s="4"/>
       <c r="E189" s="4"/>
@@ -17365,8 +18216,12 @@
       <c r="CD189" s="4"/>
       <c r="CE189" s="4"/>
       <c r="CF189" s="4"/>
-    </row>
-    <row r="190" spans="3:84" x14ac:dyDescent="0.2">
+      <c r="CG189" s="4"/>
+      <c r="CH189" s="4"/>
+      <c r="CI189" s="4"/>
+      <c r="CJ189" s="4"/>
+    </row>
+    <row r="190" spans="3:88" x14ac:dyDescent="0.2">
       <c r="C190" s="4"/>
       <c r="D190" s="4"/>
       <c r="E190" s="4"/>
@@ -17449,8 +18304,12 @@
       <c r="CD190" s="4"/>
       <c r="CE190" s="4"/>
       <c r="CF190" s="4"/>
-    </row>
-    <row r="191" spans="3:84" x14ac:dyDescent="0.2">
+      <c r="CG190" s="4"/>
+      <c r="CH190" s="4"/>
+      <c r="CI190" s="4"/>
+      <c r="CJ190" s="4"/>
+    </row>
+    <row r="191" spans="3:88" x14ac:dyDescent="0.2">
       <c r="C191" s="4"/>
       <c r="D191" s="4"/>
       <c r="E191" s="4"/>
@@ -17533,8 +18392,12 @@
       <c r="CD191" s="4"/>
       <c r="CE191" s="4"/>
       <c r="CF191" s="4"/>
-    </row>
-    <row r="192" spans="3:84" x14ac:dyDescent="0.2">
+      <c r="CG191" s="4"/>
+      <c r="CH191" s="4"/>
+      <c r="CI191" s="4"/>
+      <c r="CJ191" s="4"/>
+    </row>
+    <row r="192" spans="3:88" x14ac:dyDescent="0.2">
       <c r="C192" s="4"/>
       <c r="D192" s="4"/>
       <c r="E192" s="4"/>
@@ -17617,8 +18480,12 @@
       <c r="CD192" s="4"/>
       <c r="CE192" s="4"/>
       <c r="CF192" s="4"/>
-    </row>
-    <row r="193" spans="3:84" x14ac:dyDescent="0.2">
+      <c r="CG192" s="4"/>
+      <c r="CH192" s="4"/>
+      <c r="CI192" s="4"/>
+      <c r="CJ192" s="4"/>
+    </row>
+    <row r="193" spans="3:88" x14ac:dyDescent="0.2">
       <c r="C193" s="4"/>
       <c r="D193" s="4"/>
       <c r="E193" s="4"/>
@@ -17701,8 +18568,12 @@
       <c r="CD193" s="4"/>
       <c r="CE193" s="4"/>
       <c r="CF193" s="4"/>
-    </row>
-    <row r="194" spans="3:84" x14ac:dyDescent="0.2">
+      <c r="CG193" s="4"/>
+      <c r="CH193" s="4"/>
+      <c r="CI193" s="4"/>
+      <c r="CJ193" s="4"/>
+    </row>
+    <row r="194" spans="3:88" x14ac:dyDescent="0.2">
       <c r="C194" s="4"/>
       <c r="D194" s="4"/>
       <c r="E194" s="4"/>
@@ -17785,8 +18656,12 @@
       <c r="CD194" s="4"/>
       <c r="CE194" s="4"/>
       <c r="CF194" s="4"/>
-    </row>
-    <row r="195" spans="3:84" x14ac:dyDescent="0.2">
+      <c r="CG194" s="4"/>
+      <c r="CH194" s="4"/>
+      <c r="CI194" s="4"/>
+      <c r="CJ194" s="4"/>
+    </row>
+    <row r="195" spans="3:88" x14ac:dyDescent="0.2">
       <c r="C195" s="4"/>
       <c r="D195" s="4"/>
       <c r="E195" s="4"/>
@@ -17869,8 +18744,12 @@
       <c r="CD195" s="4"/>
       <c r="CE195" s="4"/>
       <c r="CF195" s="4"/>
-    </row>
-    <row r="196" spans="3:84" x14ac:dyDescent="0.2">
+      <c r="CG195" s="4"/>
+      <c r="CH195" s="4"/>
+      <c r="CI195" s="4"/>
+      <c r="CJ195" s="4"/>
+    </row>
+    <row r="196" spans="3:88" x14ac:dyDescent="0.2">
       <c r="C196" s="4"/>
       <c r="D196" s="4"/>
       <c r="E196" s="4"/>
@@ -17953,8 +18832,12 @@
       <c r="CD196" s="4"/>
       <c r="CE196" s="4"/>
       <c r="CF196" s="4"/>
-    </row>
-    <row r="197" spans="3:84" x14ac:dyDescent="0.2">
+      <c r="CG196" s="4"/>
+      <c r="CH196" s="4"/>
+      <c r="CI196" s="4"/>
+      <c r="CJ196" s="4"/>
+    </row>
+    <row r="197" spans="3:88" x14ac:dyDescent="0.2">
       <c r="C197" s="4"/>
       <c r="D197" s="4"/>
       <c r="E197" s="4"/>
@@ -18037,8 +18920,12 @@
       <c r="CD197" s="4"/>
       <c r="CE197" s="4"/>
       <c r="CF197" s="4"/>
-    </row>
-    <row r="198" spans="3:84" x14ac:dyDescent="0.2">
+      <c r="CG197" s="4"/>
+      <c r="CH197" s="4"/>
+      <c r="CI197" s="4"/>
+      <c r="CJ197" s="4"/>
+    </row>
+    <row r="198" spans="3:88" x14ac:dyDescent="0.2">
       <c r="C198" s="4"/>
       <c r="D198" s="4"/>
       <c r="E198" s="4"/>
@@ -18121,8 +19008,12 @@
       <c r="CD198" s="4"/>
       <c r="CE198" s="4"/>
       <c r="CF198" s="4"/>
-    </row>
-    <row r="199" spans="3:84" x14ac:dyDescent="0.2">
+      <c r="CG198" s="4"/>
+      <c r="CH198" s="4"/>
+      <c r="CI198" s="4"/>
+      <c r="CJ198" s="4"/>
+    </row>
+    <row r="199" spans="3:88" x14ac:dyDescent="0.2">
       <c r="C199" s="4"/>
       <c r="D199" s="4"/>
       <c r="E199" s="4"/>
@@ -18205,8 +19096,12 @@
       <c r="CD199" s="4"/>
       <c r="CE199" s="4"/>
       <c r="CF199" s="4"/>
-    </row>
-    <row r="200" spans="3:84" x14ac:dyDescent="0.2">
+      <c r="CG199" s="4"/>
+      <c r="CH199" s="4"/>
+      <c r="CI199" s="4"/>
+      <c r="CJ199" s="4"/>
+    </row>
+    <row r="200" spans="3:88" x14ac:dyDescent="0.2">
       <c r="C200" s="4"/>
       <c r="D200" s="4"/>
       <c r="E200" s="4"/>
@@ -18289,8 +19184,12 @@
       <c r="CD200" s="4"/>
       <c r="CE200" s="4"/>
       <c r="CF200" s="4"/>
-    </row>
-    <row r="201" spans="3:84" x14ac:dyDescent="0.2">
+      <c r="CG200" s="4"/>
+      <c r="CH200" s="4"/>
+      <c r="CI200" s="4"/>
+      <c r="CJ200" s="4"/>
+    </row>
+    <row r="201" spans="3:88" x14ac:dyDescent="0.2">
       <c r="C201" s="4"/>
       <c r="D201" s="4"/>
       <c r="E201" s="4"/>
@@ -18373,8 +19272,12 @@
       <c r="CD201" s="4"/>
       <c r="CE201" s="4"/>
       <c r="CF201" s="4"/>
-    </row>
-    <row r="202" spans="3:84" x14ac:dyDescent="0.2">
+      <c r="CG201" s="4"/>
+      <c r="CH201" s="4"/>
+      <c r="CI201" s="4"/>
+      <c r="CJ201" s="4"/>
+    </row>
+    <row r="202" spans="3:88" x14ac:dyDescent="0.2">
       <c r="C202" s="4"/>
       <c r="D202" s="4"/>
       <c r="E202" s="4"/>
@@ -18457,8 +19360,12 @@
       <c r="CD202" s="4"/>
       <c r="CE202" s="4"/>
       <c r="CF202" s="4"/>
-    </row>
-    <row r="203" spans="3:84" x14ac:dyDescent="0.2">
+      <c r="CG202" s="4"/>
+      <c r="CH202" s="4"/>
+      <c r="CI202" s="4"/>
+      <c r="CJ202" s="4"/>
+    </row>
+    <row r="203" spans="3:88" x14ac:dyDescent="0.2">
       <c r="C203" s="4"/>
       <c r="D203" s="4"/>
       <c r="E203" s="4"/>
@@ -18541,8 +19448,12 @@
       <c r="CD203" s="4"/>
       <c r="CE203" s="4"/>
       <c r="CF203" s="4"/>
-    </row>
-    <row r="204" spans="3:84" x14ac:dyDescent="0.2">
+      <c r="CG203" s="4"/>
+      <c r="CH203" s="4"/>
+      <c r="CI203" s="4"/>
+      <c r="CJ203" s="4"/>
+    </row>
+    <row r="204" spans="3:88" x14ac:dyDescent="0.2">
       <c r="C204" s="4"/>
       <c r="D204" s="4"/>
       <c r="E204" s="4"/>
@@ -18625,8 +19536,12 @@
       <c r="CD204" s="4"/>
       <c r="CE204" s="4"/>
       <c r="CF204" s="4"/>
-    </row>
-    <row r="205" spans="3:84" x14ac:dyDescent="0.2">
+      <c r="CG204" s="4"/>
+      <c r="CH204" s="4"/>
+      <c r="CI204" s="4"/>
+      <c r="CJ204" s="4"/>
+    </row>
+    <row r="205" spans="3:88" x14ac:dyDescent="0.2">
       <c r="C205" s="4"/>
       <c r="D205" s="4"/>
       <c r="E205" s="4"/>
@@ -18709,8 +19624,12 @@
       <c r="CD205" s="4"/>
       <c r="CE205" s="4"/>
       <c r="CF205" s="4"/>
-    </row>
-    <row r="206" spans="3:84" x14ac:dyDescent="0.2">
+      <c r="CG205" s="4"/>
+      <c r="CH205" s="4"/>
+      <c r="CI205" s="4"/>
+      <c r="CJ205" s="4"/>
+    </row>
+    <row r="206" spans="3:88" x14ac:dyDescent="0.2">
       <c r="C206" s="4"/>
       <c r="D206" s="4"/>
       <c r="E206" s="4"/>
@@ -18793,8 +19712,12 @@
       <c r="CD206" s="4"/>
       <c r="CE206" s="4"/>
       <c r="CF206" s="4"/>
-    </row>
-    <row r="207" spans="3:84" x14ac:dyDescent="0.2">
+      <c r="CG206" s="4"/>
+      <c r="CH206" s="4"/>
+      <c r="CI206" s="4"/>
+      <c r="CJ206" s="4"/>
+    </row>
+    <row r="207" spans="3:88" x14ac:dyDescent="0.2">
       <c r="C207" s="4"/>
       <c r="D207" s="4"/>
       <c r="E207" s="4"/>
@@ -18877,8 +19800,12 @@
       <c r="CD207" s="4"/>
       <c r="CE207" s="4"/>
       <c r="CF207" s="4"/>
-    </row>
-    <row r="208" spans="3:84" x14ac:dyDescent="0.2">
+      <c r="CG207" s="4"/>
+      <c r="CH207" s="4"/>
+      <c r="CI207" s="4"/>
+      <c r="CJ207" s="4"/>
+    </row>
+    <row r="208" spans="3:88" x14ac:dyDescent="0.2">
       <c r="C208" s="4"/>
       <c r="D208" s="4"/>
       <c r="E208" s="4"/>
@@ -18961,8 +19888,12 @@
       <c r="CD208" s="4"/>
       <c r="CE208" s="4"/>
       <c r="CF208" s="4"/>
-    </row>
-    <row r="209" spans="3:84" x14ac:dyDescent="0.2">
+      <c r="CG208" s="4"/>
+      <c r="CH208" s="4"/>
+      <c r="CI208" s="4"/>
+      <c r="CJ208" s="4"/>
+    </row>
+    <row r="209" spans="3:88" x14ac:dyDescent="0.2">
       <c r="C209" s="4"/>
       <c r="D209" s="4"/>
       <c r="E209" s="4"/>
@@ -19045,8 +19976,12 @@
       <c r="CD209" s="4"/>
       <c r="CE209" s="4"/>
       <c r="CF209" s="4"/>
-    </row>
-    <row r="210" spans="3:84" x14ac:dyDescent="0.2">
+      <c r="CG209" s="4"/>
+      <c r="CH209" s="4"/>
+      <c r="CI209" s="4"/>
+      <c r="CJ209" s="4"/>
+    </row>
+    <row r="210" spans="3:88" x14ac:dyDescent="0.2">
       <c r="C210" s="4"/>
       <c r="D210" s="4"/>
       <c r="E210" s="4"/>
@@ -19129,8 +20064,12 @@
       <c r="CD210" s="4"/>
       <c r="CE210" s="4"/>
       <c r="CF210" s="4"/>
-    </row>
-    <row r="211" spans="3:84" x14ac:dyDescent="0.2">
+      <c r="CG210" s="4"/>
+      <c r="CH210" s="4"/>
+      <c r="CI210" s="4"/>
+      <c r="CJ210" s="4"/>
+    </row>
+    <row r="211" spans="3:88" x14ac:dyDescent="0.2">
       <c r="C211" s="4"/>
       <c r="D211" s="4"/>
       <c r="E211" s="4"/>
@@ -19213,8 +20152,12 @@
       <c r="CD211" s="4"/>
       <c r="CE211" s="4"/>
       <c r="CF211" s="4"/>
-    </row>
-    <row r="212" spans="3:84" x14ac:dyDescent="0.2">
+      <c r="CG211" s="4"/>
+      <c r="CH211" s="4"/>
+      <c r="CI211" s="4"/>
+      <c r="CJ211" s="4"/>
+    </row>
+    <row r="212" spans="3:88" x14ac:dyDescent="0.2">
       <c r="C212" s="4"/>
       <c r="D212" s="4"/>
       <c r="E212" s="4"/>
@@ -19297,8 +20240,12 @@
       <c r="CD212" s="4"/>
       <c r="CE212" s="4"/>
       <c r="CF212" s="4"/>
-    </row>
-    <row r="213" spans="3:84" x14ac:dyDescent="0.2">
+      <c r="CG212" s="4"/>
+      <c r="CH212" s="4"/>
+      <c r="CI212" s="4"/>
+      <c r="CJ212" s="4"/>
+    </row>
+    <row r="213" spans="3:88" x14ac:dyDescent="0.2">
       <c r="C213" s="4"/>
       <c r="D213" s="4"/>
       <c r="E213" s="4"/>
@@ -19381,8 +20328,12 @@
       <c r="CD213" s="4"/>
       <c r="CE213" s="4"/>
       <c r="CF213" s="4"/>
-    </row>
-    <row r="214" spans="3:84" x14ac:dyDescent="0.2">
+      <c r="CG213" s="4"/>
+      <c r="CH213" s="4"/>
+      <c r="CI213" s="4"/>
+      <c r="CJ213" s="4"/>
+    </row>
+    <row r="214" spans="3:88" x14ac:dyDescent="0.2">
       <c r="C214" s="4"/>
       <c r="D214" s="4"/>
       <c r="E214" s="4"/>
@@ -19465,8 +20416,12 @@
       <c r="CD214" s="4"/>
       <c r="CE214" s="4"/>
       <c r="CF214" s="4"/>
-    </row>
-    <row r="215" spans="3:84" x14ac:dyDescent="0.2">
+      <c r="CG214" s="4"/>
+      <c r="CH214" s="4"/>
+      <c r="CI214" s="4"/>
+      <c r="CJ214" s="4"/>
+    </row>
+    <row r="215" spans="3:88" x14ac:dyDescent="0.2">
       <c r="C215" s="4"/>
       <c r="D215" s="4"/>
       <c r="E215" s="4"/>
@@ -19549,8 +20504,12 @@
       <c r="CD215" s="4"/>
       <c r="CE215" s="4"/>
       <c r="CF215" s="4"/>
-    </row>
-    <row r="216" spans="3:84" x14ac:dyDescent="0.2">
+      <c r="CG215" s="4"/>
+      <c r="CH215" s="4"/>
+      <c r="CI215" s="4"/>
+      <c r="CJ215" s="4"/>
+    </row>
+    <row r="216" spans="3:88" x14ac:dyDescent="0.2">
       <c r="C216" s="4"/>
       <c r="D216" s="4"/>
       <c r="E216" s="4"/>
@@ -19633,8 +20592,12 @@
       <c r="CD216" s="4"/>
       <c r="CE216" s="4"/>
       <c r="CF216" s="4"/>
-    </row>
-    <row r="217" spans="3:84" x14ac:dyDescent="0.2">
+      <c r="CG216" s="4"/>
+      <c r="CH216" s="4"/>
+      <c r="CI216" s="4"/>
+      <c r="CJ216" s="4"/>
+    </row>
+    <row r="217" spans="3:88" x14ac:dyDescent="0.2">
       <c r="C217" s="4"/>
       <c r="D217" s="4"/>
       <c r="E217" s="4"/>
@@ -19717,8 +20680,12 @@
       <c r="CD217" s="4"/>
       <c r="CE217" s="4"/>
       <c r="CF217" s="4"/>
-    </row>
-    <row r="218" spans="3:84" x14ac:dyDescent="0.2">
+      <c r="CG217" s="4"/>
+      <c r="CH217" s="4"/>
+      <c r="CI217" s="4"/>
+      <c r="CJ217" s="4"/>
+    </row>
+    <row r="218" spans="3:88" x14ac:dyDescent="0.2">
       <c r="C218" s="4"/>
       <c r="D218" s="4"/>
       <c r="E218" s="4"/>
@@ -19801,8 +20768,12 @@
       <c r="CD218" s="4"/>
       <c r="CE218" s="4"/>
       <c r="CF218" s="4"/>
-    </row>
-    <row r="219" spans="3:84" x14ac:dyDescent="0.2">
+      <c r="CG218" s="4"/>
+      <c r="CH218" s="4"/>
+      <c r="CI218" s="4"/>
+      <c r="CJ218" s="4"/>
+    </row>
+    <row r="219" spans="3:88" x14ac:dyDescent="0.2">
       <c r="C219" s="4"/>
       <c r="D219" s="4"/>
       <c r="E219" s="4"/>
@@ -19885,8 +20856,12 @@
       <c r="CD219" s="4"/>
       <c r="CE219" s="4"/>
       <c r="CF219" s="4"/>
-    </row>
-    <row r="220" spans="3:84" x14ac:dyDescent="0.2">
+      <c r="CG219" s="4"/>
+      <c r="CH219" s="4"/>
+      <c r="CI219" s="4"/>
+      <c r="CJ219" s="4"/>
+    </row>
+    <row r="220" spans="3:88" x14ac:dyDescent="0.2">
       <c r="C220" s="4"/>
       <c r="D220" s="4"/>
       <c r="E220" s="4"/>
@@ -19969,8 +20944,12 @@
       <c r="CD220" s="4"/>
       <c r="CE220" s="4"/>
       <c r="CF220" s="4"/>
-    </row>
-    <row r="221" spans="3:84" x14ac:dyDescent="0.2">
+      <c r="CG220" s="4"/>
+      <c r="CH220" s="4"/>
+      <c r="CI220" s="4"/>
+      <c r="CJ220" s="4"/>
+    </row>
+    <row r="221" spans="3:88" x14ac:dyDescent="0.2">
       <c r="C221" s="4"/>
       <c r="D221" s="4"/>
       <c r="E221" s="4"/>
@@ -20053,8 +21032,12 @@
       <c r="CD221" s="4"/>
       <c r="CE221" s="4"/>
       <c r="CF221" s="4"/>
-    </row>
-    <row r="222" spans="3:84" x14ac:dyDescent="0.2">
+      <c r="CG221" s="4"/>
+      <c r="CH221" s="4"/>
+      <c r="CI221" s="4"/>
+      <c r="CJ221" s="4"/>
+    </row>
+    <row r="222" spans="3:88" x14ac:dyDescent="0.2">
       <c r="C222" s="4"/>
       <c r="D222" s="4"/>
       <c r="E222" s="4"/>
@@ -20137,8 +21120,12 @@
       <c r="CD222" s="4"/>
       <c r="CE222" s="4"/>
       <c r="CF222" s="4"/>
-    </row>
-    <row r="223" spans="3:84" x14ac:dyDescent="0.2">
+      <c r="CG222" s="4"/>
+      <c r="CH222" s="4"/>
+      <c r="CI222" s="4"/>
+      <c r="CJ222" s="4"/>
+    </row>
+    <row r="223" spans="3:88" x14ac:dyDescent="0.2">
       <c r="C223" s="4"/>
       <c r="D223" s="4"/>
       <c r="E223" s="4"/>
@@ -20221,8 +21208,12 @@
       <c r="CD223" s="4"/>
       <c r="CE223" s="4"/>
       <c r="CF223" s="4"/>
-    </row>
-    <row r="224" spans="3:84" x14ac:dyDescent="0.2">
+      <c r="CG223" s="4"/>
+      <c r="CH223" s="4"/>
+      <c r="CI223" s="4"/>
+      <c r="CJ223" s="4"/>
+    </row>
+    <row r="224" spans="3:88" x14ac:dyDescent="0.2">
       <c r="C224" s="4"/>
       <c r="D224" s="4"/>
       <c r="E224" s="4"/>
@@ -20305,8 +21296,12 @@
       <c r="CD224" s="4"/>
       <c r="CE224" s="4"/>
       <c r="CF224" s="4"/>
-    </row>
-    <row r="225" spans="3:84" x14ac:dyDescent="0.2">
+      <c r="CG224" s="4"/>
+      <c r="CH224" s="4"/>
+      <c r="CI224" s="4"/>
+      <c r="CJ224" s="4"/>
+    </row>
+    <row r="225" spans="3:88" x14ac:dyDescent="0.2">
       <c r="C225" s="4"/>
       <c r="D225" s="4"/>
       <c r="E225" s="4"/>
@@ -20389,8 +21384,12 @@
       <c r="CD225" s="4"/>
       <c r="CE225" s="4"/>
       <c r="CF225" s="4"/>
-    </row>
-    <row r="226" spans="3:84" x14ac:dyDescent="0.2">
+      <c r="CG225" s="4"/>
+      <c r="CH225" s="4"/>
+      <c r="CI225" s="4"/>
+      <c r="CJ225" s="4"/>
+    </row>
+    <row r="226" spans="3:88" x14ac:dyDescent="0.2">
       <c r="C226" s="4"/>
       <c r="D226" s="4"/>
       <c r="E226" s="4"/>
@@ -20473,8 +21472,12 @@
       <c r="CD226" s="4"/>
       <c r="CE226" s="4"/>
       <c r="CF226" s="4"/>
-    </row>
-    <row r="227" spans="3:84" x14ac:dyDescent="0.2">
+      <c r="CG226" s="4"/>
+      <c r="CH226" s="4"/>
+      <c r="CI226" s="4"/>
+      <c r="CJ226" s="4"/>
+    </row>
+    <row r="227" spans="3:88" x14ac:dyDescent="0.2">
       <c r="C227" s="4"/>
       <c r="D227" s="4"/>
       <c r="E227" s="4"/>
@@ -20557,8 +21560,12 @@
       <c r="CD227" s="4"/>
       <c r="CE227" s="4"/>
       <c r="CF227" s="4"/>
-    </row>
-    <row r="228" spans="3:84" x14ac:dyDescent="0.2">
+      <c r="CG227" s="4"/>
+      <c r="CH227" s="4"/>
+      <c r="CI227" s="4"/>
+      <c r="CJ227" s="4"/>
+    </row>
+    <row r="228" spans="3:88" x14ac:dyDescent="0.2">
       <c r="C228" s="4"/>
       <c r="D228" s="4"/>
       <c r="E228" s="4"/>
@@ -20641,8 +21648,12 @@
       <c r="CD228" s="4"/>
       <c r="CE228" s="4"/>
       <c r="CF228" s="4"/>
-    </row>
-    <row r="229" spans="3:84" x14ac:dyDescent="0.2">
+      <c r="CG228" s="4"/>
+      <c r="CH228" s="4"/>
+      <c r="CI228" s="4"/>
+      <c r="CJ228" s="4"/>
+    </row>
+    <row r="229" spans="3:88" x14ac:dyDescent="0.2">
       <c r="C229" s="4"/>
       <c r="D229" s="4"/>
       <c r="E229" s="4"/>
@@ -20725,8 +21736,12 @@
       <c r="CD229" s="4"/>
       <c r="CE229" s="4"/>
       <c r="CF229" s="4"/>
-    </row>
-    <row r="230" spans="3:84" x14ac:dyDescent="0.2">
+      <c r="CG229" s="4"/>
+      <c r="CH229" s="4"/>
+      <c r="CI229" s="4"/>
+      <c r="CJ229" s="4"/>
+    </row>
+    <row r="230" spans="3:88" x14ac:dyDescent="0.2">
       <c r="C230" s="4"/>
       <c r="D230" s="4"/>
       <c r="E230" s="4"/>
@@ -20809,8 +21824,12 @@
       <c r="CD230" s="4"/>
       <c r="CE230" s="4"/>
       <c r="CF230" s="4"/>
-    </row>
-    <row r="231" spans="3:84" x14ac:dyDescent="0.2">
+      <c r="CG230" s="4"/>
+      <c r="CH230" s="4"/>
+      <c r="CI230" s="4"/>
+      <c r="CJ230" s="4"/>
+    </row>
+    <row r="231" spans="3:88" x14ac:dyDescent="0.2">
       <c r="C231" s="4"/>
       <c r="D231" s="4"/>
       <c r="E231" s="4"/>
@@ -20893,8 +21912,12 @@
       <c r="CD231" s="4"/>
       <c r="CE231" s="4"/>
       <c r="CF231" s="4"/>
-    </row>
-    <row r="232" spans="3:84" x14ac:dyDescent="0.2">
+      <c r="CG231" s="4"/>
+      <c r="CH231" s="4"/>
+      <c r="CI231" s="4"/>
+      <c r="CJ231" s="4"/>
+    </row>
+    <row r="232" spans="3:88" x14ac:dyDescent="0.2">
       <c r="C232" s="4"/>
       <c r="D232" s="4"/>
       <c r="E232" s="4"/>
@@ -20977,8 +22000,12 @@
       <c r="CD232" s="4"/>
       <c r="CE232" s="4"/>
       <c r="CF232" s="4"/>
-    </row>
-    <row r="233" spans="3:84" x14ac:dyDescent="0.2">
+      <c r="CG232" s="4"/>
+      <c r="CH232" s="4"/>
+      <c r="CI232" s="4"/>
+      <c r="CJ232" s="4"/>
+    </row>
+    <row r="233" spans="3:88" x14ac:dyDescent="0.2">
       <c r="C233" s="4"/>
       <c r="D233" s="4"/>
       <c r="E233" s="4"/>
@@ -21061,8 +22088,12 @@
       <c r="CD233" s="4"/>
       <c r="CE233" s="4"/>
       <c r="CF233" s="4"/>
-    </row>
-    <row r="234" spans="3:84" x14ac:dyDescent="0.2">
+      <c r="CG233" s="4"/>
+      <c r="CH233" s="4"/>
+      <c r="CI233" s="4"/>
+      <c r="CJ233" s="4"/>
+    </row>
+    <row r="234" spans="3:88" x14ac:dyDescent="0.2">
       <c r="C234" s="4"/>
       <c r="D234" s="4"/>
       <c r="E234" s="4"/>
@@ -21145,8 +22176,12 @@
       <c r="CD234" s="4"/>
       <c r="CE234" s="4"/>
       <c r="CF234" s="4"/>
-    </row>
-    <row r="235" spans="3:84" x14ac:dyDescent="0.2">
+      <c r="CG234" s="4"/>
+      <c r="CH234" s="4"/>
+      <c r="CI234" s="4"/>
+      <c r="CJ234" s="4"/>
+    </row>
+    <row r="235" spans="3:88" x14ac:dyDescent="0.2">
       <c r="C235" s="4"/>
       <c r="D235" s="4"/>
       <c r="E235" s="4"/>
@@ -21229,8 +22264,12 @@
       <c r="CD235" s="4"/>
       <c r="CE235" s="4"/>
       <c r="CF235" s="4"/>
-    </row>
-    <row r="236" spans="3:84" x14ac:dyDescent="0.2">
+      <c r="CG235" s="4"/>
+      <c r="CH235" s="4"/>
+      <c r="CI235" s="4"/>
+      <c r="CJ235" s="4"/>
+    </row>
+    <row r="236" spans="3:88" x14ac:dyDescent="0.2">
       <c r="C236" s="4"/>
       <c r="D236" s="4"/>
       <c r="E236" s="4"/>
@@ -21313,8 +22352,12 @@
       <c r="CD236" s="4"/>
       <c r="CE236" s="4"/>
       <c r="CF236" s="4"/>
-    </row>
-    <row r="237" spans="3:84" x14ac:dyDescent="0.2">
+      <c r="CG236" s="4"/>
+      <c r="CH236" s="4"/>
+      <c r="CI236" s="4"/>
+      <c r="CJ236" s="4"/>
+    </row>
+    <row r="237" spans="3:88" x14ac:dyDescent="0.2">
       <c r="C237" s="4"/>
       <c r="D237" s="4"/>
       <c r="E237" s="4"/>
@@ -21397,8 +22440,12 @@
       <c r="CD237" s="4"/>
       <c r="CE237" s="4"/>
       <c r="CF237" s="4"/>
-    </row>
-    <row r="238" spans="3:84" x14ac:dyDescent="0.2">
+      <c r="CG237" s="4"/>
+      <c r="CH237" s="4"/>
+      <c r="CI237" s="4"/>
+      <c r="CJ237" s="4"/>
+    </row>
+    <row r="238" spans="3:88" x14ac:dyDescent="0.2">
       <c r="C238" s="4"/>
       <c r="D238" s="4"/>
       <c r="E238" s="4"/>
@@ -21481,8 +22528,12 @@
       <c r="CD238" s="4"/>
       <c r="CE238" s="4"/>
       <c r="CF238" s="4"/>
-    </row>
-    <row r="239" spans="3:84" x14ac:dyDescent="0.2">
+      <c r="CG238" s="4"/>
+      <c r="CH238" s="4"/>
+      <c r="CI238" s="4"/>
+      <c r="CJ238" s="4"/>
+    </row>
+    <row r="239" spans="3:88" x14ac:dyDescent="0.2">
       <c r="C239" s="4"/>
       <c r="D239" s="4"/>
       <c r="E239" s="4"/>
@@ -21565,8 +22616,12 @@
       <c r="CD239" s="4"/>
       <c r="CE239" s="4"/>
       <c r="CF239" s="4"/>
-    </row>
-    <row r="240" spans="3:84" x14ac:dyDescent="0.2">
+      <c r="CG239" s="4"/>
+      <c r="CH239" s="4"/>
+      <c r="CI239" s="4"/>
+      <c r="CJ239" s="4"/>
+    </row>
+    <row r="240" spans="3:88" x14ac:dyDescent="0.2">
       <c r="C240" s="4"/>
       <c r="D240" s="4"/>
       <c r="E240" s="4"/>
@@ -21649,8 +22704,12 @@
       <c r="CD240" s="4"/>
       <c r="CE240" s="4"/>
       <c r="CF240" s="4"/>
-    </row>
-    <row r="241" spans="3:84" x14ac:dyDescent="0.2">
+      <c r="CG240" s="4"/>
+      <c r="CH240" s="4"/>
+      <c r="CI240" s="4"/>
+      <c r="CJ240" s="4"/>
+    </row>
+    <row r="241" spans="3:88" x14ac:dyDescent="0.2">
       <c r="C241" s="4"/>
       <c r="D241" s="4"/>
       <c r="E241" s="4"/>
@@ -21733,8 +22792,12 @@
       <c r="CD241" s="4"/>
       <c r="CE241" s="4"/>
       <c r="CF241" s="4"/>
-    </row>
-    <row r="242" spans="3:84" x14ac:dyDescent="0.2">
+      <c r="CG241" s="4"/>
+      <c r="CH241" s="4"/>
+      <c r="CI241" s="4"/>
+      <c r="CJ241" s="4"/>
+    </row>
+    <row r="242" spans="3:88" x14ac:dyDescent="0.2">
       <c r="C242" s="4"/>
       <c r="D242" s="4"/>
       <c r="E242" s="4"/>
@@ -21817,8 +22880,12 @@
       <c r="CD242" s="4"/>
       <c r="CE242" s="4"/>
       <c r="CF242" s="4"/>
-    </row>
-    <row r="243" spans="3:84" x14ac:dyDescent="0.2">
+      <c r="CG242" s="4"/>
+      <c r="CH242" s="4"/>
+      <c r="CI242" s="4"/>
+      <c r="CJ242" s="4"/>
+    </row>
+    <row r="243" spans="3:88" x14ac:dyDescent="0.2">
       <c r="C243" s="4"/>
       <c r="D243" s="4"/>
       <c r="E243" s="4"/>
@@ -21901,8 +22968,12 @@
       <c r="CD243" s="4"/>
       <c r="CE243" s="4"/>
       <c r="CF243" s="4"/>
-    </row>
-    <row r="244" spans="3:84" x14ac:dyDescent="0.2">
+      <c r="CG243" s="4"/>
+      <c r="CH243" s="4"/>
+      <c r="CI243" s="4"/>
+      <c r="CJ243" s="4"/>
+    </row>
+    <row r="244" spans="3:88" x14ac:dyDescent="0.2">
       <c r="C244" s="4"/>
       <c r="D244" s="4"/>
       <c r="E244" s="4"/>
@@ -21985,8 +23056,12 @@
       <c r="CD244" s="4"/>
       <c r="CE244" s="4"/>
       <c r="CF244" s="4"/>
-    </row>
-    <row r="245" spans="3:84" x14ac:dyDescent="0.2">
+      <c r="CG244" s="4"/>
+      <c r="CH244" s="4"/>
+      <c r="CI244" s="4"/>
+      <c r="CJ244" s="4"/>
+    </row>
+    <row r="245" spans="3:88" x14ac:dyDescent="0.2">
       <c r="C245" s="4"/>
       <c r="D245" s="4"/>
       <c r="E245" s="4"/>
@@ -22069,8 +23144,12 @@
       <c r="CD245" s="4"/>
       <c r="CE245" s="4"/>
       <c r="CF245" s="4"/>
-    </row>
-    <row r="246" spans="3:84" x14ac:dyDescent="0.2">
+      <c r="CG245" s="4"/>
+      <c r="CH245" s="4"/>
+      <c r="CI245" s="4"/>
+      <c r="CJ245" s="4"/>
+    </row>
+    <row r="246" spans="3:88" x14ac:dyDescent="0.2">
       <c r="C246" s="4"/>
       <c r="D246" s="4"/>
       <c r="E246" s="4"/>
@@ -22153,8 +23232,12 @@
       <c r="CD246" s="4"/>
       <c r="CE246" s="4"/>
       <c r="CF246" s="4"/>
-    </row>
-    <row r="247" spans="3:84" x14ac:dyDescent="0.2">
+      <c r="CG246" s="4"/>
+      <c r="CH246" s="4"/>
+      <c r="CI246" s="4"/>
+      <c r="CJ246" s="4"/>
+    </row>
+    <row r="247" spans="3:88" x14ac:dyDescent="0.2">
       <c r="C247" s="4"/>
       <c r="D247" s="4"/>
       <c r="E247" s="4"/>
@@ -22237,8 +23320,12 @@
       <c r="CD247" s="4"/>
       <c r="CE247" s="4"/>
       <c r="CF247" s="4"/>
-    </row>
-    <row r="248" spans="3:84" x14ac:dyDescent="0.2">
+      <c r="CG247" s="4"/>
+      <c r="CH247" s="4"/>
+      <c r="CI247" s="4"/>
+      <c r="CJ247" s="4"/>
+    </row>
+    <row r="248" spans="3:88" x14ac:dyDescent="0.2">
       <c r="C248" s="4"/>
       <c r="D248" s="4"/>
       <c r="E248" s="4"/>
@@ -22321,8 +23408,12 @@
       <c r="CD248" s="4"/>
       <c r="CE248" s="4"/>
       <c r="CF248" s="4"/>
-    </row>
-    <row r="249" spans="3:84" x14ac:dyDescent="0.2">
+      <c r="CG248" s="4"/>
+      <c r="CH248" s="4"/>
+      <c r="CI248" s="4"/>
+      <c r="CJ248" s="4"/>
+    </row>
+    <row r="249" spans="3:88" x14ac:dyDescent="0.2">
       <c r="C249" s="4"/>
       <c r="D249" s="4"/>
       <c r="E249" s="4"/>
@@ -22405,8 +23496,12 @@
       <c r="CD249" s="4"/>
       <c r="CE249" s="4"/>
       <c r="CF249" s="4"/>
-    </row>
-    <row r="250" spans="3:84" x14ac:dyDescent="0.2">
+      <c r="CG249" s="4"/>
+      <c r="CH249" s="4"/>
+      <c r="CI249" s="4"/>
+      <c r="CJ249" s="4"/>
+    </row>
+    <row r="250" spans="3:88" x14ac:dyDescent="0.2">
       <c r="C250" s="4"/>
       <c r="D250" s="4"/>
       <c r="E250" s="4"/>
@@ -22489,8 +23584,12 @@
       <c r="CD250" s="4"/>
       <c r="CE250" s="4"/>
       <c r="CF250" s="4"/>
-    </row>
-    <row r="251" spans="3:84" x14ac:dyDescent="0.2">
+      <c r="CG250" s="4"/>
+      <c r="CH250" s="4"/>
+      <c r="CI250" s="4"/>
+      <c r="CJ250" s="4"/>
+    </row>
+    <row r="251" spans="3:88" x14ac:dyDescent="0.2">
       <c r="C251" s="4"/>
       <c r="D251" s="4"/>
       <c r="E251" s="4"/>
@@ -22573,8 +23672,12 @@
       <c r="CD251" s="4"/>
       <c r="CE251" s="4"/>
       <c r="CF251" s="4"/>
-    </row>
-    <row r="252" spans="3:84" x14ac:dyDescent="0.2">
+      <c r="CG251" s="4"/>
+      <c r="CH251" s="4"/>
+      <c r="CI251" s="4"/>
+      <c r="CJ251" s="4"/>
+    </row>
+    <row r="252" spans="3:88" x14ac:dyDescent="0.2">
       <c r="C252" s="4"/>
       <c r="D252" s="4"/>
       <c r="E252" s="4"/>
@@ -22657,8 +23760,12 @@
       <c r="CD252" s="4"/>
       <c r="CE252" s="4"/>
       <c r="CF252" s="4"/>
-    </row>
-    <row r="253" spans="3:84" x14ac:dyDescent="0.2">
+      <c r="CG252" s="4"/>
+      <c r="CH252" s="4"/>
+      <c r="CI252" s="4"/>
+      <c r="CJ252" s="4"/>
+    </row>
+    <row r="253" spans="3:88" x14ac:dyDescent="0.2">
       <c r="C253" s="4"/>
       <c r="D253" s="4"/>
       <c r="E253" s="4"/>
@@ -22741,8 +23848,12 @@
       <c r="CD253" s="4"/>
       <c r="CE253" s="4"/>
       <c r="CF253" s="4"/>
-    </row>
-    <row r="254" spans="3:84" x14ac:dyDescent="0.2">
+      <c r="CG253" s="4"/>
+      <c r="CH253" s="4"/>
+      <c r="CI253" s="4"/>
+      <c r="CJ253" s="4"/>
+    </row>
+    <row r="254" spans="3:88" x14ac:dyDescent="0.2">
       <c r="C254" s="4"/>
       <c r="D254" s="4"/>
       <c r="E254" s="4"/>
@@ -22825,8 +23936,12 @@
       <c r="CD254" s="4"/>
       <c r="CE254" s="4"/>
       <c r="CF254" s="4"/>
-    </row>
-    <row r="255" spans="3:84" x14ac:dyDescent="0.2">
+      <c r="CG254" s="4"/>
+      <c r="CH254" s="4"/>
+      <c r="CI254" s="4"/>
+      <c r="CJ254" s="4"/>
+    </row>
+    <row r="255" spans="3:88" x14ac:dyDescent="0.2">
       <c r="C255" s="4"/>
       <c r="D255" s="4"/>
       <c r="E255" s="4"/>
@@ -22909,8 +24024,12 @@
       <c r="CD255" s="4"/>
       <c r="CE255" s="4"/>
       <c r="CF255" s="4"/>
-    </row>
-    <row r="256" spans="3:84" x14ac:dyDescent="0.2">
+      <c r="CG255" s="4"/>
+      <c r="CH255" s="4"/>
+      <c r="CI255" s="4"/>
+      <c r="CJ255" s="4"/>
+    </row>
+    <row r="256" spans="3:88" x14ac:dyDescent="0.2">
       <c r="C256" s="4"/>
       <c r="D256" s="4"/>
       <c r="E256" s="4"/>
@@ -22993,8 +24112,12 @@
       <c r="CD256" s="4"/>
       <c r="CE256" s="4"/>
       <c r="CF256" s="4"/>
-    </row>
-    <row r="257" spans="3:84" x14ac:dyDescent="0.2">
+      <c r="CG256" s="4"/>
+      <c r="CH256" s="4"/>
+      <c r="CI256" s="4"/>
+      <c r="CJ256" s="4"/>
+    </row>
+    <row r="257" spans="3:88" x14ac:dyDescent="0.2">
       <c r="C257" s="4"/>
       <c r="D257" s="4"/>
       <c r="E257" s="4"/>
@@ -23077,8 +24200,12 @@
       <c r="CD257" s="4"/>
       <c r="CE257" s="4"/>
       <c r="CF257" s="4"/>
-    </row>
-    <row r="258" spans="3:84" x14ac:dyDescent="0.2">
+      <c r="CG257" s="4"/>
+      <c r="CH257" s="4"/>
+      <c r="CI257" s="4"/>
+      <c r="CJ257" s="4"/>
+    </row>
+    <row r="258" spans="3:88" x14ac:dyDescent="0.2">
       <c r="C258" s="4"/>
       <c r="D258" s="4"/>
       <c r="E258" s="4"/>
@@ -23161,8 +24288,12 @@
       <c r="CD258" s="4"/>
       <c r="CE258" s="4"/>
       <c r="CF258" s="4"/>
-    </row>
-    <row r="259" spans="3:84" x14ac:dyDescent="0.2">
+      <c r="CG258" s="4"/>
+      <c r="CH258" s="4"/>
+      <c r="CI258" s="4"/>
+      <c r="CJ258" s="4"/>
+    </row>
+    <row r="259" spans="3:88" x14ac:dyDescent="0.2">
       <c r="C259" s="4"/>
       <c r="D259" s="4"/>
       <c r="E259" s="4"/>
@@ -23245,8 +24376,12 @@
       <c r="CD259" s="4"/>
       <c r="CE259" s="4"/>
       <c r="CF259" s="4"/>
-    </row>
-    <row r="260" spans="3:84" x14ac:dyDescent="0.2">
+      <c r="CG259" s="4"/>
+      <c r="CH259" s="4"/>
+      <c r="CI259" s="4"/>
+      <c r="CJ259" s="4"/>
+    </row>
+    <row r="260" spans="3:88" x14ac:dyDescent="0.2">
       <c r="C260" s="4"/>
       <c r="D260" s="4"/>
       <c r="E260" s="4"/>
@@ -23329,8 +24464,12 @@
       <c r="CD260" s="4"/>
       <c r="CE260" s="4"/>
       <c r="CF260" s="4"/>
-    </row>
-    <row r="261" spans="3:84" x14ac:dyDescent="0.2">
+      <c r="CG260" s="4"/>
+      <c r="CH260" s="4"/>
+      <c r="CI260" s="4"/>
+      <c r="CJ260" s="4"/>
+    </row>
+    <row r="261" spans="3:88" x14ac:dyDescent="0.2">
       <c r="C261" s="4"/>
       <c r="D261" s="4"/>
       <c r="E261" s="4"/>
@@ -23413,8 +24552,12 @@
       <c r="CD261" s="4"/>
       <c r="CE261" s="4"/>
       <c r="CF261" s="4"/>
-    </row>
-    <row r="262" spans="3:84" x14ac:dyDescent="0.2">
+      <c r="CG261" s="4"/>
+      <c r="CH261" s="4"/>
+      <c r="CI261" s="4"/>
+      <c r="CJ261" s="4"/>
+    </row>
+    <row r="262" spans="3:88" x14ac:dyDescent="0.2">
       <c r="C262" s="4"/>
       <c r="D262" s="4"/>
       <c r="E262" s="4"/>
@@ -23497,8 +24640,12 @@
       <c r="CD262" s="4"/>
       <c r="CE262" s="4"/>
       <c r="CF262" s="4"/>
-    </row>
-    <row r="263" spans="3:84" x14ac:dyDescent="0.2">
+      <c r="CG262" s="4"/>
+      <c r="CH262" s="4"/>
+      <c r="CI262" s="4"/>
+      <c r="CJ262" s="4"/>
+    </row>
+    <row r="263" spans="3:88" x14ac:dyDescent="0.2">
       <c r="C263" s="4"/>
       <c r="D263" s="4"/>
       <c r="E263" s="4"/>
@@ -23581,8 +24728,12 @@
       <c r="CD263" s="4"/>
       <c r="CE263" s="4"/>
       <c r="CF263" s="4"/>
-    </row>
-    <row r="264" spans="3:84" x14ac:dyDescent="0.2">
+      <c r="CG263" s="4"/>
+      <c r="CH263" s="4"/>
+      <c r="CI263" s="4"/>
+      <c r="CJ263" s="4"/>
+    </row>
+    <row r="264" spans="3:88" x14ac:dyDescent="0.2">
       <c r="C264" s="4"/>
       <c r="D264" s="4"/>
       <c r="E264" s="4"/>
@@ -23665,8 +24816,12 @@
       <c r="CD264" s="4"/>
       <c r="CE264" s="4"/>
       <c r="CF264" s="4"/>
-    </row>
-    <row r="265" spans="3:84" x14ac:dyDescent="0.2">
+      <c r="CG264" s="4"/>
+      <c r="CH264" s="4"/>
+      <c r="CI264" s="4"/>
+      <c r="CJ264" s="4"/>
+    </row>
+    <row r="265" spans="3:88" x14ac:dyDescent="0.2">
       <c r="C265" s="4"/>
       <c r="D265" s="4"/>
       <c r="E265" s="4"/>
@@ -23749,8 +24904,12 @@
       <c r="CD265" s="4"/>
       <c r="CE265" s="4"/>
       <c r="CF265" s="4"/>
-    </row>
-    <row r="266" spans="3:84" x14ac:dyDescent="0.2">
+      <c r="CG265" s="4"/>
+      <c r="CH265" s="4"/>
+      <c r="CI265" s="4"/>
+      <c r="CJ265" s="4"/>
+    </row>
+    <row r="266" spans="3:88" x14ac:dyDescent="0.2">
       <c r="C266" s="4"/>
       <c r="D266" s="4"/>
       <c r="E266" s="4"/>
@@ -23833,8 +24992,12 @@
       <c r="CD266" s="4"/>
       <c r="CE266" s="4"/>
       <c r="CF266" s="4"/>
-    </row>
-    <row r="267" spans="3:84" x14ac:dyDescent="0.2">
+      <c r="CG266" s="4"/>
+      <c r="CH266" s="4"/>
+      <c r="CI266" s="4"/>
+      <c r="CJ266" s="4"/>
+    </row>
+    <row r="267" spans="3:88" x14ac:dyDescent="0.2">
       <c r="C267" s="4"/>
       <c r="D267" s="4"/>
       <c r="E267" s="4"/>
@@ -23917,8 +25080,12 @@
       <c r="CD267" s="4"/>
       <c r="CE267" s="4"/>
       <c r="CF267" s="4"/>
-    </row>
-    <row r="268" spans="3:84" x14ac:dyDescent="0.2">
+      <c r="CG267" s="4"/>
+      <c r="CH267" s="4"/>
+      <c r="CI267" s="4"/>
+      <c r="CJ267" s="4"/>
+    </row>
+    <row r="268" spans="3:88" x14ac:dyDescent="0.2">
       <c r="C268" s="4"/>
       <c r="D268" s="4"/>
       <c r="E268" s="4"/>
@@ -24001,8 +25168,12 @@
       <c r="CD268" s="4"/>
       <c r="CE268" s="4"/>
       <c r="CF268" s="4"/>
-    </row>
-    <row r="269" spans="3:84" x14ac:dyDescent="0.2">
+      <c r="CG268" s="4"/>
+      <c r="CH268" s="4"/>
+      <c r="CI268" s="4"/>
+      <c r="CJ268" s="4"/>
+    </row>
+    <row r="269" spans="3:88" x14ac:dyDescent="0.2">
       <c r="C269" s="4"/>
       <c r="D269" s="4"/>
       <c r="E269" s="4"/>
@@ -24085,8 +25256,12 @@
       <c r="CD269" s="4"/>
       <c r="CE269" s="4"/>
       <c r="CF269" s="4"/>
-    </row>
-    <row r="270" spans="3:84" x14ac:dyDescent="0.2">
+      <c r="CG269" s="4"/>
+      <c r="CH269" s="4"/>
+      <c r="CI269" s="4"/>
+      <c r="CJ269" s="4"/>
+    </row>
+    <row r="270" spans="3:88" x14ac:dyDescent="0.2">
       <c r="C270" s="4"/>
       <c r="D270" s="4"/>
       <c r="E270" s="4"/>
@@ -24169,8 +25344,12 @@
       <c r="CD270" s="4"/>
       <c r="CE270" s="4"/>
       <c r="CF270" s="4"/>
-    </row>
-    <row r="271" spans="3:84" x14ac:dyDescent="0.2">
+      <c r="CG270" s="4"/>
+      <c r="CH270" s="4"/>
+      <c r="CI270" s="4"/>
+      <c r="CJ270" s="4"/>
+    </row>
+    <row r="271" spans="3:88" x14ac:dyDescent="0.2">
       <c r="C271" s="4"/>
       <c r="D271" s="4"/>
       <c r="E271" s="4"/>
@@ -24253,8 +25432,12 @@
       <c r="CD271" s="4"/>
       <c r="CE271" s="4"/>
       <c r="CF271" s="4"/>
-    </row>
-    <row r="272" spans="3:84" x14ac:dyDescent="0.2">
+      <c r="CG271" s="4"/>
+      <c r="CH271" s="4"/>
+      <c r="CI271" s="4"/>
+      <c r="CJ271" s="4"/>
+    </row>
+    <row r="272" spans="3:88" x14ac:dyDescent="0.2">
       <c r="C272" s="4"/>
       <c r="D272" s="4"/>
       <c r="E272" s="4"/>
@@ -24337,8 +25520,12 @@
       <c r="CD272" s="4"/>
       <c r="CE272" s="4"/>
       <c r="CF272" s="4"/>
-    </row>
-    <row r="273" spans="3:84" x14ac:dyDescent="0.2">
+      <c r="CG272" s="4"/>
+      <c r="CH272" s="4"/>
+      <c r="CI272" s="4"/>
+      <c r="CJ272" s="4"/>
+    </row>
+    <row r="273" spans="3:88" x14ac:dyDescent="0.2">
       <c r="C273" s="4"/>
       <c r="D273" s="4"/>
       <c r="E273" s="4"/>
@@ -24421,6 +25608,10 @@
       <c r="CD273" s="4"/>
       <c r="CE273" s="4"/>
       <c r="CF273" s="4"/>
+      <c r="CG273" s="4"/>
+      <c r="CH273" s="4"/>
+      <c r="CI273" s="4"/>
+      <c r="CJ273" s="4"/>
     </row>
   </sheetData>
   <hyperlinks>
